--- a/SparteNet_Manager/Kleingarten_Gateway_Planung.xlsx
+++ b/SparteNet_Manager/Kleingarten_Gateway_Planung.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Ergebnis" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Anlagen!$A$4:$Z$92</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Anlagen!$A$4:$AB$92</definedName>
     <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">Ergebnis!$A$4:$N$92</definedName>
     <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Standorte!$A$4:$P$92</definedName>
     <definedName function="false" hidden="false" name="Abg_1" vbProcedure="false">Annahmen!$C$80</definedName>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="558">
   <si>
     <t xml:space="preserve">SparteNet – Gateway-Standorte, Investition und Buchungsquote der Kleingartenanlagen</t>
   </si>
@@ -177,6 +177,9 @@
     <t xml:space="preserve">• „Entfernung manuell“, „APs/Masten/Leitung manuell“: überschreiben Kartenmaß bzw. Faustregeln.</t>
   </si>
   <si>
+    <t xml:space="preserve">• „Kürzel“ (2–5 Zeichen A–Z/0–9) und „VLAN-Block“ (1–15, leer = Reihenfolge am Standort) für den VLAN-Plan (Blatt „Netz“, rechts).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Buchungsquote (Blatt „Annahmen“)</t>
   </si>
   <si>
@@ -735,6 +738,12 @@
     <t xml:space="preserve">Leitungsweg m manuell</t>
   </si>
   <si>
+    <t xml:space="preserve">Kürzel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VLAN-Block (eigene Wahl)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. März</t>
   </si>
   <si>
@@ -747,6 +756,9 @@
     <t xml:space="preserve">Stadt BRB</t>
   </si>
   <si>
+    <t xml:space="preserve">MAERZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Abendfrieden</t>
   </si>
   <si>
@@ -759,6 +771,9 @@
     <t xml:space="preserve">Stadt / Kirche</t>
   </si>
   <si>
+    <t xml:space="preserve">ABFRI</t>
+  </si>
+  <si>
     <t xml:space="preserve">Abendrot</t>
   </si>
   <si>
@@ -771,12 +786,18 @@
     <t xml:space="preserve">Stadt / privat</t>
   </si>
   <si>
+    <t xml:space="preserve">ABROT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Abendruh</t>
   </si>
   <si>
     <t xml:space="preserve">Mahlerstraße 21</t>
   </si>
   <si>
+    <t xml:space="preserve">ABRUH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Abendsonne</t>
   </si>
   <si>
@@ -786,30 +807,45 @@
     <t xml:space="preserve">Privat</t>
   </si>
   <si>
+    <t xml:space="preserve">ABSON</t>
+  </si>
+  <si>
     <t xml:space="preserve">Altstadt Forst</t>
   </si>
   <si>
     <t xml:space="preserve">Rathenower Landstraße 3</t>
   </si>
   <si>
+    <t xml:space="preserve">ALTFO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Am Beetzseeufer</t>
   </si>
   <si>
     <t xml:space="preserve">Beetzseeufer 8</t>
   </si>
   <si>
+    <t xml:space="preserve">BEETZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Am Büttelhandfassgraben</t>
   </si>
   <si>
     <t xml:space="preserve">Am Bittelhandfassgraben 14</t>
   </si>
   <si>
+    <t xml:space="preserve">BUETT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Am Eichenweg</t>
   </si>
   <si>
     <t xml:space="preserve">Ziesarer Landstraße 1</t>
   </si>
   <si>
+    <t xml:space="preserve">EICHW</t>
+  </si>
+  <si>
     <t xml:space="preserve">Am Jakobsgraben</t>
   </si>
   <si>
@@ -819,24 +855,36 @@
     <t xml:space="preserve">D – Planungskonflikt</t>
   </si>
   <si>
+    <t xml:space="preserve">JAKGR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Am Schafdamm</t>
   </si>
   <si>
     <t xml:space="preserve">Schafdamm 3</t>
   </si>
   <si>
+    <t xml:space="preserve">SCHAF</t>
+  </si>
+  <si>
     <t xml:space="preserve">Am Schlangenpfad</t>
   </si>
   <si>
     <t xml:space="preserve">Schlangenpfad 21</t>
   </si>
   <si>
+    <t xml:space="preserve">SCHLA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Am Waldesrand</t>
   </si>
   <si>
     <t xml:space="preserve">Schafdamm 1</t>
   </si>
   <si>
+    <t xml:space="preserve">WALDR</t>
+  </si>
+  <si>
     <t xml:space="preserve">An der Plane I</t>
   </si>
   <si>
@@ -846,78 +894,117 @@
     <t xml:space="preserve">Kirche</t>
   </si>
   <si>
+    <t xml:space="preserve">PLAN1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bergeshöh</t>
   </si>
   <si>
     <t xml:space="preserve">Triglafweg 20</t>
   </si>
   <si>
+    <t xml:space="preserve">BERGH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bergfrieden</t>
   </si>
   <si>
     <t xml:space="preserve">Wusterwitzer Str. 71</t>
   </si>
   <si>
+    <t xml:space="preserve">BERGF</t>
+  </si>
+  <si>
     <t xml:space="preserve">Birkenwäldchen</t>
   </si>
   <si>
     <t xml:space="preserve">Wittstocker Gäßchen 36</t>
   </si>
   <si>
+    <t xml:space="preserve">BIRKE</t>
+  </si>
+  <si>
     <t xml:space="preserve">BKV Pfefferland</t>
   </si>
   <si>
     <t xml:space="preserve">Pfefferlander Weg 11</t>
   </si>
   <si>
+    <t xml:space="preserve">PFEFF</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brielower Dreieck</t>
   </si>
   <si>
     <t xml:space="preserve">Am Industriegelande 1</t>
   </si>
   <si>
+    <t xml:space="preserve">BRIDR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Buchenweg</t>
   </si>
   <si>
     <t xml:space="preserve">Buchenweg 77</t>
   </si>
   <si>
+    <t xml:space="preserve">BW</t>
+  </si>
+  <si>
     <t xml:space="preserve">Butterlake</t>
   </si>
   <si>
     <t xml:space="preserve">Brielower Aue 30</t>
   </si>
   <si>
+    <t xml:space="preserve">BUTTL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eichhorstweg</t>
   </si>
   <si>
     <t xml:space="preserve">Eichhorstweg 15</t>
   </si>
   <si>
+    <t xml:space="preserve">EICHH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eigener Fleiß</t>
   </si>
   <si>
     <t xml:space="preserve">Hannoversche Str. 38</t>
   </si>
   <si>
+    <t xml:space="preserve">FLEIS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Einheit</t>
   </si>
   <si>
     <t xml:space="preserve">Thuringer Str. 18</t>
   </si>
   <si>
+    <t xml:space="preserve">EINH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Einigkeit</t>
   </si>
   <si>
     <t xml:space="preserve">Klingenbergstr. 2b</t>
   </si>
   <si>
+    <t xml:space="preserve">EINIG</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eintracht I</t>
   </si>
   <si>
     <t xml:space="preserve">Franz-Ziegler-Str. 29b</t>
   </si>
   <si>
+    <t xml:space="preserve">EINT1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eintracht II</t>
   </si>
   <si>
@@ -927,372 +1014,558 @@
     <t xml:space="preserve">k. A.</t>
   </si>
   <si>
+    <t xml:space="preserve">EINT2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Erdenglück</t>
   </si>
   <si>
     <t xml:space="preserve">Johannisburger Anger 26</t>
   </si>
   <si>
+    <t xml:space="preserve">ERDGL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Erntesegen</t>
   </si>
   <si>
     <t xml:space="preserve">Brahmsstr. 12b</t>
   </si>
   <si>
+    <t xml:space="preserve">ERNTE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Feierabend</t>
   </si>
   <si>
     <t xml:space="preserve">Beethovenstr. 31</t>
   </si>
   <si>
+    <t xml:space="preserve">FEIER</t>
+  </si>
+  <si>
     <t xml:space="preserve">Feldstraße</t>
   </si>
   <si>
     <t xml:space="preserve">Feldstraße 1c</t>
   </si>
   <si>
+    <t xml:space="preserve">FELD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Finkenhain</t>
   </si>
   <si>
     <t xml:space="preserve">Mendelssohnstr. 13</t>
   </si>
   <si>
+    <t xml:space="preserve">FINK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fohrder Landstraße</t>
   </si>
   <si>
     <t xml:space="preserve">Brielower Aue 33</t>
   </si>
   <si>
+    <t xml:space="preserve">FOHRD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Freiheit</t>
   </si>
   <si>
     <t xml:space="preserve">Feldstr. 1b</t>
   </si>
   <si>
+    <t xml:space="preserve">FREIH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Freizeit</t>
   </si>
   <si>
     <t xml:space="preserve">Ziesarer Landstr. 64</t>
   </si>
   <si>
+    <t xml:space="preserve">FREIZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Friedland</t>
   </si>
   <si>
     <t xml:space="preserve">Klingenbergstr. 19</t>
   </si>
   <si>
+    <t xml:space="preserve">FRIED</t>
+  </si>
+  <si>
     <t xml:space="preserve">Frisch Auf</t>
   </si>
   <si>
     <t xml:space="preserve">Klingenbergstr. 4</t>
   </si>
   <si>
+    <t xml:space="preserve">FRISA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Frohsinn</t>
   </si>
   <si>
     <t xml:space="preserve">Ziesarer Landstr. 3</t>
   </si>
   <si>
+    <t xml:space="preserve">FROH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gartenfreunde Brielower Aue</t>
   </si>
   <si>
     <t xml:space="preserve">Brielower Aue 47</t>
   </si>
   <si>
+    <t xml:space="preserve">BRAUE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Glück Auf</t>
   </si>
   <si>
     <t xml:space="preserve">Ziesarer Landstr. 117</t>
   </si>
   <si>
+    <t xml:space="preserve">GLAUF</t>
+  </si>
+  <si>
     <t xml:space="preserve">Glück im Winkel</t>
   </si>
   <si>
     <t xml:space="preserve">Eichhorstweg 3</t>
   </si>
   <si>
+    <t xml:space="preserve">GLWIN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Grüne Ecke</t>
   </si>
   <si>
     <t xml:space="preserve">Pfefferlander Weg 48</t>
   </si>
   <si>
+    <t xml:space="preserve">GRECK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Grüner Kranz</t>
   </si>
   <si>
     <t xml:space="preserve">GutsMuthsstr. 21a</t>
   </si>
   <si>
+    <t xml:space="preserve">GRKRZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Grünes Heim</t>
   </si>
   <si>
     <t xml:space="preserve">Ferdinand-Lassalle-Str. 12</t>
   </si>
   <si>
+    <t xml:space="preserve">GRHEI</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gut Wetter</t>
   </si>
   <si>
     <t xml:space="preserve">Fohrder Landstr. 9</t>
   </si>
   <si>
+    <t xml:space="preserve">GUTWE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Handwerker</t>
   </si>
   <si>
     <t xml:space="preserve">Planeweg 1b</t>
   </si>
   <si>
+    <t xml:space="preserve">HANDW</t>
+  </si>
+  <si>
     <t xml:space="preserve">Harmonie</t>
   </si>
   <si>
     <t xml:space="preserve">August-Bebel-Str. 19</t>
   </si>
   <si>
+    <t xml:space="preserve">HARMO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Heidekrug</t>
   </si>
   <si>
     <t xml:space="preserve">Plauer Landstr. 42</t>
   </si>
   <si>
+    <t xml:space="preserve">HEIDE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Helgoland</t>
   </si>
   <si>
     <t xml:space="preserve">Grune Aue 31</t>
   </si>
   <si>
+    <t xml:space="preserve">HELGO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hoffnung</t>
   </si>
   <si>
     <t xml:space="preserve">Baebenrothufer 7</t>
   </si>
   <si>
+    <t xml:space="preserve">HOFFN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Holland</t>
   </si>
   <si>
     <t xml:space="preserve">Klingenbergstr. 2</t>
   </si>
   <si>
+    <t xml:space="preserve">HOLL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Im Mittelbruch I</t>
   </si>
   <si>
     <t xml:space="preserve">Krakauer Str. 28</t>
   </si>
   <si>
+    <t xml:space="preserve">MBR1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Im Mittelbruch II</t>
   </si>
   <si>
     <t xml:space="preserve">Krakauer Str. 29</t>
   </si>
   <si>
+    <t xml:space="preserve">MBR2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Immergrün</t>
   </si>
   <si>
     <t xml:space="preserve">Gordenallee 169</t>
   </si>
   <si>
+    <t xml:space="preserve">IMMER</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jakobswerder</t>
   </si>
   <si>
     <t xml:space="preserve">Grune Aue 48</t>
   </si>
   <si>
+    <t xml:space="preserve">JAKWE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kammgarn</t>
   </si>
   <si>
     <t xml:space="preserve">Klingenbergstr. 2a</t>
   </si>
   <si>
+    <t xml:space="preserve">KAMM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kirchmöser-Dorf</t>
   </si>
   <si>
     <t xml:space="preserve">Bahnhofstr. 3</t>
   </si>
   <si>
+    <t xml:space="preserve">KMDOR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kirchmöser-Lehmgarten</t>
   </si>
   <si>
     <t xml:space="preserve">Uferstr. 71b</t>
   </si>
   <si>
+    <t xml:space="preserve">KMLEH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kirchmöser-Ost</t>
   </si>
   <si>
     <t xml:space="preserve">Kurze Str. 17</t>
   </si>
   <si>
+    <t xml:space="preserve">KMOST</t>
+  </si>
+  <si>
     <t xml:space="preserve">Landheim</t>
   </si>
   <si>
     <t xml:space="preserve">Wilhelmsdorfer Landstr. 65</t>
   </si>
   <si>
+    <t xml:space="preserve">LANDH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Märkische Aue</t>
   </si>
   <si>
     <t xml:space="preserve">Krakauer Str. 27</t>
   </si>
   <si>
+    <t xml:space="preserve">MAERK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mittelweg</t>
   </si>
   <si>
     <t xml:space="preserve">Buchenweg 63a</t>
   </si>
   <si>
+    <t xml:space="preserve">MITTW</t>
+  </si>
+  <si>
     <t xml:space="preserve">Morgenrot</t>
   </si>
   <si>
     <t xml:space="preserve">Ziesarer Landstr. 66</t>
   </si>
   <si>
+    <t xml:space="preserve">MORGE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Neues Leben</t>
   </si>
   <si>
     <t xml:space="preserve">Koppehlstr. 7</t>
   </si>
   <si>
+    <t xml:space="preserve">NEUL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Neu-Sanssouci</t>
   </si>
   <si>
     <t xml:space="preserve">Grune Aue 46</t>
   </si>
   <si>
+    <t xml:space="preserve">NSANS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oase</t>
   </si>
   <si>
     <t xml:space="preserve">Brahmsstr. 14b</t>
   </si>
   <si>
+    <t xml:space="preserve">OASE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pferdewiese</t>
   </si>
   <si>
     <t xml:space="preserve">Seestr. 50</t>
   </si>
   <si>
+    <t xml:space="preserve">PFERD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Plane II</t>
   </si>
   <si>
     <t xml:space="preserve">Planeweg 4&amp;</t>
   </si>
   <si>
+    <t xml:space="preserve">PLAN2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Platz der Einheit</t>
   </si>
   <si>
     <t xml:space="preserve">Platz der Einheit 19</t>
   </si>
   <si>
+    <t xml:space="preserve">PLEIN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sandfurth-Oase</t>
   </si>
   <si>
     <t xml:space="preserve">Sandfurthweg 27</t>
   </si>
   <si>
+    <t xml:space="preserve">SFOAS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sanssouci</t>
   </si>
   <si>
     <t xml:space="preserve">Wilhelmsdorfer Landstr. 55</t>
   </si>
   <si>
+    <t xml:space="preserve">SANS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sommerfreude I</t>
   </si>
   <si>
     <t xml:space="preserve">Eichhorstweg 9</t>
   </si>
   <si>
+    <t xml:space="preserve">SOMF1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sommerfreude II</t>
   </si>
   <si>
     <t xml:space="preserve">Pfefferlander Weg 9</t>
   </si>
   <si>
+    <t xml:space="preserve">SOMF2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sonnenrot</t>
   </si>
   <si>
     <t xml:space="preserve">Ziesarer Landstr. 68</t>
   </si>
   <si>
+    <t xml:space="preserve">SOROT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sonnenschein</t>
   </si>
   <si>
     <t xml:space="preserve">Mahlerstr. 22</t>
   </si>
   <si>
+    <t xml:space="preserve">SOSCH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sonnenwinkel</t>
   </si>
   <si>
     <t xml:space="preserve">Buchenweg 65a</t>
   </si>
   <si>
+    <t xml:space="preserve">SOWIN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sorgenfrei I</t>
   </si>
   <si>
     <t xml:space="preserve">Ziesarer Landstr. 76</t>
   </si>
   <si>
+    <t xml:space="preserve">SORG1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sorgenfrei II</t>
   </si>
   <si>
     <t xml:space="preserve">Buchenweg 62</t>
   </si>
   <si>
+    <t xml:space="preserve">SORG2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sportpark</t>
   </si>
   <si>
     <t xml:space="preserve">Wilhelmsdorfer Landstr. 90</t>
   </si>
   <si>
+    <t xml:space="preserve">SPORT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stiller Winkel</t>
   </si>
   <si>
     <t xml:space="preserve">Pfefferlander Weg 50</t>
   </si>
   <si>
+    <t xml:space="preserve">STILL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Traumland</t>
   </si>
   <si>
     <t xml:space="preserve">Fritze-Bollmann-Weg 82</t>
   </si>
   <si>
+    <t xml:space="preserve">TRAUM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Waldfrieden</t>
   </si>
   <si>
     <t xml:space="preserve">Weberstr. 59</t>
   </si>
   <si>
+    <t xml:space="preserve">WALDF</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weinmeisterweg</t>
   </si>
   <si>
     <t xml:space="preserve">Weinmeisterweg 10</t>
   </si>
   <si>
+    <t xml:space="preserve">WEINM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wittstocker Gäßchen</t>
   </si>
   <si>
     <t xml:space="preserve">Wittstocker Gäßchen 15</t>
   </si>
   <si>
+    <t xml:space="preserve">WITTS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zukunft</t>
   </si>
   <si>
     <t xml:space="preserve">Hagelberger Str. 3</t>
   </si>
   <si>
+    <t xml:space="preserve">ZUKUN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zum Burgweg</t>
   </si>
   <si>
     <t xml:space="preserve">Burgweg 4a</t>
   </si>
   <si>
+    <t xml:space="preserve">BURGW</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zum kühlen Grunde</t>
   </si>
   <si>
     <t xml:space="preserve">Grillendamm 8</t>
   </si>
   <si>
+    <t xml:space="preserve">KUEHL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zur Insel</t>
   </si>
   <si>
     <t xml:space="preserve">Domkietz 8a</t>
   </si>
   <si>
+    <t xml:space="preserve">INSEL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rot: Parzellenzahl in den Konzept-Tabellen 5–8 weicht vom Steckbrief ab (gerechnet wird mit dem Steckbrief, Summe 5.017 = Konzept S. 18).</t>
   </si>
   <si>
@@ -1395,7 +1668,34 @@
     <t xml:space="preserve">Prüfung</t>
   </si>
   <si>
+    <t xml:space="preserve">VLAN-Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VLAN Parzellen von</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VLAN Parzellen bis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VLAN Vorstand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VLAN Gäste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VLAN Technik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subnetz Parzelle 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prüfung VLAN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Summe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VLAN-Schema: Parzelle = 1000 + 200 × (VLAN-Block − 1) + Parzelle (letzte zwei Ziffern = Parzelle) · Vorstand 100 + Nr. · Gäste 200 + Nr. · Technik 300 + Nr. · Subnetz 10.&lt;Nr.&gt;.&lt;Parzelle&gt;.0/24 · eindeutig je Standort</t>
   </si>
   <si>
     <t xml:space="preserve">Investition – Technik in den Sparten (ohne Gateways und Standort, die stehen im Blatt „Standorte“)</t>
@@ -2227,7 +2527,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="170"/>
@@ -2302,15 +2602,15 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4"/>
+      <c r="A16" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2320,15 +2620,15 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4"/>
+      <c r="A20" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2338,15 +2638,15 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4"/>
+      <c r="A24" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="A25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2363,6 +2663,11 @@
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2392,31 +2697,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2424,7 +2729,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">COUNT(Anlagen!A5:A92)</f>
@@ -2441,7 +2746,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">Investition!P93</f>
@@ -2458,7 +2763,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">SUMPRODUCT(--(Anlagen!A5:A92&gt;0))</f>
@@ -2475,7 +2780,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>0</v>
@@ -2491,16 +2796,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">COUNTIF(Netz!P5:P92,"Fehler*")</f>
+        <f aca="false">COUNTIF(Netz!P5:P92,"Fehler*")+COUNTIF(Netz!Y5:Y92,"Fehler*")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -2508,7 +2813,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">Investition!Q93</f>
@@ -2525,7 +2830,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="11" t="n">
         <f aca="false">Investition!R93</f>
@@ -2542,7 +2847,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">B12+B13*Jahre</f>
@@ -2559,7 +2864,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2567,7 +2872,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">SUM(Anlagen!F5:F92)</f>
@@ -2576,7 +2881,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">Buchungsquote!E93</f>
@@ -2585,7 +2890,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">Buchungsquote!Q93</f>
@@ -2594,7 +2899,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" s="13" t="n">
         <f aca="false">Buchungsquote!T93</f>
@@ -2603,7 +2908,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="9" t="n">
         <f aca="false">Buchungsquote!V93</f>
@@ -2612,7 +2917,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">Ergebnis!H93</f>
@@ -2621,7 +2926,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" s="11" t="n">
         <f aca="false">Ergebnis!L93</f>
@@ -2630,7 +2935,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" s="14" t="n">
         <f aca="false">Ergebnis!M93</f>
@@ -2639,7 +2944,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" s="11" t="n">
         <f aca="false">Ergebnis!N93</f>
@@ -2648,7 +2953,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C26" s="2" t="str">
         <f aca="false">IF(Quote_Modus=2,"feste Quote "&amp;TEXT(Quote_fest,"0%"),IF(Szenario=2,"aus Alter und Leerstand, in 5 Jahren","aus Alter und Leerstand, heute"))</f>
@@ -2682,29 +2987,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -2712,40 +3017,40 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="15" t="n">
         <v>55</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" s="15" t="n">
         <v>10</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" s="17" t="n">
         <v>1.3</v>
@@ -2754,51 +3059,51 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>1000</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" s="15" t="n">
         <v>8</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>30</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>5</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2806,260 +3111,260 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" s="17" t="n">
         <v>250</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" s="17" t="n">
         <v>240</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" s="17" t="n">
         <v>20</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C20" s="17" t="n">
         <v>1500</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C21" s="17" t="n">
         <v>250</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C22" s="17" t="n">
         <v>21.9</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" s="17" t="n">
         <v>179</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" s="17" t="n">
         <v>70</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" s="17" t="n">
         <v>8.5</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" s="17" t="n">
         <v>45</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" s="17" t="n">
         <v>32.9</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" s="17" t="n">
         <v>300</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" s="17" t="n">
         <v>80</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C30" s="17" t="n">
         <v>12</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C31" s="17" t="n">
         <v>250</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32" s="17" t="n">
         <v>392</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C33" s="17" t="n">
         <v>120</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C34" s="17" t="n">
         <v>1.5</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C35" s="17" t="n">
         <v>1.2</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C36" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C37" s="17" t="n">
         <v>500</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C38" s="17" t="n">
         <v>150</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C39" s="17" t="n">
         <v>150</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -3067,18 +3372,18 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C42" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" s="19" t="n">
         <v>0.19</v>
@@ -3087,19 +3392,19 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C44" s="20" t="n">
         <f aca="false">IF(KU=1,1+USt,1)</f>
         <v>1.19</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -3107,95 +3412,95 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C47" s="17" t="n">
         <v>3.6</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C48" s="17" t="n">
         <v>2.2</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C49" s="19" t="n">
         <v>0.5</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C50" s="21" t="n">
         <v>2.806</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C51" s="17" t="n">
         <v>1.66</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C52" s="17" t="n">
         <v>1.06</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C53" s="17" t="n">
         <v>0.42</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C54" s="15" t="n">
         <v>8</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -3203,84 +3508,84 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C57" s="17" t="n">
         <v>75</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C58" s="17" t="n">
         <v>80</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" s="17" t="n">
         <v>25</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C60" s="17" t="n">
         <v>50</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C61" s="19" t="n">
         <v>0.03</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C62" s="19" t="n">
         <v>0.03</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C63" s="17" t="n">
         <v>120</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -3288,29 +3593,29 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C66" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C67" s="19" t="n">
         <v>0.6</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C68" s="15" t="n">
         <v>1</v>
@@ -3319,106 +3624,106 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C69" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C70" s="19" t="n">
         <v>0.75</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C71" s="19" t="n">
         <v>0.6</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C72" s="19" t="n">
         <v>0.35</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C73" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C74" s="19" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C75" s="19" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C76" s="19" t="n">
         <v>0.9</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C77" s="19" t="n">
         <v>0.75</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -3426,91 +3731,91 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C80" s="19" t="n">
         <v>0.05</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C81" s="19" t="n">
         <v>0.05</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C82" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C83" s="19" t="n">
         <v>0.3</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C84" s="19" t="n">
         <v>0.6</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C85" s="19" t="n">
         <v>0.7</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C86" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C87" s="22" t="n">
         <f aca="false">Neig_2</f>
         <v>0.75</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3529,7 +3834,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z95"/>
+  <dimension ref="A1:AB95"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -3549,96 +3854,104 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="24" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y4" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3646,16 +3959,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>30</v>
@@ -3704,22 +4017,26 @@
       <c r="X5" s="27"/>
       <c r="Y5" s="27"/>
       <c r="Z5" s="27"/>
+      <c r="AA5" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB5" s="27"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>75</v>
@@ -3768,22 +4085,26 @@
       <c r="X6" s="27"/>
       <c r="Y6" s="27"/>
       <c r="Z6" s="27"/>
+      <c r="AA6" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB6" s="27"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F7" s="24" t="n">
         <v>137</v>
@@ -3832,22 +4153,26 @@
       <c r="X7" s="27"/>
       <c r="Y7" s="27"/>
       <c r="Z7" s="27"/>
+      <c r="AA7" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB7" s="27"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>142</v>
@@ -3896,22 +4221,26 @@
       <c r="X8" s="27"/>
       <c r="Y8" s="27"/>
       <c r="Z8" s="27"/>
+      <c r="AA8" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB8" s="27"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C9" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>209</v>
-      </c>
       <c r="E9" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F9" s="24" t="n">
         <v>67</v>
@@ -3960,22 +4289,26 @@
       <c r="X9" s="27"/>
       <c r="Y9" s="27"/>
       <c r="Z9" s="27"/>
+      <c r="AA9" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB9" s="27"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>88</v>
@@ -4024,22 +4357,26 @@
       <c r="X10" s="27"/>
       <c r="Y10" s="27"/>
       <c r="Z10" s="27"/>
+      <c r="AA10" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="AB10" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F11" s="24" t="n">
         <v>77</v>
@@ -4088,22 +4425,26 @@
       <c r="X11" s="27"/>
       <c r="Y11" s="27"/>
       <c r="Z11" s="27"/>
+      <c r="AA11" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB11" s="27"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>5</v>
@@ -4152,22 +4493,26 @@
       <c r="X12" s="27"/>
       <c r="Y12" s="27"/>
       <c r="Z12" s="27"/>
+      <c r="AA12" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F13" s="24" t="n">
         <v>54</v>
@@ -4216,22 +4561,26 @@
       <c r="X13" s="27"/>
       <c r="Y13" s="27"/>
       <c r="Z13" s="27"/>
+      <c r="AA13" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB13" s="27"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>41</v>
@@ -4280,22 +4629,26 @@
       <c r="X14" s="27"/>
       <c r="Y14" s="27"/>
       <c r="Z14" s="27"/>
+      <c r="AA14" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="AB14" s="27"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F15" s="24" t="n">
         <v>10</v>
@@ -4344,22 +4697,26 @@
       <c r="X15" s="27"/>
       <c r="Y15" s="27"/>
       <c r="Z15" s="27"/>
+      <c r="AA15" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB15" s="27"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D16" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>202</v>
       </c>
       <c r="F16" s="24" t="n">
         <v>19</v>
@@ -4408,22 +4765,26 @@
       <c r="X16" s="27"/>
       <c r="Y16" s="27"/>
       <c r="Z16" s="27"/>
+      <c r="AA16" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB16" s="27"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F17" s="24" t="n">
         <v>96</v>
@@ -4472,22 +4833,26 @@
       <c r="X17" s="27"/>
       <c r="Y17" s="27"/>
       <c r="Z17" s="27"/>
+      <c r="AA17" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB17" s="27"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="F18" s="24" t="n">
         <v>16</v>
@@ -4536,22 +4901,26 @@
       <c r="X18" s="27"/>
       <c r="Y18" s="27"/>
       <c r="Z18" s="27"/>
+      <c r="AA18" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB18" s="27"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F19" s="24" t="n">
         <v>14</v>
@@ -4600,22 +4969,26 @@
       <c r="X19" s="27"/>
       <c r="Y19" s="27"/>
       <c r="Z19" s="27"/>
+      <c r="AA19" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB19" s="27"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="D20" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E20" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>202</v>
       </c>
       <c r="F20" s="24" t="n">
         <v>130</v>
@@ -4662,22 +5035,26 @@
       <c r="X20" s="27"/>
       <c r="Y20" s="27"/>
       <c r="Z20" s="27"/>
+      <c r="AA20" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="AB20" s="27"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F21" s="24" t="n">
         <v>56</v>
@@ -4724,22 +5101,26 @@
       <c r="X21" s="27"/>
       <c r="Y21" s="27"/>
       <c r="Z21" s="27"/>
+      <c r="AA21" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="AB21" s="27"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F22" s="24" t="n">
         <v>64</v>
@@ -4788,22 +5169,26 @@
       <c r="X22" s="27"/>
       <c r="Y22" s="27"/>
       <c r="Z22" s="27"/>
+      <c r="AA22" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB22" s="27"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F23" s="24" t="n">
         <v>35</v>
@@ -4852,22 +5237,26 @@
       <c r="X23" s="27"/>
       <c r="Y23" s="27"/>
       <c r="Z23" s="27"/>
+      <c r="AA23" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="AB23" s="27"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F24" s="24" t="n">
         <v>86</v>
@@ -4916,22 +5305,26 @@
       <c r="X24" s="27"/>
       <c r="Y24" s="27"/>
       <c r="Z24" s="27"/>
+      <c r="AA24" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="AB24" s="27"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F25" s="24" t="n">
         <v>75</v>
@@ -4980,22 +5373,26 @@
       <c r="X25" s="27"/>
       <c r="Y25" s="27"/>
       <c r="Z25" s="27"/>
+      <c r="AA25" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="AB25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F26" s="24" t="n">
         <v>38</v>
@@ -5042,22 +5439,26 @@
       <c r="X26" s="27"/>
       <c r="Y26" s="27"/>
       <c r="Z26" s="27"/>
+      <c r="AA26" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB26" s="27"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F27" s="24" t="n">
         <v>123</v>
@@ -5104,22 +5505,26 @@
       <c r="X27" s="27"/>
       <c r="Y27" s="27"/>
       <c r="Z27" s="27"/>
+      <c r="AA27" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB27" s="27"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F28" s="24" t="n">
         <v>99</v>
@@ -5168,22 +5573,26 @@
       <c r="X28" s="27"/>
       <c r="Y28" s="27"/>
       <c r="Z28" s="27"/>
+      <c r="AA28" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB28" s="27"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F29" s="24" t="n">
         <v>14</v>
@@ -5232,22 +5641,26 @@
       <c r="X29" s="27"/>
       <c r="Y29" s="27"/>
       <c r="Z29" s="27"/>
+      <c r="AA29" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB29" s="27"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F30" s="24" t="n">
         <v>32</v>
@@ -5296,22 +5709,26 @@
       <c r="X30" s="27"/>
       <c r="Y30" s="27"/>
       <c r="Z30" s="27"/>
+      <c r="AA30" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB30" s="27"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="n">
         <v>27</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="F31" s="24" t="n">
         <v>42</v>
@@ -5360,22 +5777,26 @@
       <c r="X31" s="27"/>
       <c r="Y31" s="27"/>
       <c r="Z31" s="27"/>
+      <c r="AA31" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB31" s="27"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="n">
         <v>28</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F32" s="24" t="n">
         <v>99</v>
@@ -5422,22 +5843,26 @@
       <c r="X32" s="27"/>
       <c r="Y32" s="27"/>
       <c r="Z32" s="27"/>
+      <c r="AA32" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="AB32" s="27"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="n">
         <v>29</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F33" s="24" t="n">
         <v>92</v>
@@ -5486,22 +5911,26 @@
       <c r="X33" s="27"/>
       <c r="Y33" s="27"/>
       <c r="Z33" s="27"/>
+      <c r="AA33" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="AB33" s="27"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="n">
         <v>30</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F34" s="24" t="n">
         <v>190</v>
@@ -5548,22 +5977,26 @@
       <c r="X34" s="27"/>
       <c r="Y34" s="27"/>
       <c r="Z34" s="27"/>
+      <c r="AA34" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="AB34" s="27"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="n">
         <v>31</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="D35" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E35" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>202</v>
       </c>
       <c r="F35" s="24" t="n">
         <v>68</v>
@@ -5612,22 +6045,26 @@
       <c r="X35" s="27"/>
       <c r="Y35" s="27"/>
       <c r="Z35" s="27"/>
+      <c r="AA35" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB35" s="27"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="n">
         <v>32</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="D36" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E36" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>202</v>
       </c>
       <c r="F36" s="24" t="n">
         <v>8</v>
@@ -5676,22 +6113,26 @@
       <c r="X36" s="27"/>
       <c r="Y36" s="27"/>
       <c r="Z36" s="27"/>
+      <c r="AA36" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="AB36" s="27"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="n">
         <v>33</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F37" s="24" t="n">
         <v>127</v>
@@ -5738,22 +6179,26 @@
       <c r="X37" s="27"/>
       <c r="Y37" s="27"/>
       <c r="Z37" s="27"/>
+      <c r="AA37" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB37" s="27"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="n">
         <v>34</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="D38" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E38" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>202</v>
       </c>
       <c r="F38" s="24" t="n">
         <v>55</v>
@@ -5802,22 +6247,26 @@
       <c r="X38" s="27"/>
       <c r="Y38" s="27"/>
       <c r="Z38" s="27"/>
+      <c r="AA38" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="AB38" s="27"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="n">
         <v>35</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F39" s="24" t="n">
         <v>63</v>
@@ -5866,22 +6315,26 @@
       <c r="X39" s="27"/>
       <c r="Y39" s="27"/>
       <c r="Z39" s="27"/>
+      <c r="AA39" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="AB39" s="27"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="n">
         <v>36</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="F40" s="24" t="n">
         <v>64</v>
@@ -5930,22 +6383,26 @@
       <c r="X40" s="27"/>
       <c r="Y40" s="27"/>
       <c r="Z40" s="27"/>
+      <c r="AA40" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="AB40" s="27"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="n">
         <v>37</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>281</v>
+        <v>320</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F41" s="24" t="n">
         <v>19</v>
@@ -5994,22 +6451,26 @@
       <c r="X41" s="27"/>
       <c r="Y41" s="27"/>
       <c r="Z41" s="27"/>
+      <c r="AA41" s="27" t="s">
+        <v>322</v>
+      </c>
+      <c r="AB41" s="27"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="23" t="n">
         <v>38</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>283</v>
+        <v>323</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>284</v>
+        <v>324</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F42" s="24" t="n">
         <v>54</v>
@@ -6058,22 +6519,26 @@
       <c r="X42" s="27"/>
       <c r="Y42" s="27"/>
       <c r="Z42" s="27"/>
+      <c r="AA42" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="AB42" s="27"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="n">
         <v>39</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>285</v>
+        <v>326</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F43" s="24" t="n">
         <v>69</v>
@@ -6122,22 +6587,26 @@
       <c r="X43" s="27"/>
       <c r="Y43" s="27"/>
       <c r="Z43" s="27"/>
+      <c r="AA43" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="AB43" s="27"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="n">
         <v>40</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>287</v>
+        <v>329</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>288</v>
+        <v>330</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F44" s="24" t="n">
         <v>34</v>
@@ -6186,22 +6655,26 @@
       <c r="X44" s="27"/>
       <c r="Y44" s="27"/>
       <c r="Z44" s="27"/>
+      <c r="AA44" s="27" t="s">
+        <v>331</v>
+      </c>
+      <c r="AB44" s="27"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="n">
         <v>41</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>290</v>
+        <v>333</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F45" s="24" t="n">
         <v>139</v>
@@ -6248,22 +6721,26 @@
       <c r="X45" s="27"/>
       <c r="Y45" s="27"/>
       <c r="Z45" s="27"/>
+      <c r="AA45" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="AB45" s="27"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="n">
         <v>42</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>291</v>
+        <v>335</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F46" s="24" t="n">
         <v>50</v>
@@ -6312,22 +6789,26 @@
       <c r="X46" s="27"/>
       <c r="Y46" s="27"/>
       <c r="Z46" s="27"/>
+      <c r="AA46" s="27" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB46" s="27"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="23" t="n">
         <v>43</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F47" s="24" t="n">
         <v>70</v>
@@ -6376,22 +6857,26 @@
       <c r="X47" s="27"/>
       <c r="Y47" s="27"/>
       <c r="Z47" s="27"/>
+      <c r="AA47" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="AB47" s="27"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="23" t="n">
         <v>44</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>295</v>
+        <v>341</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="F48" s="24" t="n">
         <v>23</v>
@@ -6440,22 +6925,26 @@
       <c r="X48" s="27"/>
       <c r="Y48" s="27"/>
       <c r="Z48" s="27"/>
+      <c r="AA48" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="AB48" s="27"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="n">
         <v>45</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F49" s="24" t="n">
         <v>17</v>
@@ -6504,22 +6993,26 @@
       <c r="X49" s="27"/>
       <c r="Y49" s="27"/>
       <c r="Z49" s="27"/>
+      <c r="AA49" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="AB49" s="27"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="23" t="n">
         <v>46</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>299</v>
+        <v>347</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>300</v>
+        <v>348</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="F50" s="24" t="n">
         <v>36</v>
@@ -6568,22 +7061,26 @@
       <c r="X50" s="27"/>
       <c r="Y50" s="27"/>
       <c r="Z50" s="27"/>
+      <c r="AA50" s="27" t="s">
+        <v>349</v>
+      </c>
+      <c r="AB50" s="27"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="n">
         <v>47</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>301</v>
+        <v>350</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>302</v>
+        <v>351</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F51" s="24" t="n">
         <v>60</v>
@@ -6632,22 +7129,26 @@
       <c r="X51" s="27"/>
       <c r="Y51" s="27"/>
       <c r="Z51" s="27"/>
+      <c r="AA51" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="AB51" s="27"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="23" t="n">
         <v>48</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F52" s="24" t="n">
         <v>34</v>
@@ -6694,22 +7195,26 @@
       <c r="X52" s="27"/>
       <c r="Y52" s="27"/>
       <c r="Z52" s="27"/>
+      <c r="AA52" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="AB52" s="27"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="23" t="n">
         <v>49</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>305</v>
+        <v>356</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>306</v>
+        <v>357</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F53" s="24" t="n">
         <v>110</v>
@@ -6756,22 +7261,26 @@
       <c r="X53" s="27"/>
       <c r="Y53" s="27"/>
       <c r="Z53" s="27"/>
+      <c r="AA53" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="AB53" s="27"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="n">
         <v>50</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>307</v>
+        <v>359</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F54" s="24" t="n">
         <v>7</v>
@@ -6820,22 +7329,26 @@
       <c r="X54" s="27"/>
       <c r="Y54" s="27"/>
       <c r="Z54" s="27"/>
+      <c r="AA54" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="AB54" s="27"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="23" t="n">
         <v>51</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>309</v>
+        <v>362</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>310</v>
+        <v>363</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F55" s="24" t="n">
         <v>9</v>
@@ -6884,22 +7397,26 @@
       <c r="X55" s="27"/>
       <c r="Y55" s="27"/>
       <c r="Z55" s="27"/>
+      <c r="AA55" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB55" s="27"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="23" t="n">
         <v>52</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>312</v>
+        <v>366</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F56" s="24" t="n">
         <v>33</v>
@@ -6948,22 +7465,26 @@
       <c r="X56" s="27"/>
       <c r="Y56" s="27"/>
       <c r="Z56" s="27"/>
+      <c r="AA56" s="27" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB56" s="27"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="23" t="n">
         <v>53</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>313</v>
+        <v>368</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F57" s="24" t="n">
         <v>47</v>
@@ -7012,22 +7533,26 @@
       <c r="X57" s="27"/>
       <c r="Y57" s="27"/>
       <c r="Z57" s="27"/>
+      <c r="AA57" s="27" t="s">
+        <v>370</v>
+      </c>
+      <c r="AB57" s="27"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="23" t="n">
         <v>54</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>315</v>
+        <v>371</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>316</v>
+        <v>372</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F58" s="24" t="n">
         <v>57</v>
@@ -7076,22 +7601,26 @@
       <c r="X58" s="27"/>
       <c r="Y58" s="27"/>
       <c r="Z58" s="27"/>
+      <c r="AA58" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB58" s="27"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="23" t="n">
         <v>55</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>317</v>
+        <v>374</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F59" s="24" t="n">
         <v>49</v>
@@ -7140,22 +7669,26 @@
       <c r="X59" s="27"/>
       <c r="Y59" s="27"/>
       <c r="Z59" s="27"/>
+      <c r="AA59" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="AB59" s="27"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="23" t="n">
         <v>56</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>319</v>
+        <v>377</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>320</v>
+        <v>378</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F60" s="24" t="n">
         <v>28</v>
@@ -7202,22 +7735,26 @@
       <c r="X60" s="27"/>
       <c r="Y60" s="27"/>
       <c r="Z60" s="27"/>
+      <c r="AA60" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="AB60" s="27"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="23" t="n">
         <v>57</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>321</v>
+        <v>380</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F61" s="24" t="n">
         <v>48</v>
@@ -7264,22 +7801,26 @@
       <c r="X61" s="27"/>
       <c r="Y61" s="27"/>
       <c r="Z61" s="27"/>
+      <c r="AA61" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="AB61" s="27"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="23" t="n">
         <v>58</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>323</v>
+        <v>383</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>324</v>
+        <v>384</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F62" s="24" t="n">
         <v>38</v>
@@ -7328,22 +7869,26 @@
       <c r="X62" s="27"/>
       <c r="Y62" s="27"/>
       <c r="Z62" s="27"/>
+      <c r="AA62" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="AB62" s="27"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="23" t="n">
         <v>59</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>325</v>
+        <v>386</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>326</v>
+        <v>387</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F63" s="24" t="n">
         <v>66</v>
@@ -7390,22 +7935,26 @@
       <c r="X63" s="27"/>
       <c r="Y63" s="27"/>
       <c r="Z63" s="27"/>
+      <c r="AA63" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="AB63" s="27"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="23" t="n">
         <v>60</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F64" s="24" t="n">
         <v>109</v>
@@ -7454,22 +8003,26 @@
       <c r="X64" s="27"/>
       <c r="Y64" s="27"/>
       <c r="Z64" s="27"/>
+      <c r="AA64" s="27" t="s">
+        <v>391</v>
+      </c>
+      <c r="AB64" s="27"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="23" t="n">
         <v>61</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>329</v>
+        <v>392</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F65" s="24" t="n">
         <v>73</v>
@@ -7518,22 +8071,26 @@
       <c r="X65" s="27"/>
       <c r="Y65" s="27"/>
       <c r="Z65" s="27"/>
+      <c r="AA65" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="AB65" s="27"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="23" t="n">
         <v>62</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>331</v>
+        <v>395</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>332</v>
+        <v>396</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F66" s="24" t="n">
         <v>36</v>
@@ -7582,22 +8139,26 @@
       <c r="X66" s="27"/>
       <c r="Y66" s="27"/>
       <c r="Z66" s="27"/>
+      <c r="AA66" s="27" t="s">
+        <v>397</v>
+      </c>
+      <c r="AB66" s="27"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="23" t="n">
         <v>63</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>334</v>
+        <v>399</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F67" s="24" t="n">
         <v>25</v>
@@ -7646,22 +8207,26 @@
       <c r="X67" s="27"/>
       <c r="Y67" s="27"/>
       <c r="Z67" s="27"/>
+      <c r="AA67" s="27" t="s">
+        <v>400</v>
+      </c>
+      <c r="AB67" s="27"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="23" t="n">
         <v>64</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>335</v>
+        <v>401</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>336</v>
+        <v>402</v>
       </c>
       <c r="D68" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E68" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="E68" s="23" t="s">
-        <v>202</v>
       </c>
       <c r="F68" s="24" t="n">
         <v>62</v>
@@ -7710,22 +8275,26 @@
       <c r="X68" s="27"/>
       <c r="Y68" s="27"/>
       <c r="Z68" s="27"/>
+      <c r="AA68" s="27" t="s">
+        <v>403</v>
+      </c>
+      <c r="AB68" s="27"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="23" t="n">
         <v>65</v>
       </c>
       <c r="B69" s="23" t="s">
-        <v>337</v>
+        <v>404</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>338</v>
+        <v>405</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F69" s="24" t="n">
         <v>77</v>
@@ -7774,22 +8343,26 @@
       <c r="X69" s="27"/>
       <c r="Y69" s="27"/>
       <c r="Z69" s="27"/>
+      <c r="AA69" s="27" t="s">
+        <v>406</v>
+      </c>
+      <c r="AB69" s="27"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="23" t="n">
         <v>66</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>339</v>
+        <v>407</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F70" s="24" t="n">
         <v>47</v>
@@ -7838,22 +8411,26 @@
       <c r="X70" s="27"/>
       <c r="Y70" s="27"/>
       <c r="Z70" s="27"/>
+      <c r="AA70" s="27" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB70" s="27"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="23" t="n">
         <v>67</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>341</v>
+        <v>410</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>342</v>
+        <v>411</v>
       </c>
       <c r="D71" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E71" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="E71" s="23" t="s">
-        <v>202</v>
       </c>
       <c r="F71" s="24" t="n">
         <v>55</v>
@@ -7902,22 +8479,26 @@
       <c r="X71" s="27"/>
       <c r="Y71" s="27"/>
       <c r="Z71" s="27"/>
+      <c r="AA71" s="27" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB71" s="27"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="23" t="n">
         <v>68</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>343</v>
+        <v>413</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>344</v>
+        <v>414</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F72" s="24" t="n">
         <v>28</v>
@@ -7966,22 +8547,26 @@
       <c r="X72" s="27"/>
       <c r="Y72" s="27"/>
       <c r="Z72" s="27"/>
+      <c r="AA72" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="AB72" s="27"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="23" t="n">
         <v>69</v>
       </c>
       <c r="B73" s="23" t="s">
-        <v>345</v>
+        <v>416</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>346</v>
+        <v>417</v>
       </c>
       <c r="D73" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E73" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="E73" s="23" t="s">
-        <v>202</v>
       </c>
       <c r="F73" s="24" t="n">
         <v>48</v>
@@ -8030,22 +8615,26 @@
       <c r="X73" s="27"/>
       <c r="Y73" s="27"/>
       <c r="Z73" s="27"/>
+      <c r="AA73" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="AB73" s="27"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="23" t="n">
         <v>70</v>
       </c>
       <c r="B74" s="23" t="s">
-        <v>347</v>
+        <v>419</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>348</v>
+        <v>420</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E74" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F74" s="24" t="n">
         <v>15</v>
@@ -8094,22 +8683,26 @@
       <c r="X74" s="27"/>
       <c r="Y74" s="27"/>
       <c r="Z74" s="27"/>
+      <c r="AA74" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="AB74" s="27"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="23" t="n">
         <v>71</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>349</v>
+        <v>422</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>350</v>
+        <v>423</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F75" s="24" t="n">
         <v>39</v>
@@ -8158,22 +8751,26 @@
       <c r="X75" s="27"/>
       <c r="Y75" s="27"/>
       <c r="Z75" s="27"/>
+      <c r="AA75" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="AB75" s="27"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="23" t="n">
         <v>72</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>351</v>
+        <v>425</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>352</v>
+        <v>426</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F76" s="24" t="n">
         <v>49</v>
@@ -8222,22 +8819,26 @@
       <c r="X76" s="27"/>
       <c r="Y76" s="27"/>
       <c r="Z76" s="27"/>
+      <c r="AA76" s="27" t="s">
+        <v>427</v>
+      </c>
+      <c r="AB76" s="27"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="23" t="n">
         <v>73</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>353</v>
+        <v>428</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>354</v>
+        <v>429</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F77" s="24" t="n">
         <v>130</v>
@@ -8284,22 +8885,26 @@
       <c r="X77" s="27"/>
       <c r="Y77" s="27"/>
       <c r="Z77" s="27"/>
+      <c r="AA77" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="AB77" s="27"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="23" t="n">
         <v>74</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F78" s="24" t="n">
         <v>28</v>
@@ -8348,22 +8953,26 @@
       <c r="X78" s="27"/>
       <c r="Y78" s="27"/>
       <c r="Z78" s="27"/>
+      <c r="AA78" s="27" t="s">
+        <v>433</v>
+      </c>
+      <c r="AB78" s="27"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="23" t="n">
         <v>75</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>357</v>
+        <v>434</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>358</v>
+        <v>435</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F79" s="24" t="n">
         <v>40</v>
@@ -8412,22 +9021,26 @@
       <c r="X79" s="27"/>
       <c r="Y79" s="27"/>
       <c r="Z79" s="27"/>
+      <c r="AA79" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="AB79" s="27"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="23" t="n">
         <v>76</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>359</v>
+        <v>437</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>360</v>
+        <v>438</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F80" s="24" t="n">
         <v>48</v>
@@ -8476,22 +9089,26 @@
       <c r="X80" s="27"/>
       <c r="Y80" s="27"/>
       <c r="Z80" s="27"/>
+      <c r="AA80" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="AB80" s="27"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="23" t="n">
         <v>77</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>361</v>
+        <v>440</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>362</v>
+        <v>441</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F81" s="24" t="n">
         <v>45</v>
@@ -8540,22 +9157,26 @@
       <c r="X81" s="27"/>
       <c r="Y81" s="27"/>
       <c r="Z81" s="27"/>
+      <c r="AA81" s="27" t="s">
+        <v>442</v>
+      </c>
+      <c r="AB81" s="27"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="23" t="n">
         <v>78</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>363</v>
+        <v>443</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>364</v>
+        <v>444</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F82" s="24" t="n">
         <v>23</v>
@@ -8604,22 +9225,26 @@
       <c r="X82" s="27"/>
       <c r="Y82" s="27"/>
       <c r="Z82" s="27"/>
+      <c r="AA82" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="AB82" s="27"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="23" t="n">
         <v>79</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>365</v>
+        <v>446</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>366</v>
+        <v>447</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F83" s="24" t="n">
         <v>37</v>
@@ -8668,22 +9293,26 @@
       <c r="X83" s="27"/>
       <c r="Y83" s="27"/>
       <c r="Z83" s="27"/>
+      <c r="AA83" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="AB83" s="27"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="23" t="n">
         <v>80</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>367</v>
+        <v>449</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>368</v>
+        <v>450</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F84" s="24" t="n">
         <v>50</v>
@@ -8732,22 +9361,26 @@
       <c r="X84" s="27"/>
       <c r="Y84" s="27"/>
       <c r="Z84" s="27"/>
+      <c r="AA84" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="AB84" s="27"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="23" t="n">
         <v>81</v>
       </c>
       <c r="B85" s="23" t="s">
-        <v>369</v>
+        <v>452</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>370</v>
+        <v>453</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E85" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F85" s="24" t="n">
         <v>49</v>
@@ -8794,22 +9427,26 @@
       <c r="X85" s="27"/>
       <c r="Y85" s="27"/>
       <c r="Z85" s="27"/>
+      <c r="AA85" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="AB85" s="27"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="23" t="n">
         <v>82</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>371</v>
+        <v>455</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>372</v>
+        <v>456</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E86" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F86" s="24" t="n">
         <v>90</v>
@@ -8858,22 +9495,26 @@
       <c r="X86" s="27"/>
       <c r="Y86" s="27"/>
       <c r="Z86" s="27"/>
+      <c r="AA86" s="27" t="s">
+        <v>457</v>
+      </c>
+      <c r="AB86" s="27"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="23" t="n">
         <v>83</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>373</v>
+        <v>458</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>374</v>
+        <v>459</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F87" s="24" t="n">
         <v>26</v>
@@ -8922,22 +9563,26 @@
       <c r="X87" s="27"/>
       <c r="Y87" s="27"/>
       <c r="Z87" s="27"/>
+      <c r="AA87" s="27" t="s">
+        <v>460</v>
+      </c>
+      <c r="AB87" s="27"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="23" t="n">
         <v>84</v>
       </c>
       <c r="B88" s="23" t="s">
-        <v>375</v>
+        <v>461</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>376</v>
+        <v>462</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E88" s="23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F88" s="24" t="n">
         <v>54</v>
@@ -8986,22 +9631,26 @@
       <c r="X88" s="27"/>
       <c r="Y88" s="27"/>
       <c r="Z88" s="27"/>
+      <c r="AA88" s="27" t="s">
+        <v>463</v>
+      </c>
+      <c r="AB88" s="27"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="23" t="n">
         <v>85</v>
       </c>
       <c r="B89" s="23" t="s">
-        <v>377</v>
+        <v>464</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>378</v>
+        <v>465</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F89" s="24" t="n">
         <v>85</v>
@@ -9048,22 +9697,26 @@
       <c r="X89" s="27"/>
       <c r="Y89" s="27"/>
       <c r="Z89" s="27"/>
+      <c r="AA89" s="27" t="s">
+        <v>466</v>
+      </c>
+      <c r="AB89" s="27"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="23" t="n">
         <v>86</v>
       </c>
       <c r="B90" s="23" t="s">
-        <v>379</v>
+        <v>467</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>380</v>
+        <v>468</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E90" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F90" s="24" t="n">
         <v>9</v>
@@ -9112,22 +9765,26 @@
       <c r="X90" s="27"/>
       <c r="Y90" s="27"/>
       <c r="Z90" s="27"/>
+      <c r="AA90" s="27" t="s">
+        <v>469</v>
+      </c>
+      <c r="AB90" s="27"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="23" t="n">
         <v>87</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>381</v>
+        <v>470</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>382</v>
+        <v>471</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E91" s="23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F91" s="24" t="n">
         <v>26</v>
@@ -9176,22 +9833,26 @@
       <c r="X91" s="27"/>
       <c r="Y91" s="27"/>
       <c r="Z91" s="27"/>
+      <c r="AA91" s="27" t="s">
+        <v>472</v>
+      </c>
+      <c r="AB91" s="27"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="23" t="n">
         <v>88</v>
       </c>
       <c r="B92" s="23" t="s">
-        <v>383</v>
+        <v>473</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>384</v>
+        <v>474</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E92" s="23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F92" s="24" t="n">
         <v>86</v>
@@ -9240,20 +9901,24 @@
       <c r="X92" s="27"/>
       <c r="Y92" s="27"/>
       <c r="Z92" s="27"/>
+      <c r="AA92" s="27" t="s">
+        <v>475</v>
+      </c>
+      <c r="AB92" s="27"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>385</v>
+        <v>476</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>386</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Z92"/>
-  <dataValidations count="3">
+  <autoFilter ref="A4:AB92"/>
+  <dataValidations count="4">
     <dataValidation allowBlank="true" error="Nr. einer Anlage 1–88" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="S5:T92" type="whole">
       <formula1>1</formula1>
       <formula2>88</formula2>
@@ -9261,6 +9926,10 @@
     <dataValidation allowBlank="true" error="Reihenfolge 1, 2, 3 …" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="U5:U92" type="whole">
       <formula1>1</formula1>
       <formula2>999</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="VLAN-Block 1–15" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AB5:AB92" type="whole">
+      <formula1>1</formula1>
+      <formula2>15</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Quote 0 % bis 100 %" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="W5:W92" type="decimal">
       <formula1>0</formula1>
@@ -9303,80 +9972,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>388</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>389</v>
+        <v>480</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>390</v>
+        <v>481</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>391</v>
+        <v>482</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>392</v>
+        <v>483</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>393</v>
+        <v>484</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>394</v>
+        <v>485</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>395</v>
+        <v>486</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>396</v>
+        <v>487</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>397</v>
+        <v>488</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>398</v>
+        <v>489</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>399</v>
+        <v>490</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>400</v>
+        <v>491</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>401</v>
+        <v>492</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>402</v>
+        <v>493</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17301,7 +17970,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="32" t="s">
-        <v>403</v>
+        <v>494</v>
       </c>
       <c r="C93" s="33" t="n">
         <f aca="false">SUM(C5:C92)</f>
@@ -17361,7 +18030,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:Y95"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -17377,66 +18046,98 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="21" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>404</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>405</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>406</v>
+        <v>497</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>407</v>
+        <v>498</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>408</v>
+        <v>499</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>409</v>
+        <v>500</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>410</v>
+        <v>501</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>411</v>
+        <v>502</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>412</v>
+        <v>503</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>413</v>
+        <v>504</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>414</v>
+        <v>505</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>415</v>
+        <v>506</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>416</v>
+        <v>507</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>417</v>
+        <v>508</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>418</v>
+        <v>509</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17504,6 +18205,42 @@
         <f aca="false">IF(ISNA(MATCH(C5,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C5=A5,"OK",IF(INDEX($C$5:$C$92,MATCH(C5,Anlagen!$A$5:$A$92,0))&lt;&gt;C5,"Fehler: Standort hängt selbst an anderem Standort",IF(D5=A5,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D5,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D5,Anlagen!$A$5:$A$92,0))&lt;&gt;C5,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q5" s="23" t="str">
+        <f aca="false">Anlagen!AA5</f>
+        <v>MAERZ</v>
+      </c>
+      <c r="R5" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB5&lt;&gt;"",Anlagen!AB5,COUNTIFS($C$5:$C$92,C5,$J$5:$J$92,"&lt;"&amp;J5)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S5" s="23" t="n">
+        <f aca="false">1000+200*(R5-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T5" s="23" t="n">
+        <f aca="false">1000+200*(R5-1)+Anlagen!F5</f>
+        <v>1230</v>
+      </c>
+      <c r="U5" s="23" t="n">
+        <f aca="false">100+A5</f>
+        <v>101</v>
+      </c>
+      <c r="V5" s="23" t="n">
+        <f aca="false">200+A5</f>
+        <v>201</v>
+      </c>
+      <c r="W5" s="23" t="n">
+        <f aca="false">300+A5</f>
+        <v>301</v>
+      </c>
+      <c r="X5" s="23" t="str">
+        <f aca="false">"10."&amp;A5&amp;".1.0/24"</f>
+        <v>10.1.1.0/24</v>
+      </c>
+      <c r="Y5" s="23" t="str">
+        <f aca="false">IF(R5&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C5,$R$5:$R$92,R5)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q5)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F5&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="n">
@@ -17570,6 +18307,42 @@
         <f aca="false">IF(ISNA(MATCH(C6,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C6=A6,"OK",IF(INDEX($C$5:$C$92,MATCH(C6,Anlagen!$A$5:$A$92,0))&lt;&gt;C6,"Fehler: Standort hängt selbst an anderem Standort",IF(D6=A6,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D6,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D6,Anlagen!$A$5:$A$92,0))&lt;&gt;C6,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q6" s="23" t="str">
+        <f aca="false">Anlagen!AA6</f>
+        <v>ABFRI</v>
+      </c>
+      <c r="R6" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB6&lt;&gt;"",Anlagen!AB6,COUNTIFS($C$5:$C$92,C6,$J$5:$J$92,"&lt;"&amp;J6)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S6" s="23" t="n">
+        <f aca="false">1000+200*(R6-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T6" s="23" t="n">
+        <f aca="false">1000+200*(R6-1)+Anlagen!F6</f>
+        <v>1275</v>
+      </c>
+      <c r="U6" s="23" t="n">
+        <f aca="false">100+A6</f>
+        <v>102</v>
+      </c>
+      <c r="V6" s="23" t="n">
+        <f aca="false">200+A6</f>
+        <v>202</v>
+      </c>
+      <c r="W6" s="23" t="n">
+        <f aca="false">300+A6</f>
+        <v>302</v>
+      </c>
+      <c r="X6" s="23" t="str">
+        <f aca="false">"10."&amp;A6&amp;".1.0/24"</f>
+        <v>10.2.1.0/24</v>
+      </c>
+      <c r="Y6" s="23" t="str">
+        <f aca="false">IF(R6&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C6,$R$5:$R$92,R6)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q6)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F6&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="n">
@@ -17636,6 +18409,42 @@
         <f aca="false">IF(ISNA(MATCH(C7,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C7=A7,"OK",IF(INDEX($C$5:$C$92,MATCH(C7,Anlagen!$A$5:$A$92,0))&lt;&gt;C7,"Fehler: Standort hängt selbst an anderem Standort",IF(D7=A7,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D7,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D7,Anlagen!$A$5:$A$92,0))&lt;&gt;C7,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q7" s="23" t="str">
+        <f aca="false">Anlagen!AA7</f>
+        <v>ABROT</v>
+      </c>
+      <c r="R7" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB7&lt;&gt;"",Anlagen!AB7,COUNTIFS($C$5:$C$92,C7,$J$5:$J$92,"&lt;"&amp;J7)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S7" s="23" t="n">
+        <f aca="false">1000+200*(R7-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T7" s="23" t="n">
+        <f aca="false">1000+200*(R7-1)+Anlagen!F7</f>
+        <v>1337</v>
+      </c>
+      <c r="U7" s="23" t="n">
+        <f aca="false">100+A7</f>
+        <v>103</v>
+      </c>
+      <c r="V7" s="23" t="n">
+        <f aca="false">200+A7</f>
+        <v>203</v>
+      </c>
+      <c r="W7" s="23" t="n">
+        <f aca="false">300+A7</f>
+        <v>303</v>
+      </c>
+      <c r="X7" s="23" t="str">
+        <f aca="false">"10."&amp;A7&amp;".1.0/24"</f>
+        <v>10.3.1.0/24</v>
+      </c>
+      <c r="Y7" s="23" t="str">
+        <f aca="false">IF(R7&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C7,$R$5:$R$92,R7)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q7)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F7&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="n">
@@ -17702,6 +18511,42 @@
         <f aca="false">IF(ISNA(MATCH(C8,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C8=A8,"OK",IF(INDEX($C$5:$C$92,MATCH(C8,Anlagen!$A$5:$A$92,0))&lt;&gt;C8,"Fehler: Standort hängt selbst an anderem Standort",IF(D8=A8,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D8,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D8,Anlagen!$A$5:$A$92,0))&lt;&gt;C8,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q8" s="23" t="str">
+        <f aca="false">Anlagen!AA8</f>
+        <v>ABRUH</v>
+      </c>
+      <c r="R8" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB8&lt;&gt;"",Anlagen!AB8,COUNTIFS($C$5:$C$92,C8,$J$5:$J$92,"&lt;"&amp;J8)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="S8" s="23" t="n">
+        <f aca="false">1000+200*(R8-1)+1</f>
+        <v>1401</v>
+      </c>
+      <c r="T8" s="23" t="n">
+        <f aca="false">1000+200*(R8-1)+Anlagen!F8</f>
+        <v>1542</v>
+      </c>
+      <c r="U8" s="23" t="n">
+        <f aca="false">100+A8</f>
+        <v>104</v>
+      </c>
+      <c r="V8" s="23" t="n">
+        <f aca="false">200+A8</f>
+        <v>204</v>
+      </c>
+      <c r="W8" s="23" t="n">
+        <f aca="false">300+A8</f>
+        <v>304</v>
+      </c>
+      <c r="X8" s="23" t="str">
+        <f aca="false">"10."&amp;A8&amp;".1.0/24"</f>
+        <v>10.4.1.0/24</v>
+      </c>
+      <c r="Y8" s="23" t="str">
+        <f aca="false">IF(R8&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C8,$R$5:$R$92,R8)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q8)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F8&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="n">
@@ -17768,6 +18613,42 @@
         <f aca="false">IF(ISNA(MATCH(C9,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C9=A9,"OK",IF(INDEX($C$5:$C$92,MATCH(C9,Anlagen!$A$5:$A$92,0))&lt;&gt;C9,"Fehler: Standort hängt selbst an anderem Standort",IF(D9=A9,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D9,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D9,Anlagen!$A$5:$A$92,0))&lt;&gt;C9,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q9" s="23" t="str">
+        <f aca="false">Anlagen!AA9</f>
+        <v>ABSON</v>
+      </c>
+      <c r="R9" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB9&lt;&gt;"",Anlagen!AB9,COUNTIFS($C$5:$C$92,C9,$J$5:$J$92,"&lt;"&amp;J9)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S9" s="23" t="n">
+        <f aca="false">1000+200*(R9-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T9" s="23" t="n">
+        <f aca="false">1000+200*(R9-1)+Anlagen!F9</f>
+        <v>1267</v>
+      </c>
+      <c r="U9" s="23" t="n">
+        <f aca="false">100+A9</f>
+        <v>105</v>
+      </c>
+      <c r="V9" s="23" t="n">
+        <f aca="false">200+A9</f>
+        <v>205</v>
+      </c>
+      <c r="W9" s="23" t="n">
+        <f aca="false">300+A9</f>
+        <v>305</v>
+      </c>
+      <c r="X9" s="23" t="str">
+        <f aca="false">"10."&amp;A9&amp;".1.0/24"</f>
+        <v>10.5.1.0/24</v>
+      </c>
+      <c r="Y9" s="23" t="str">
+        <f aca="false">IF(R9&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C9,$R$5:$R$92,R9)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q9)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F9&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="n">
@@ -17834,6 +18715,42 @@
         <f aca="false">IF(ISNA(MATCH(C10,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C10=A10,"OK",IF(INDEX($C$5:$C$92,MATCH(C10,Anlagen!$A$5:$A$92,0))&lt;&gt;C10,"Fehler: Standort hängt selbst an anderem Standort",IF(D10=A10,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D10,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D10,Anlagen!$A$5:$A$92,0))&lt;&gt;C10,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q10" s="23" t="str">
+        <f aca="false">Anlagen!AA10</f>
+        <v>ALTFO</v>
+      </c>
+      <c r="R10" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB10&lt;&gt;"",Anlagen!AB10,COUNTIFS($C$5:$C$92,C10,$J$5:$J$92,"&lt;"&amp;J10)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="S10" s="23" t="n">
+        <f aca="false">1000+200*(R10-1)+1</f>
+        <v>1401</v>
+      </c>
+      <c r="T10" s="23" t="n">
+        <f aca="false">1000+200*(R10-1)+Anlagen!F10</f>
+        <v>1488</v>
+      </c>
+      <c r="U10" s="23" t="n">
+        <f aca="false">100+A10</f>
+        <v>106</v>
+      </c>
+      <c r="V10" s="23" t="n">
+        <f aca="false">200+A10</f>
+        <v>206</v>
+      </c>
+      <c r="W10" s="23" t="n">
+        <f aca="false">300+A10</f>
+        <v>306</v>
+      </c>
+      <c r="X10" s="23" t="str">
+        <f aca="false">"10."&amp;A10&amp;".1.0/24"</f>
+        <v>10.6.1.0/24</v>
+      </c>
+      <c r="Y10" s="23" t="str">
+        <f aca="false">IF(R10&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C10,$R$5:$R$92,R10)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q10)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F10&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="n">
@@ -17900,6 +18817,42 @@
         <f aca="false">IF(ISNA(MATCH(C11,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C11=A11,"OK",IF(INDEX($C$5:$C$92,MATCH(C11,Anlagen!$A$5:$A$92,0))&lt;&gt;C11,"Fehler: Standort hängt selbst an anderem Standort",IF(D11=A11,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D11,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D11,Anlagen!$A$5:$A$92,0))&lt;&gt;C11,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q11" s="23" t="str">
+        <f aca="false">Anlagen!AA11</f>
+        <v>BEETZ</v>
+      </c>
+      <c r="R11" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB11&lt;&gt;"",Anlagen!AB11,COUNTIFS($C$5:$C$92,C11,$J$5:$J$92,"&lt;"&amp;J11)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S11" s="23" t="n">
+        <f aca="false">1000+200*(R11-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T11" s="23" t="n">
+        <f aca="false">1000+200*(R11-1)+Anlagen!F11</f>
+        <v>1277</v>
+      </c>
+      <c r="U11" s="23" t="n">
+        <f aca="false">100+A11</f>
+        <v>107</v>
+      </c>
+      <c r="V11" s="23" t="n">
+        <f aca="false">200+A11</f>
+        <v>207</v>
+      </c>
+      <c r="W11" s="23" t="n">
+        <f aca="false">300+A11</f>
+        <v>307</v>
+      </c>
+      <c r="X11" s="23" t="str">
+        <f aca="false">"10."&amp;A11&amp;".1.0/24"</f>
+        <v>10.7.1.0/24</v>
+      </c>
+      <c r="Y11" s="23" t="str">
+        <f aca="false">IF(R11&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C11,$R$5:$R$92,R11)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q11)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F11&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="n">
@@ -17966,6 +18919,42 @@
         <f aca="false">IF(ISNA(MATCH(C12,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C12=A12,"OK",IF(INDEX($C$5:$C$92,MATCH(C12,Anlagen!$A$5:$A$92,0))&lt;&gt;C12,"Fehler: Standort hängt selbst an anderem Standort",IF(D12=A12,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D12,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D12,Anlagen!$A$5:$A$92,0))&lt;&gt;C12,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q12" s="23" t="str">
+        <f aca="false">Anlagen!AA12</f>
+        <v>BUETT</v>
+      </c>
+      <c r="R12" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB12&lt;&gt;"",Anlagen!AB12,COUNTIFS($C$5:$C$92,C12,$J$5:$J$92,"&lt;"&amp;J12)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="S12" s="23" t="n">
+        <f aca="false">1000+200*(R12-1)+1</f>
+        <v>1401</v>
+      </c>
+      <c r="T12" s="23" t="n">
+        <f aca="false">1000+200*(R12-1)+Anlagen!F12</f>
+        <v>1405</v>
+      </c>
+      <c r="U12" s="23" t="n">
+        <f aca="false">100+A12</f>
+        <v>108</v>
+      </c>
+      <c r="V12" s="23" t="n">
+        <f aca="false">200+A12</f>
+        <v>208</v>
+      </c>
+      <c r="W12" s="23" t="n">
+        <f aca="false">300+A12</f>
+        <v>308</v>
+      </c>
+      <c r="X12" s="23" t="str">
+        <f aca="false">"10."&amp;A12&amp;".1.0/24"</f>
+        <v>10.8.1.0/24</v>
+      </c>
+      <c r="Y12" s="23" t="str">
+        <f aca="false">IF(R12&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C12,$R$5:$R$92,R12)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q12)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F12&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="n">
@@ -18032,6 +19021,42 @@
         <f aca="false">IF(ISNA(MATCH(C13,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C13=A13,"OK",IF(INDEX($C$5:$C$92,MATCH(C13,Anlagen!$A$5:$A$92,0))&lt;&gt;C13,"Fehler: Standort hängt selbst an anderem Standort",IF(D13=A13,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D13,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D13,Anlagen!$A$5:$A$92,0))&lt;&gt;C13,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q13" s="23" t="str">
+        <f aca="false">Anlagen!AA13</f>
+        <v>EICHW</v>
+      </c>
+      <c r="R13" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB13&lt;&gt;"",Anlagen!AB13,COUNTIFS($C$5:$C$92,C13,$J$5:$J$92,"&lt;"&amp;J13)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S13" s="23" t="n">
+        <f aca="false">1000+200*(R13-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T13" s="23" t="n">
+        <f aca="false">1000+200*(R13-1)+Anlagen!F13</f>
+        <v>1254</v>
+      </c>
+      <c r="U13" s="23" t="n">
+        <f aca="false">100+A13</f>
+        <v>109</v>
+      </c>
+      <c r="V13" s="23" t="n">
+        <f aca="false">200+A13</f>
+        <v>209</v>
+      </c>
+      <c r="W13" s="23" t="n">
+        <f aca="false">300+A13</f>
+        <v>309</v>
+      </c>
+      <c r="X13" s="23" t="str">
+        <f aca="false">"10."&amp;A13&amp;".1.0/24"</f>
+        <v>10.9.1.0/24</v>
+      </c>
+      <c r="Y13" s="23" t="str">
+        <f aca="false">IF(R13&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C13,$R$5:$R$92,R13)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q13)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F13&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="n">
@@ -18098,6 +19123,42 @@
         <f aca="false">IF(ISNA(MATCH(C14,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C14=A14,"OK",IF(INDEX($C$5:$C$92,MATCH(C14,Anlagen!$A$5:$A$92,0))&lt;&gt;C14,"Fehler: Standort hängt selbst an anderem Standort",IF(D14=A14,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D14,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D14,Anlagen!$A$5:$A$92,0))&lt;&gt;C14,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q14" s="23" t="str">
+        <f aca="false">Anlagen!AA14</f>
+        <v>JAKGR</v>
+      </c>
+      <c r="R14" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB14&lt;&gt;"",Anlagen!AB14,COUNTIFS($C$5:$C$92,C14,$J$5:$J$92,"&lt;"&amp;J14)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="S14" s="23" t="n">
+        <f aca="false">1000+200*(R14-1)+1</f>
+        <v>1401</v>
+      </c>
+      <c r="T14" s="23" t="n">
+        <f aca="false">1000+200*(R14-1)+Anlagen!F14</f>
+        <v>1441</v>
+      </c>
+      <c r="U14" s="23" t="n">
+        <f aca="false">100+A14</f>
+        <v>110</v>
+      </c>
+      <c r="V14" s="23" t="n">
+        <f aca="false">200+A14</f>
+        <v>210</v>
+      </c>
+      <c r="W14" s="23" t="n">
+        <f aca="false">300+A14</f>
+        <v>310</v>
+      </c>
+      <c r="X14" s="23" t="str">
+        <f aca="false">"10."&amp;A14&amp;".1.0/24"</f>
+        <v>10.10.1.0/24</v>
+      </c>
+      <c r="Y14" s="23" t="str">
+        <f aca="false">IF(R14&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C14,$R$5:$R$92,R14)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q14)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F14&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="n">
@@ -18164,6 +19225,42 @@
         <f aca="false">IF(ISNA(MATCH(C15,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C15=A15,"OK",IF(INDEX($C$5:$C$92,MATCH(C15,Anlagen!$A$5:$A$92,0))&lt;&gt;C15,"Fehler: Standort hängt selbst an anderem Standort",IF(D15=A15,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D15,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D15,Anlagen!$A$5:$A$92,0))&lt;&gt;C15,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q15" s="23" t="str">
+        <f aca="false">Anlagen!AA15</f>
+        <v>SCHAF</v>
+      </c>
+      <c r="R15" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB15&lt;&gt;"",Anlagen!AB15,COUNTIFS($C$5:$C$92,C15,$J$5:$J$92,"&lt;"&amp;J15)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="S15" s="23" t="n">
+        <f aca="false">1000+200*(R15-1)+1</f>
+        <v>1601</v>
+      </c>
+      <c r="T15" s="23" t="n">
+        <f aca="false">1000+200*(R15-1)+Anlagen!F15</f>
+        <v>1610</v>
+      </c>
+      <c r="U15" s="23" t="n">
+        <f aca="false">100+A15</f>
+        <v>111</v>
+      </c>
+      <c r="V15" s="23" t="n">
+        <f aca="false">200+A15</f>
+        <v>211</v>
+      </c>
+      <c r="W15" s="23" t="n">
+        <f aca="false">300+A15</f>
+        <v>311</v>
+      </c>
+      <c r="X15" s="23" t="str">
+        <f aca="false">"10."&amp;A15&amp;".1.0/24"</f>
+        <v>10.11.1.0/24</v>
+      </c>
+      <c r="Y15" s="23" t="str">
+        <f aca="false">IF(R15&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C15,$R$5:$R$92,R15)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q15)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F15&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="n">
@@ -18230,6 +19327,42 @@
         <f aca="false">IF(ISNA(MATCH(C16,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C16=A16,"OK",IF(INDEX($C$5:$C$92,MATCH(C16,Anlagen!$A$5:$A$92,0))&lt;&gt;C16,"Fehler: Standort hängt selbst an anderem Standort",IF(D16=A16,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D16,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D16,Anlagen!$A$5:$A$92,0))&lt;&gt;C16,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q16" s="23" t="str">
+        <f aca="false">Anlagen!AA16</f>
+        <v>SCHLA</v>
+      </c>
+      <c r="R16" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB16&lt;&gt;"",Anlagen!AB16,COUNTIFS($C$5:$C$92,C16,$J$5:$J$92,"&lt;"&amp;J16)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="S16" s="23" t="n">
+        <f aca="false">1000+200*(R16-1)+1</f>
+        <v>1801</v>
+      </c>
+      <c r="T16" s="23" t="n">
+        <f aca="false">1000+200*(R16-1)+Anlagen!F16</f>
+        <v>1819</v>
+      </c>
+      <c r="U16" s="23" t="n">
+        <f aca="false">100+A16</f>
+        <v>112</v>
+      </c>
+      <c r="V16" s="23" t="n">
+        <f aca="false">200+A16</f>
+        <v>212</v>
+      </c>
+      <c r="W16" s="23" t="n">
+        <f aca="false">300+A16</f>
+        <v>312</v>
+      </c>
+      <c r="X16" s="23" t="str">
+        <f aca="false">"10."&amp;A16&amp;".1.0/24"</f>
+        <v>10.12.1.0/24</v>
+      </c>
+      <c r="Y16" s="23" t="str">
+        <f aca="false">IF(R16&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C16,$R$5:$R$92,R16)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q16)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F16&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="n">
@@ -18296,6 +19429,42 @@
         <f aca="false">IF(ISNA(MATCH(C17,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C17=A17,"OK",IF(INDEX($C$5:$C$92,MATCH(C17,Anlagen!$A$5:$A$92,0))&lt;&gt;C17,"Fehler: Standort hängt selbst an anderem Standort",IF(D17=A17,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D17,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D17,Anlagen!$A$5:$A$92,0))&lt;&gt;C17,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q17" s="23" t="str">
+        <f aca="false">Anlagen!AA17</f>
+        <v>WALDR</v>
+      </c>
+      <c r="R17" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB17&lt;&gt;"",Anlagen!AB17,COUNTIFS($C$5:$C$92,C17,$J$5:$J$92,"&lt;"&amp;J17)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="S17" s="23" t="n">
+        <f aca="false">1000+200*(R17-1)+1</f>
+        <v>2001</v>
+      </c>
+      <c r="T17" s="23" t="n">
+        <f aca="false">1000+200*(R17-1)+Anlagen!F17</f>
+        <v>2096</v>
+      </c>
+      <c r="U17" s="23" t="n">
+        <f aca="false">100+A17</f>
+        <v>113</v>
+      </c>
+      <c r="V17" s="23" t="n">
+        <f aca="false">200+A17</f>
+        <v>213</v>
+      </c>
+      <c r="W17" s="23" t="n">
+        <f aca="false">300+A17</f>
+        <v>313</v>
+      </c>
+      <c r="X17" s="23" t="str">
+        <f aca="false">"10."&amp;A17&amp;".1.0/24"</f>
+        <v>10.13.1.0/24</v>
+      </c>
+      <c r="Y17" s="23" t="str">
+        <f aca="false">IF(R17&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C17,$R$5:$R$92,R17)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q17)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F17&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="n">
@@ -18362,6 +19531,42 @@
         <f aca="false">IF(ISNA(MATCH(C18,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C18=A18,"OK",IF(INDEX($C$5:$C$92,MATCH(C18,Anlagen!$A$5:$A$92,0))&lt;&gt;C18,"Fehler: Standort hängt selbst an anderem Standort",IF(D18=A18,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D18,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D18,Anlagen!$A$5:$A$92,0))&lt;&gt;C18,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q18" s="23" t="str">
+        <f aca="false">Anlagen!AA18</f>
+        <v>PLAN1</v>
+      </c>
+      <c r="R18" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB18&lt;&gt;"",Anlagen!AB18,COUNTIFS($C$5:$C$92,C18,$J$5:$J$92,"&lt;"&amp;J18)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S18" s="23" t="n">
+        <f aca="false">1000+200*(R18-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T18" s="23" t="n">
+        <f aca="false">1000+200*(R18-1)+Anlagen!F18</f>
+        <v>1216</v>
+      </c>
+      <c r="U18" s="23" t="n">
+        <f aca="false">100+A18</f>
+        <v>114</v>
+      </c>
+      <c r="V18" s="23" t="n">
+        <f aca="false">200+A18</f>
+        <v>214</v>
+      </c>
+      <c r="W18" s="23" t="n">
+        <f aca="false">300+A18</f>
+        <v>314</v>
+      </c>
+      <c r="X18" s="23" t="str">
+        <f aca="false">"10."&amp;A18&amp;".1.0/24"</f>
+        <v>10.14.1.0/24</v>
+      </c>
+      <c r="Y18" s="23" t="str">
+        <f aca="false">IF(R18&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C18,$R$5:$R$92,R18)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q18)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F18&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="n">
@@ -18428,6 +19633,42 @@
         <f aca="false">IF(ISNA(MATCH(C19,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C19=A19,"OK",IF(INDEX($C$5:$C$92,MATCH(C19,Anlagen!$A$5:$A$92,0))&lt;&gt;C19,"Fehler: Standort hängt selbst an anderem Standort",IF(D19=A19,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D19,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D19,Anlagen!$A$5:$A$92,0))&lt;&gt;C19,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q19" s="23" t="str">
+        <f aca="false">Anlagen!AA19</f>
+        <v>BERGH</v>
+      </c>
+      <c r="R19" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB19&lt;&gt;"",Anlagen!AB19,COUNTIFS($C$5:$C$92,C19,$J$5:$J$92,"&lt;"&amp;J19)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S19" s="23" t="n">
+        <f aca="false">1000+200*(R19-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T19" s="23" t="n">
+        <f aca="false">1000+200*(R19-1)+Anlagen!F19</f>
+        <v>1214</v>
+      </c>
+      <c r="U19" s="23" t="n">
+        <f aca="false">100+A19</f>
+        <v>115</v>
+      </c>
+      <c r="V19" s="23" t="n">
+        <f aca="false">200+A19</f>
+        <v>215</v>
+      </c>
+      <c r="W19" s="23" t="n">
+        <f aca="false">300+A19</f>
+        <v>315</v>
+      </c>
+      <c r="X19" s="23" t="str">
+        <f aca="false">"10."&amp;A19&amp;".1.0/24"</f>
+        <v>10.15.1.0/24</v>
+      </c>
+      <c r="Y19" s="23" t="str">
+        <f aca="false">IF(R19&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C19,$R$5:$R$92,R19)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q19)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F19&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="n">
@@ -18494,6 +19735,42 @@
         <f aca="false">IF(ISNA(MATCH(C20,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C20=A20,"OK",IF(INDEX($C$5:$C$92,MATCH(C20,Anlagen!$A$5:$A$92,0))&lt;&gt;C20,"Fehler: Standort hängt selbst an anderem Standort",IF(D20=A20,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D20,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D20,Anlagen!$A$5:$A$92,0))&lt;&gt;C20,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q20" s="23" t="str">
+        <f aca="false">Anlagen!AA20</f>
+        <v>BERGF</v>
+      </c>
+      <c r="R20" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB20&lt;&gt;"",Anlagen!AB20,COUNTIFS($C$5:$C$92,C20,$J$5:$J$92,"&lt;"&amp;J20)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S20" s="23" t="n">
+        <f aca="false">1000+200*(R20-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T20" s="23" t="n">
+        <f aca="false">1000+200*(R20-1)+Anlagen!F20</f>
+        <v>1130</v>
+      </c>
+      <c r="U20" s="23" t="n">
+        <f aca="false">100+A20</f>
+        <v>116</v>
+      </c>
+      <c r="V20" s="23" t="n">
+        <f aca="false">200+A20</f>
+        <v>216</v>
+      </c>
+      <c r="W20" s="23" t="n">
+        <f aca="false">300+A20</f>
+        <v>316</v>
+      </c>
+      <c r="X20" s="23" t="str">
+        <f aca="false">"10."&amp;A20&amp;".1.0/24"</f>
+        <v>10.16.1.0/24</v>
+      </c>
+      <c r="Y20" s="23" t="str">
+        <f aca="false">IF(R20&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C20,$R$5:$R$92,R20)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q20)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F20&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="n">
@@ -18560,6 +19837,42 @@
         <f aca="false">IF(ISNA(MATCH(C21,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C21=A21,"OK",IF(INDEX($C$5:$C$92,MATCH(C21,Anlagen!$A$5:$A$92,0))&lt;&gt;C21,"Fehler: Standort hängt selbst an anderem Standort",IF(D21=A21,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D21,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D21,Anlagen!$A$5:$A$92,0))&lt;&gt;C21,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q21" s="23" t="str">
+        <f aca="false">Anlagen!AA21</f>
+        <v>BIRKE</v>
+      </c>
+      <c r="R21" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB21&lt;&gt;"",Anlagen!AB21,COUNTIFS($C$5:$C$92,C21,$J$5:$J$92,"&lt;"&amp;J21)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S21" s="23" t="n">
+        <f aca="false">1000+200*(R21-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T21" s="23" t="n">
+        <f aca="false">1000+200*(R21-1)+Anlagen!F21</f>
+        <v>1056</v>
+      </c>
+      <c r="U21" s="23" t="n">
+        <f aca="false">100+A21</f>
+        <v>117</v>
+      </c>
+      <c r="V21" s="23" t="n">
+        <f aca="false">200+A21</f>
+        <v>217</v>
+      </c>
+      <c r="W21" s="23" t="n">
+        <f aca="false">300+A21</f>
+        <v>317</v>
+      </c>
+      <c r="X21" s="23" t="str">
+        <f aca="false">"10."&amp;A21&amp;".1.0/24"</f>
+        <v>10.17.1.0/24</v>
+      </c>
+      <c r="Y21" s="23" t="str">
+        <f aca="false">IF(R21&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C21,$R$5:$R$92,R21)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q21)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F21&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="n">
@@ -18626,6 +19939,42 @@
         <f aca="false">IF(ISNA(MATCH(C22,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C22=A22,"OK",IF(INDEX($C$5:$C$92,MATCH(C22,Anlagen!$A$5:$A$92,0))&lt;&gt;C22,"Fehler: Standort hängt selbst an anderem Standort",IF(D22=A22,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D22,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D22,Anlagen!$A$5:$A$92,0))&lt;&gt;C22,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q22" s="23" t="str">
+        <f aca="false">Anlagen!AA22</f>
+        <v>PFEFF</v>
+      </c>
+      <c r="R22" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB22&lt;&gt;"",Anlagen!AB22,COUNTIFS($C$5:$C$92,C22,$J$5:$J$92,"&lt;"&amp;J22)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="S22" s="23" t="n">
+        <f aca="false">1000+200*(R22-1)+1</f>
+        <v>1401</v>
+      </c>
+      <c r="T22" s="23" t="n">
+        <f aca="false">1000+200*(R22-1)+Anlagen!F22</f>
+        <v>1464</v>
+      </c>
+      <c r="U22" s="23" t="n">
+        <f aca="false">100+A22</f>
+        <v>118</v>
+      </c>
+      <c r="V22" s="23" t="n">
+        <f aca="false">200+A22</f>
+        <v>218</v>
+      </c>
+      <c r="W22" s="23" t="n">
+        <f aca="false">300+A22</f>
+        <v>318</v>
+      </c>
+      <c r="X22" s="23" t="str">
+        <f aca="false">"10."&amp;A22&amp;".1.0/24"</f>
+        <v>10.18.1.0/24</v>
+      </c>
+      <c r="Y22" s="23" t="str">
+        <f aca="false">IF(R22&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C22,$R$5:$R$92,R22)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q22)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F22&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="n">
@@ -18692,6 +20041,42 @@
         <f aca="false">IF(ISNA(MATCH(C23,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C23=A23,"OK",IF(INDEX($C$5:$C$92,MATCH(C23,Anlagen!$A$5:$A$92,0))&lt;&gt;C23,"Fehler: Standort hängt selbst an anderem Standort",IF(D23=A23,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D23,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D23,Anlagen!$A$5:$A$92,0))&lt;&gt;C23,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q23" s="23" t="str">
+        <f aca="false">Anlagen!AA23</f>
+        <v>BRIDR</v>
+      </c>
+      <c r="R23" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB23&lt;&gt;"",Anlagen!AB23,COUNTIFS($C$5:$C$92,C23,$J$5:$J$92,"&lt;"&amp;J23)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S23" s="23" t="n">
+        <f aca="false">1000+200*(R23-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T23" s="23" t="n">
+        <f aca="false">1000+200*(R23-1)+Anlagen!F23</f>
+        <v>1235</v>
+      </c>
+      <c r="U23" s="23" t="n">
+        <f aca="false">100+A23</f>
+        <v>119</v>
+      </c>
+      <c r="V23" s="23" t="n">
+        <f aca="false">200+A23</f>
+        <v>219</v>
+      </c>
+      <c r="W23" s="23" t="n">
+        <f aca="false">300+A23</f>
+        <v>319</v>
+      </c>
+      <c r="X23" s="23" t="str">
+        <f aca="false">"10."&amp;A23&amp;".1.0/24"</f>
+        <v>10.19.1.0/24</v>
+      </c>
+      <c r="Y23" s="23" t="str">
+        <f aca="false">IF(R23&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C23,$R$5:$R$92,R23)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q23)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F23&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="n">
@@ -18758,6 +20143,42 @@
         <f aca="false">IF(ISNA(MATCH(C24,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C24=A24,"OK",IF(INDEX($C$5:$C$92,MATCH(C24,Anlagen!$A$5:$A$92,0))&lt;&gt;C24,"Fehler: Standort hängt selbst an anderem Standort",IF(D24=A24,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D24,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D24,Anlagen!$A$5:$A$92,0))&lt;&gt;C24,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q24" s="23" t="str">
+        <f aca="false">Anlagen!AA24</f>
+        <v>BW</v>
+      </c>
+      <c r="R24" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB24&lt;&gt;"",Anlagen!AB24,COUNTIFS($C$5:$C$92,C24,$J$5:$J$92,"&lt;"&amp;J24)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="S24" s="23" t="n">
+        <f aca="false">1000+200*(R24-1)+1</f>
+        <v>1401</v>
+      </c>
+      <c r="T24" s="23" t="n">
+        <f aca="false">1000+200*(R24-1)+Anlagen!F24</f>
+        <v>1486</v>
+      </c>
+      <c r="U24" s="23" t="n">
+        <f aca="false">100+A24</f>
+        <v>120</v>
+      </c>
+      <c r="V24" s="23" t="n">
+        <f aca="false">200+A24</f>
+        <v>220</v>
+      </c>
+      <c r="W24" s="23" t="n">
+        <f aca="false">300+A24</f>
+        <v>320</v>
+      </c>
+      <c r="X24" s="23" t="str">
+        <f aca="false">"10."&amp;A24&amp;".1.0/24"</f>
+        <v>10.20.1.0/24</v>
+      </c>
+      <c r="Y24" s="23" t="str">
+        <f aca="false">IF(R24&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C24,$R$5:$R$92,R24)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q24)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F24&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="n">
@@ -18824,6 +20245,42 @@
         <f aca="false">IF(ISNA(MATCH(C25,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C25=A25,"OK",IF(INDEX($C$5:$C$92,MATCH(C25,Anlagen!$A$5:$A$92,0))&lt;&gt;C25,"Fehler: Standort hängt selbst an anderem Standort",IF(D25=A25,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D25,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D25,Anlagen!$A$5:$A$92,0))&lt;&gt;C25,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q25" s="23" t="str">
+        <f aca="false">Anlagen!AA25</f>
+        <v>BUTTL</v>
+      </c>
+      <c r="R25" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB25&lt;&gt;"",Anlagen!AB25,COUNTIFS($C$5:$C$92,C25,$J$5:$J$92,"&lt;"&amp;J25)+1)</f>
+        <v>7</v>
+      </c>
+      <c r="S25" s="23" t="n">
+        <f aca="false">1000+200*(R25-1)+1</f>
+        <v>2201</v>
+      </c>
+      <c r="T25" s="23" t="n">
+        <f aca="false">1000+200*(R25-1)+Anlagen!F25</f>
+        <v>2275</v>
+      </c>
+      <c r="U25" s="23" t="n">
+        <f aca="false">100+A25</f>
+        <v>121</v>
+      </c>
+      <c r="V25" s="23" t="n">
+        <f aca="false">200+A25</f>
+        <v>221</v>
+      </c>
+      <c r="W25" s="23" t="n">
+        <f aca="false">300+A25</f>
+        <v>321</v>
+      </c>
+      <c r="X25" s="23" t="str">
+        <f aca="false">"10."&amp;A25&amp;".1.0/24"</f>
+        <v>10.21.1.0/24</v>
+      </c>
+      <c r="Y25" s="23" t="str">
+        <f aca="false">IF(R25&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C25,$R$5:$R$92,R25)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q25)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F25&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="n">
@@ -18890,6 +20347,42 @@
         <f aca="false">IF(ISNA(MATCH(C26,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C26=A26,"OK",IF(INDEX($C$5:$C$92,MATCH(C26,Anlagen!$A$5:$A$92,0))&lt;&gt;C26,"Fehler: Standort hängt selbst an anderem Standort",IF(D26=A26,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D26,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D26,Anlagen!$A$5:$A$92,0))&lt;&gt;C26,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q26" s="23" t="str">
+        <f aca="false">Anlagen!AA26</f>
+        <v>EICHH</v>
+      </c>
+      <c r="R26" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB26&lt;&gt;"",Anlagen!AB26,COUNTIFS($C$5:$C$92,C26,$J$5:$J$92,"&lt;"&amp;J26)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S26" s="23" t="n">
+        <f aca="false">1000+200*(R26-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T26" s="23" t="n">
+        <f aca="false">1000+200*(R26-1)+Anlagen!F26</f>
+        <v>1038</v>
+      </c>
+      <c r="U26" s="23" t="n">
+        <f aca="false">100+A26</f>
+        <v>122</v>
+      </c>
+      <c r="V26" s="23" t="n">
+        <f aca="false">200+A26</f>
+        <v>222</v>
+      </c>
+      <c r="W26" s="23" t="n">
+        <f aca="false">300+A26</f>
+        <v>322</v>
+      </c>
+      <c r="X26" s="23" t="str">
+        <f aca="false">"10."&amp;A26&amp;".1.0/24"</f>
+        <v>10.22.1.0/24</v>
+      </c>
+      <c r="Y26" s="23" t="str">
+        <f aca="false">IF(R26&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C26,$R$5:$R$92,R26)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q26)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F26&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="n">
@@ -18956,6 +20449,42 @@
         <f aca="false">IF(ISNA(MATCH(C27,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C27=A27,"OK",IF(INDEX($C$5:$C$92,MATCH(C27,Anlagen!$A$5:$A$92,0))&lt;&gt;C27,"Fehler: Standort hängt selbst an anderem Standort",IF(D27=A27,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D27,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D27,Anlagen!$A$5:$A$92,0))&lt;&gt;C27,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q27" s="23" t="str">
+        <f aca="false">Anlagen!AA27</f>
+        <v>FLEIS</v>
+      </c>
+      <c r="R27" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB27&lt;&gt;"",Anlagen!AB27,COUNTIFS($C$5:$C$92,C27,$J$5:$J$92,"&lt;"&amp;J27)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S27" s="23" t="n">
+        <f aca="false">1000+200*(R27-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T27" s="23" t="n">
+        <f aca="false">1000+200*(R27-1)+Anlagen!F27</f>
+        <v>1123</v>
+      </c>
+      <c r="U27" s="23" t="n">
+        <f aca="false">100+A27</f>
+        <v>123</v>
+      </c>
+      <c r="V27" s="23" t="n">
+        <f aca="false">200+A27</f>
+        <v>223</v>
+      </c>
+      <c r="W27" s="23" t="n">
+        <f aca="false">300+A27</f>
+        <v>323</v>
+      </c>
+      <c r="X27" s="23" t="str">
+        <f aca="false">"10."&amp;A27&amp;".1.0/24"</f>
+        <v>10.23.1.0/24</v>
+      </c>
+      <c r="Y27" s="23" t="str">
+        <f aca="false">IF(R27&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C27,$R$5:$R$92,R27)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q27)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F27&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="n">
@@ -19022,6 +20551,42 @@
         <f aca="false">IF(ISNA(MATCH(C28,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C28=A28,"OK",IF(INDEX($C$5:$C$92,MATCH(C28,Anlagen!$A$5:$A$92,0))&lt;&gt;C28,"Fehler: Standort hängt selbst an anderem Standort",IF(D28=A28,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D28,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D28,Anlagen!$A$5:$A$92,0))&lt;&gt;C28,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q28" s="23" t="str">
+        <f aca="false">Anlagen!AA28</f>
+        <v>EINH</v>
+      </c>
+      <c r="R28" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB28&lt;&gt;"",Anlagen!AB28,COUNTIFS($C$5:$C$92,C28,$J$5:$J$92,"&lt;"&amp;J28)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="S28" s="23" t="n">
+        <f aca="false">1000+200*(R28-1)+1</f>
+        <v>1401</v>
+      </c>
+      <c r="T28" s="23" t="n">
+        <f aca="false">1000+200*(R28-1)+Anlagen!F28</f>
+        <v>1499</v>
+      </c>
+      <c r="U28" s="23" t="n">
+        <f aca="false">100+A28</f>
+        <v>124</v>
+      </c>
+      <c r="V28" s="23" t="n">
+        <f aca="false">200+A28</f>
+        <v>224</v>
+      </c>
+      <c r="W28" s="23" t="n">
+        <f aca="false">300+A28</f>
+        <v>324</v>
+      </c>
+      <c r="X28" s="23" t="str">
+        <f aca="false">"10."&amp;A28&amp;".1.0/24"</f>
+        <v>10.24.1.0/24</v>
+      </c>
+      <c r="Y28" s="23" t="str">
+        <f aca="false">IF(R28&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C28,$R$5:$R$92,R28)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q28)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F28&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="n">
@@ -19088,6 +20653,42 @@
         <f aca="false">IF(ISNA(MATCH(C29,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C29=A29,"OK",IF(INDEX($C$5:$C$92,MATCH(C29,Anlagen!$A$5:$A$92,0))&lt;&gt;C29,"Fehler: Standort hängt selbst an anderem Standort",IF(D29=A29,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D29,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D29,Anlagen!$A$5:$A$92,0))&lt;&gt;C29,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q29" s="23" t="str">
+        <f aca="false">Anlagen!AA29</f>
+        <v>EINIG</v>
+      </c>
+      <c r="R29" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB29&lt;&gt;"",Anlagen!AB29,COUNTIFS($C$5:$C$92,C29,$J$5:$J$92,"&lt;"&amp;J29)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S29" s="23" t="n">
+        <f aca="false">1000+200*(R29-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T29" s="23" t="n">
+        <f aca="false">1000+200*(R29-1)+Anlagen!F29</f>
+        <v>1214</v>
+      </c>
+      <c r="U29" s="23" t="n">
+        <f aca="false">100+A29</f>
+        <v>125</v>
+      </c>
+      <c r="V29" s="23" t="n">
+        <f aca="false">200+A29</f>
+        <v>225</v>
+      </c>
+      <c r="W29" s="23" t="n">
+        <f aca="false">300+A29</f>
+        <v>325</v>
+      </c>
+      <c r="X29" s="23" t="str">
+        <f aca="false">"10."&amp;A29&amp;".1.0/24"</f>
+        <v>10.25.1.0/24</v>
+      </c>
+      <c r="Y29" s="23" t="str">
+        <f aca="false">IF(R29&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C29,$R$5:$R$92,R29)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q29)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F29&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="n">
@@ -19154,6 +20755,42 @@
         <f aca="false">IF(ISNA(MATCH(C30,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C30=A30,"OK",IF(INDEX($C$5:$C$92,MATCH(C30,Anlagen!$A$5:$A$92,0))&lt;&gt;C30,"Fehler: Standort hängt selbst an anderem Standort",IF(D30=A30,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D30,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D30,Anlagen!$A$5:$A$92,0))&lt;&gt;C30,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q30" s="23" t="str">
+        <f aca="false">Anlagen!AA30</f>
+        <v>EINT1</v>
+      </c>
+      <c r="R30" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB30&lt;&gt;"",Anlagen!AB30,COUNTIFS($C$5:$C$92,C30,$J$5:$J$92,"&lt;"&amp;J30)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="S30" s="23" t="n">
+        <f aca="false">1000+200*(R30-1)+1</f>
+        <v>1601</v>
+      </c>
+      <c r="T30" s="23" t="n">
+        <f aca="false">1000+200*(R30-1)+Anlagen!F30</f>
+        <v>1632</v>
+      </c>
+      <c r="U30" s="23" t="n">
+        <f aca="false">100+A30</f>
+        <v>126</v>
+      </c>
+      <c r="V30" s="23" t="n">
+        <f aca="false">200+A30</f>
+        <v>226</v>
+      </c>
+      <c r="W30" s="23" t="n">
+        <f aca="false">300+A30</f>
+        <v>326</v>
+      </c>
+      <c r="X30" s="23" t="str">
+        <f aca="false">"10."&amp;A30&amp;".1.0/24"</f>
+        <v>10.26.1.0/24</v>
+      </c>
+      <c r="Y30" s="23" t="str">
+        <f aca="false">IF(R30&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C30,$R$5:$R$92,R30)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q30)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F30&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="n">
@@ -19220,6 +20857,42 @@
         <f aca="false">IF(ISNA(MATCH(C31,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C31=A31,"OK",IF(INDEX($C$5:$C$92,MATCH(C31,Anlagen!$A$5:$A$92,0))&lt;&gt;C31,"Fehler: Standort hängt selbst an anderem Standort",IF(D31=A31,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D31,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D31,Anlagen!$A$5:$A$92,0))&lt;&gt;C31,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q31" s="23" t="str">
+        <f aca="false">Anlagen!AA31</f>
+        <v>EINT2</v>
+      </c>
+      <c r="R31" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB31&lt;&gt;"",Anlagen!AB31,COUNTIFS($C$5:$C$92,C31,$J$5:$J$92,"&lt;"&amp;J31)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="S31" s="23" t="n">
+        <f aca="false">1000+200*(R31-1)+1</f>
+        <v>1601</v>
+      </c>
+      <c r="T31" s="23" t="n">
+        <f aca="false">1000+200*(R31-1)+Anlagen!F31</f>
+        <v>1642</v>
+      </c>
+      <c r="U31" s="23" t="n">
+        <f aca="false">100+A31</f>
+        <v>127</v>
+      </c>
+      <c r="V31" s="23" t="n">
+        <f aca="false">200+A31</f>
+        <v>227</v>
+      </c>
+      <c r="W31" s="23" t="n">
+        <f aca="false">300+A31</f>
+        <v>327</v>
+      </c>
+      <c r="X31" s="23" t="str">
+        <f aca="false">"10."&amp;A31&amp;".1.0/24"</f>
+        <v>10.27.1.0/24</v>
+      </c>
+      <c r="Y31" s="23" t="str">
+        <f aca="false">IF(R31&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C31,$R$5:$R$92,R31)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q31)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F31&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="n">
@@ -19286,6 +20959,42 @@
         <f aca="false">IF(ISNA(MATCH(C32,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C32=A32,"OK",IF(INDEX($C$5:$C$92,MATCH(C32,Anlagen!$A$5:$A$92,0))&lt;&gt;C32,"Fehler: Standort hängt selbst an anderem Standort",IF(D32=A32,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D32,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D32,Anlagen!$A$5:$A$92,0))&lt;&gt;C32,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q32" s="23" t="str">
+        <f aca="false">Anlagen!AA32</f>
+        <v>ERDGL</v>
+      </c>
+      <c r="R32" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB32&lt;&gt;"",Anlagen!AB32,COUNTIFS($C$5:$C$92,C32,$J$5:$J$92,"&lt;"&amp;J32)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S32" s="23" t="n">
+        <f aca="false">1000+200*(R32-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T32" s="23" t="n">
+        <f aca="false">1000+200*(R32-1)+Anlagen!F32</f>
+        <v>1099</v>
+      </c>
+      <c r="U32" s="23" t="n">
+        <f aca="false">100+A32</f>
+        <v>128</v>
+      </c>
+      <c r="V32" s="23" t="n">
+        <f aca="false">200+A32</f>
+        <v>228</v>
+      </c>
+      <c r="W32" s="23" t="n">
+        <f aca="false">300+A32</f>
+        <v>328</v>
+      </c>
+      <c r="X32" s="23" t="str">
+        <f aca="false">"10."&amp;A32&amp;".1.0/24"</f>
+        <v>10.28.1.0/24</v>
+      </c>
+      <c r="Y32" s="23" t="str">
+        <f aca="false">IF(R32&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C32,$R$5:$R$92,R32)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q32)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F32&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="n">
@@ -19352,6 +21061,42 @@
         <f aca="false">IF(ISNA(MATCH(C33,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C33=A33,"OK",IF(INDEX($C$5:$C$92,MATCH(C33,Anlagen!$A$5:$A$92,0))&lt;&gt;C33,"Fehler: Standort hängt selbst an anderem Standort",IF(D33=A33,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D33,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D33,Anlagen!$A$5:$A$92,0))&lt;&gt;C33,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q33" s="23" t="str">
+        <f aca="false">Anlagen!AA33</f>
+        <v>ERNTE</v>
+      </c>
+      <c r="R33" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB33&lt;&gt;"",Anlagen!AB33,COUNTIFS($C$5:$C$92,C33,$J$5:$J$92,"&lt;"&amp;J33)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="S33" s="23" t="n">
+        <f aca="false">1000+200*(R33-1)+1</f>
+        <v>1401</v>
+      </c>
+      <c r="T33" s="23" t="n">
+        <f aca="false">1000+200*(R33-1)+Anlagen!F33</f>
+        <v>1492</v>
+      </c>
+      <c r="U33" s="23" t="n">
+        <f aca="false">100+A33</f>
+        <v>129</v>
+      </c>
+      <c r="V33" s="23" t="n">
+        <f aca="false">200+A33</f>
+        <v>229</v>
+      </c>
+      <c r="W33" s="23" t="n">
+        <f aca="false">300+A33</f>
+        <v>329</v>
+      </c>
+      <c r="X33" s="23" t="str">
+        <f aca="false">"10."&amp;A33&amp;".1.0/24"</f>
+        <v>10.29.1.0/24</v>
+      </c>
+      <c r="Y33" s="23" t="str">
+        <f aca="false">IF(R33&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C33,$R$5:$R$92,R33)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q33)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F33&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="n">
@@ -19418,6 +21163,42 @@
         <f aca="false">IF(ISNA(MATCH(C34,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C34=A34,"OK",IF(INDEX($C$5:$C$92,MATCH(C34,Anlagen!$A$5:$A$92,0))&lt;&gt;C34,"Fehler: Standort hängt selbst an anderem Standort",IF(D34=A34,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D34,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D34,Anlagen!$A$5:$A$92,0))&lt;&gt;C34,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q34" s="23" t="str">
+        <f aca="false">Anlagen!AA34</f>
+        <v>FEIER</v>
+      </c>
+      <c r="R34" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB34&lt;&gt;"",Anlagen!AB34,COUNTIFS($C$5:$C$92,C34,$J$5:$J$92,"&lt;"&amp;J34)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S34" s="23" t="n">
+        <f aca="false">1000+200*(R34-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T34" s="23" t="n">
+        <f aca="false">1000+200*(R34-1)+Anlagen!F34</f>
+        <v>1190</v>
+      </c>
+      <c r="U34" s="23" t="n">
+        <f aca="false">100+A34</f>
+        <v>130</v>
+      </c>
+      <c r="V34" s="23" t="n">
+        <f aca="false">200+A34</f>
+        <v>230</v>
+      </c>
+      <c r="W34" s="23" t="n">
+        <f aca="false">300+A34</f>
+        <v>330</v>
+      </c>
+      <c r="X34" s="23" t="str">
+        <f aca="false">"10."&amp;A34&amp;".1.0/24"</f>
+        <v>10.30.1.0/24</v>
+      </c>
+      <c r="Y34" s="23" t="str">
+        <f aca="false">IF(R34&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C34,$R$5:$R$92,R34)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q34)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F34&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="n">
@@ -19484,6 +21265,42 @@
         <f aca="false">IF(ISNA(MATCH(C35,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C35=A35,"OK",IF(INDEX($C$5:$C$92,MATCH(C35,Anlagen!$A$5:$A$92,0))&lt;&gt;C35,"Fehler: Standort hängt selbst an anderem Standort",IF(D35=A35,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D35,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D35,Anlagen!$A$5:$A$92,0))&lt;&gt;C35,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q35" s="23" t="str">
+        <f aca="false">Anlagen!AA35</f>
+        <v>FELD</v>
+      </c>
+      <c r="R35" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB35&lt;&gt;"",Anlagen!AB35,COUNTIFS($C$5:$C$92,C35,$J$5:$J$92,"&lt;"&amp;J35)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="S35" s="23" t="n">
+        <f aca="false">1000+200*(R35-1)+1</f>
+        <v>1601</v>
+      </c>
+      <c r="T35" s="23" t="n">
+        <f aca="false">1000+200*(R35-1)+Anlagen!F35</f>
+        <v>1668</v>
+      </c>
+      <c r="U35" s="23" t="n">
+        <f aca="false">100+A35</f>
+        <v>131</v>
+      </c>
+      <c r="V35" s="23" t="n">
+        <f aca="false">200+A35</f>
+        <v>231</v>
+      </c>
+      <c r="W35" s="23" t="n">
+        <f aca="false">300+A35</f>
+        <v>331</v>
+      </c>
+      <c r="X35" s="23" t="str">
+        <f aca="false">"10."&amp;A35&amp;".1.0/24"</f>
+        <v>10.31.1.0/24</v>
+      </c>
+      <c r="Y35" s="23" t="str">
+        <f aca="false">IF(R35&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C35,$R$5:$R$92,R35)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q35)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F35&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="n">
@@ -19550,6 +21367,42 @@
         <f aca="false">IF(ISNA(MATCH(C36,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C36=A36,"OK",IF(INDEX($C$5:$C$92,MATCH(C36,Anlagen!$A$5:$A$92,0))&lt;&gt;C36,"Fehler: Standort hängt selbst an anderem Standort",IF(D36=A36,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D36,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D36,Anlagen!$A$5:$A$92,0))&lt;&gt;C36,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q36" s="23" t="str">
+        <f aca="false">Anlagen!AA36</f>
+        <v>FINK</v>
+      </c>
+      <c r="R36" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB36&lt;&gt;"",Anlagen!AB36,COUNTIFS($C$5:$C$92,C36,$J$5:$J$92,"&lt;"&amp;J36)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="S36" s="23" t="n">
+        <f aca="false">1000+200*(R36-1)+1</f>
+        <v>1601</v>
+      </c>
+      <c r="T36" s="23" t="n">
+        <f aca="false">1000+200*(R36-1)+Anlagen!F36</f>
+        <v>1608</v>
+      </c>
+      <c r="U36" s="23" t="n">
+        <f aca="false">100+A36</f>
+        <v>132</v>
+      </c>
+      <c r="V36" s="23" t="n">
+        <f aca="false">200+A36</f>
+        <v>232</v>
+      </c>
+      <c r="W36" s="23" t="n">
+        <f aca="false">300+A36</f>
+        <v>332</v>
+      </c>
+      <c r="X36" s="23" t="str">
+        <f aca="false">"10."&amp;A36&amp;".1.0/24"</f>
+        <v>10.32.1.0/24</v>
+      </c>
+      <c r="Y36" s="23" t="str">
+        <f aca="false">IF(R36&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C36,$R$5:$R$92,R36)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q36)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F36&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="n">
@@ -19616,6 +21469,42 @@
         <f aca="false">IF(ISNA(MATCH(C37,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C37=A37,"OK",IF(INDEX($C$5:$C$92,MATCH(C37,Anlagen!$A$5:$A$92,0))&lt;&gt;C37,"Fehler: Standort hängt selbst an anderem Standort",IF(D37=A37,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D37,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D37,Anlagen!$A$5:$A$92,0))&lt;&gt;C37,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q37" s="23" t="str">
+        <f aca="false">Anlagen!AA37</f>
+        <v>FOHRD</v>
+      </c>
+      <c r="R37" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB37&lt;&gt;"",Anlagen!AB37,COUNTIFS($C$5:$C$92,C37,$J$5:$J$92,"&lt;"&amp;J37)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S37" s="23" t="n">
+        <f aca="false">1000+200*(R37-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T37" s="23" t="n">
+        <f aca="false">1000+200*(R37-1)+Anlagen!F37</f>
+        <v>1127</v>
+      </c>
+      <c r="U37" s="23" t="n">
+        <f aca="false">100+A37</f>
+        <v>133</v>
+      </c>
+      <c r="V37" s="23" t="n">
+        <f aca="false">200+A37</f>
+        <v>233</v>
+      </c>
+      <c r="W37" s="23" t="n">
+        <f aca="false">300+A37</f>
+        <v>333</v>
+      </c>
+      <c r="X37" s="23" t="str">
+        <f aca="false">"10."&amp;A37&amp;".1.0/24"</f>
+        <v>10.33.1.0/24</v>
+      </c>
+      <c r="Y37" s="23" t="str">
+        <f aca="false">IF(R37&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C37,$R$5:$R$92,R37)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q37)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F37&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="n">
@@ -19682,6 +21571,42 @@
         <f aca="false">IF(ISNA(MATCH(C38,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C38=A38,"OK",IF(INDEX($C$5:$C$92,MATCH(C38,Anlagen!$A$5:$A$92,0))&lt;&gt;C38,"Fehler: Standort hängt selbst an anderem Standort",IF(D38=A38,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D38,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D38,Anlagen!$A$5:$A$92,0))&lt;&gt;C38,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q38" s="23" t="str">
+        <f aca="false">Anlagen!AA38</f>
+        <v>FREIH</v>
+      </c>
+      <c r="R38" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB38&lt;&gt;"",Anlagen!AB38,COUNTIFS($C$5:$C$92,C38,$J$5:$J$92,"&lt;"&amp;J38)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="S38" s="23" t="n">
+        <f aca="false">1000+200*(R38-1)+1</f>
+        <v>1601</v>
+      </c>
+      <c r="T38" s="23" t="n">
+        <f aca="false">1000+200*(R38-1)+Anlagen!F38</f>
+        <v>1655</v>
+      </c>
+      <c r="U38" s="23" t="n">
+        <f aca="false">100+A38</f>
+        <v>134</v>
+      </c>
+      <c r="V38" s="23" t="n">
+        <f aca="false">200+A38</f>
+        <v>234</v>
+      </c>
+      <c r="W38" s="23" t="n">
+        <f aca="false">300+A38</f>
+        <v>334</v>
+      </c>
+      <c r="X38" s="23" t="str">
+        <f aca="false">"10."&amp;A38&amp;".1.0/24"</f>
+        <v>10.34.1.0/24</v>
+      </c>
+      <c r="Y38" s="23" t="str">
+        <f aca="false">IF(R38&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C38,$R$5:$R$92,R38)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q38)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F38&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="n">
@@ -19748,6 +21673,42 @@
         <f aca="false">IF(ISNA(MATCH(C39,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C39=A39,"OK",IF(INDEX($C$5:$C$92,MATCH(C39,Anlagen!$A$5:$A$92,0))&lt;&gt;C39,"Fehler: Standort hängt selbst an anderem Standort",IF(D39=A39,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D39,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D39,Anlagen!$A$5:$A$92,0))&lt;&gt;C39,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q39" s="23" t="str">
+        <f aca="false">Anlagen!AA39</f>
+        <v>FREIZ</v>
+      </c>
+      <c r="R39" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB39&lt;&gt;"",Anlagen!AB39,COUNTIFS($C$5:$C$92,C39,$J$5:$J$92,"&lt;"&amp;J39)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="S39" s="23" t="n">
+        <f aca="false">1000+200*(R39-1)+1</f>
+        <v>1801</v>
+      </c>
+      <c r="T39" s="23" t="n">
+        <f aca="false">1000+200*(R39-1)+Anlagen!F39</f>
+        <v>1863</v>
+      </c>
+      <c r="U39" s="23" t="n">
+        <f aca="false">100+A39</f>
+        <v>135</v>
+      </c>
+      <c r="V39" s="23" t="n">
+        <f aca="false">200+A39</f>
+        <v>235</v>
+      </c>
+      <c r="W39" s="23" t="n">
+        <f aca="false">300+A39</f>
+        <v>335</v>
+      </c>
+      <c r="X39" s="23" t="str">
+        <f aca="false">"10."&amp;A39&amp;".1.0/24"</f>
+        <v>10.35.1.0/24</v>
+      </c>
+      <c r="Y39" s="23" t="str">
+        <f aca="false">IF(R39&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C39,$R$5:$R$92,R39)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q39)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F39&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="n">
@@ -19814,6 +21775,42 @@
         <f aca="false">IF(ISNA(MATCH(C40,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C40=A40,"OK",IF(INDEX($C$5:$C$92,MATCH(C40,Anlagen!$A$5:$A$92,0))&lt;&gt;C40,"Fehler: Standort hängt selbst an anderem Standort",IF(D40=A40,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D40,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D40,Anlagen!$A$5:$A$92,0))&lt;&gt;C40,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q40" s="23" t="str">
+        <f aca="false">Anlagen!AA40</f>
+        <v>FRIED</v>
+      </c>
+      <c r="R40" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB40&lt;&gt;"",Anlagen!AB40,COUNTIFS($C$5:$C$92,C40,$J$5:$J$92,"&lt;"&amp;J40)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="S40" s="23" t="n">
+        <f aca="false">1000+200*(R40-1)+1</f>
+        <v>1801</v>
+      </c>
+      <c r="T40" s="23" t="n">
+        <f aca="false">1000+200*(R40-1)+Anlagen!F40</f>
+        <v>1864</v>
+      </c>
+      <c r="U40" s="23" t="n">
+        <f aca="false">100+A40</f>
+        <v>136</v>
+      </c>
+      <c r="V40" s="23" t="n">
+        <f aca="false">200+A40</f>
+        <v>236</v>
+      </c>
+      <c r="W40" s="23" t="n">
+        <f aca="false">300+A40</f>
+        <v>336</v>
+      </c>
+      <c r="X40" s="23" t="str">
+        <f aca="false">"10."&amp;A40&amp;".1.0/24"</f>
+        <v>10.36.1.0/24</v>
+      </c>
+      <c r="Y40" s="23" t="str">
+        <f aca="false">IF(R40&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C40,$R$5:$R$92,R40)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q40)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F40&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="n">
@@ -19880,6 +21877,42 @@
         <f aca="false">IF(ISNA(MATCH(C41,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C41=A41,"OK",IF(INDEX($C$5:$C$92,MATCH(C41,Anlagen!$A$5:$A$92,0))&lt;&gt;C41,"Fehler: Standort hängt selbst an anderem Standort",IF(D41=A41,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D41,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D41,Anlagen!$A$5:$A$92,0))&lt;&gt;C41,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q41" s="23" t="str">
+        <f aca="false">Anlagen!AA41</f>
+        <v>FRISA</v>
+      </c>
+      <c r="R41" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB41&lt;&gt;"",Anlagen!AB41,COUNTIFS($C$5:$C$92,C41,$J$5:$J$92,"&lt;"&amp;J41)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="S41" s="23" t="n">
+        <f aca="false">1000+200*(R41-1)+1</f>
+        <v>1401</v>
+      </c>
+      <c r="T41" s="23" t="n">
+        <f aca="false">1000+200*(R41-1)+Anlagen!F41</f>
+        <v>1419</v>
+      </c>
+      <c r="U41" s="23" t="n">
+        <f aca="false">100+A41</f>
+        <v>137</v>
+      </c>
+      <c r="V41" s="23" t="n">
+        <f aca="false">200+A41</f>
+        <v>237</v>
+      </c>
+      <c r="W41" s="23" t="n">
+        <f aca="false">300+A41</f>
+        <v>337</v>
+      </c>
+      <c r="X41" s="23" t="str">
+        <f aca="false">"10."&amp;A41&amp;".1.0/24"</f>
+        <v>10.37.1.0/24</v>
+      </c>
+      <c r="Y41" s="23" t="str">
+        <f aca="false">IF(R41&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C41,$R$5:$R$92,R41)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q41)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F41&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="23" t="n">
@@ -19946,6 +21979,42 @@
         <f aca="false">IF(ISNA(MATCH(C42,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C42=A42,"OK",IF(INDEX($C$5:$C$92,MATCH(C42,Anlagen!$A$5:$A$92,0))&lt;&gt;C42,"Fehler: Standort hängt selbst an anderem Standort",IF(D42=A42,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D42,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D42,Anlagen!$A$5:$A$92,0))&lt;&gt;C42,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q42" s="23" t="str">
+        <f aca="false">Anlagen!AA42</f>
+        <v>FROH</v>
+      </c>
+      <c r="R42" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB42&lt;&gt;"",Anlagen!AB42,COUNTIFS($C$5:$C$92,C42,$J$5:$J$92,"&lt;"&amp;J42)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="S42" s="23" t="n">
+        <f aca="false">1000+200*(R42-1)+1</f>
+        <v>1801</v>
+      </c>
+      <c r="T42" s="23" t="n">
+        <f aca="false">1000+200*(R42-1)+Anlagen!F42</f>
+        <v>1854</v>
+      </c>
+      <c r="U42" s="23" t="n">
+        <f aca="false">100+A42</f>
+        <v>138</v>
+      </c>
+      <c r="V42" s="23" t="n">
+        <f aca="false">200+A42</f>
+        <v>238</v>
+      </c>
+      <c r="W42" s="23" t="n">
+        <f aca="false">300+A42</f>
+        <v>338</v>
+      </c>
+      <c r="X42" s="23" t="str">
+        <f aca="false">"10."&amp;A42&amp;".1.0/24"</f>
+        <v>10.38.1.0/24</v>
+      </c>
+      <c r="Y42" s="23" t="str">
+        <f aca="false">IF(R42&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C42,$R$5:$R$92,R42)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q42)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F42&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="n">
@@ -20012,6 +22081,42 @@
         <f aca="false">IF(ISNA(MATCH(C43,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C43=A43,"OK",IF(INDEX($C$5:$C$92,MATCH(C43,Anlagen!$A$5:$A$92,0))&lt;&gt;C43,"Fehler: Standort hängt selbst an anderem Standort",IF(D43=A43,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D43,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D43,Anlagen!$A$5:$A$92,0))&lt;&gt;C43,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q43" s="23" t="str">
+        <f aca="false">Anlagen!AA43</f>
+        <v>BRAUE</v>
+      </c>
+      <c r="R43" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB43&lt;&gt;"",Anlagen!AB43,COUNTIFS($C$5:$C$92,C43,$J$5:$J$92,"&lt;"&amp;J43)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="S43" s="23" t="n">
+        <f aca="false">1000+200*(R43-1)+1</f>
+        <v>2401</v>
+      </c>
+      <c r="T43" s="23" t="n">
+        <f aca="false">1000+200*(R43-1)+Anlagen!F43</f>
+        <v>2469</v>
+      </c>
+      <c r="U43" s="23" t="n">
+        <f aca="false">100+A43</f>
+        <v>139</v>
+      </c>
+      <c r="V43" s="23" t="n">
+        <f aca="false">200+A43</f>
+        <v>239</v>
+      </c>
+      <c r="W43" s="23" t="n">
+        <f aca="false">300+A43</f>
+        <v>339</v>
+      </c>
+      <c r="X43" s="23" t="str">
+        <f aca="false">"10."&amp;A43&amp;".1.0/24"</f>
+        <v>10.39.1.0/24</v>
+      </c>
+      <c r="Y43" s="23" t="str">
+        <f aca="false">IF(R43&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C43,$R$5:$R$92,R43)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q43)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F43&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="n">
@@ -20078,6 +22183,42 @@
         <f aca="false">IF(ISNA(MATCH(C44,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C44=A44,"OK",IF(INDEX($C$5:$C$92,MATCH(C44,Anlagen!$A$5:$A$92,0))&lt;&gt;C44,"Fehler: Standort hängt selbst an anderem Standort",IF(D44=A44,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D44,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D44,Anlagen!$A$5:$A$92,0))&lt;&gt;C44,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q44" s="23" t="str">
+        <f aca="false">Anlagen!AA44</f>
+        <v>GLAUF</v>
+      </c>
+      <c r="R44" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB44&lt;&gt;"",Anlagen!AB44,COUNTIFS($C$5:$C$92,C44,$J$5:$J$92,"&lt;"&amp;J44)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="S44" s="23" t="n">
+        <f aca="false">1000+200*(R44-1)+1</f>
+        <v>1601</v>
+      </c>
+      <c r="T44" s="23" t="n">
+        <f aca="false">1000+200*(R44-1)+Anlagen!F44</f>
+        <v>1634</v>
+      </c>
+      <c r="U44" s="23" t="n">
+        <f aca="false">100+A44</f>
+        <v>140</v>
+      </c>
+      <c r="V44" s="23" t="n">
+        <f aca="false">200+A44</f>
+        <v>240</v>
+      </c>
+      <c r="W44" s="23" t="n">
+        <f aca="false">300+A44</f>
+        <v>340</v>
+      </c>
+      <c r="X44" s="23" t="str">
+        <f aca="false">"10."&amp;A44&amp;".1.0/24"</f>
+        <v>10.40.1.0/24</v>
+      </c>
+      <c r="Y44" s="23" t="str">
+        <f aca="false">IF(R44&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C44,$R$5:$R$92,R44)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q44)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F44&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="n">
@@ -20144,6 +22285,42 @@
         <f aca="false">IF(ISNA(MATCH(C45,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C45=A45,"OK",IF(INDEX($C$5:$C$92,MATCH(C45,Anlagen!$A$5:$A$92,0))&lt;&gt;C45,"Fehler: Standort hängt selbst an anderem Standort",IF(D45=A45,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D45,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D45,Anlagen!$A$5:$A$92,0))&lt;&gt;C45,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q45" s="23" t="str">
+        <f aca="false">Anlagen!AA45</f>
+        <v>GLWIN</v>
+      </c>
+      <c r="R45" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB45&lt;&gt;"",Anlagen!AB45,COUNTIFS($C$5:$C$92,C45,$J$5:$J$92,"&lt;"&amp;J45)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S45" s="23" t="n">
+        <f aca="false">1000+200*(R45-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T45" s="23" t="n">
+        <f aca="false">1000+200*(R45-1)+Anlagen!F45</f>
+        <v>1139</v>
+      </c>
+      <c r="U45" s="23" t="n">
+        <f aca="false">100+A45</f>
+        <v>141</v>
+      </c>
+      <c r="V45" s="23" t="n">
+        <f aca="false">200+A45</f>
+        <v>241</v>
+      </c>
+      <c r="W45" s="23" t="n">
+        <f aca="false">300+A45</f>
+        <v>341</v>
+      </c>
+      <c r="X45" s="23" t="str">
+        <f aca="false">"10."&amp;A45&amp;".1.0/24"</f>
+        <v>10.41.1.0/24</v>
+      </c>
+      <c r="Y45" s="23" t="str">
+        <f aca="false">IF(R45&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C45,$R$5:$R$92,R45)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q45)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F45&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="n">
@@ -20210,6 +22387,42 @@
         <f aca="false">IF(ISNA(MATCH(C46,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C46=A46,"OK",IF(INDEX($C$5:$C$92,MATCH(C46,Anlagen!$A$5:$A$92,0))&lt;&gt;C46,"Fehler: Standort hängt selbst an anderem Standort",IF(D46=A46,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D46,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D46,Anlagen!$A$5:$A$92,0))&lt;&gt;C46,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q46" s="23" t="str">
+        <f aca="false">Anlagen!AA46</f>
+        <v>GRECK</v>
+      </c>
+      <c r="R46" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB46&lt;&gt;"",Anlagen!AB46,COUNTIFS($C$5:$C$92,C46,$J$5:$J$92,"&lt;"&amp;J46)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="S46" s="23" t="n">
+        <f aca="false">1000+200*(R46-1)+1</f>
+        <v>2001</v>
+      </c>
+      <c r="T46" s="23" t="n">
+        <f aca="false">1000+200*(R46-1)+Anlagen!F46</f>
+        <v>2050</v>
+      </c>
+      <c r="U46" s="23" t="n">
+        <f aca="false">100+A46</f>
+        <v>142</v>
+      </c>
+      <c r="V46" s="23" t="n">
+        <f aca="false">200+A46</f>
+        <v>242</v>
+      </c>
+      <c r="W46" s="23" t="n">
+        <f aca="false">300+A46</f>
+        <v>342</v>
+      </c>
+      <c r="X46" s="23" t="str">
+        <f aca="false">"10."&amp;A46&amp;".1.0/24"</f>
+        <v>10.42.1.0/24</v>
+      </c>
+      <c r="Y46" s="23" t="str">
+        <f aca="false">IF(R46&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C46,$R$5:$R$92,R46)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q46)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F46&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="23" t="n">
@@ -20276,6 +22489,42 @@
         <f aca="false">IF(ISNA(MATCH(C47,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C47=A47,"OK",IF(INDEX($C$5:$C$92,MATCH(C47,Anlagen!$A$5:$A$92,0))&lt;&gt;C47,"Fehler: Standort hängt selbst an anderem Standort",IF(D47=A47,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D47,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D47,Anlagen!$A$5:$A$92,0))&lt;&gt;C47,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q47" s="23" t="str">
+        <f aca="false">Anlagen!AA47</f>
+        <v>GRKRZ</v>
+      </c>
+      <c r="R47" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB47&lt;&gt;"",Anlagen!AB47,COUNTIFS($C$5:$C$92,C47,$J$5:$J$92,"&lt;"&amp;J47)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="S47" s="23" t="n">
+        <f aca="false">1000+200*(R47-1)+1</f>
+        <v>1801</v>
+      </c>
+      <c r="T47" s="23" t="n">
+        <f aca="false">1000+200*(R47-1)+Anlagen!F47</f>
+        <v>1870</v>
+      </c>
+      <c r="U47" s="23" t="n">
+        <f aca="false">100+A47</f>
+        <v>143</v>
+      </c>
+      <c r="V47" s="23" t="n">
+        <f aca="false">200+A47</f>
+        <v>243</v>
+      </c>
+      <c r="W47" s="23" t="n">
+        <f aca="false">300+A47</f>
+        <v>343</v>
+      </c>
+      <c r="X47" s="23" t="str">
+        <f aca="false">"10."&amp;A47&amp;".1.0/24"</f>
+        <v>10.43.1.0/24</v>
+      </c>
+      <c r="Y47" s="23" t="str">
+        <f aca="false">IF(R47&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C47,$R$5:$R$92,R47)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q47)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F47&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="23" t="n">
@@ -20342,6 +22591,42 @@
         <f aca="false">IF(ISNA(MATCH(C48,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C48=A48,"OK",IF(INDEX($C$5:$C$92,MATCH(C48,Anlagen!$A$5:$A$92,0))&lt;&gt;C48,"Fehler: Standort hängt selbst an anderem Standort",IF(D48=A48,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D48,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D48,Anlagen!$A$5:$A$92,0))&lt;&gt;C48,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q48" s="23" t="str">
+        <f aca="false">Anlagen!AA48</f>
+        <v>GRHEI</v>
+      </c>
+      <c r="R48" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB48&lt;&gt;"",Anlagen!AB48,COUNTIFS($C$5:$C$92,C48,$J$5:$J$92,"&lt;"&amp;J48)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="S48" s="23" t="n">
+        <f aca="false">1000+200*(R48-1)+1</f>
+        <v>1601</v>
+      </c>
+      <c r="T48" s="23" t="n">
+        <f aca="false">1000+200*(R48-1)+Anlagen!F48</f>
+        <v>1623</v>
+      </c>
+      <c r="U48" s="23" t="n">
+        <f aca="false">100+A48</f>
+        <v>144</v>
+      </c>
+      <c r="V48" s="23" t="n">
+        <f aca="false">200+A48</f>
+        <v>244</v>
+      </c>
+      <c r="W48" s="23" t="n">
+        <f aca="false">300+A48</f>
+        <v>344</v>
+      </c>
+      <c r="X48" s="23" t="str">
+        <f aca="false">"10."&amp;A48&amp;".1.0/24"</f>
+        <v>10.44.1.0/24</v>
+      </c>
+      <c r="Y48" s="23" t="str">
+        <f aca="false">IF(R48&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C48,$R$5:$R$92,R48)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q48)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F48&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="n">
@@ -20408,6 +22693,42 @@
         <f aca="false">IF(ISNA(MATCH(C49,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C49=A49,"OK",IF(INDEX($C$5:$C$92,MATCH(C49,Anlagen!$A$5:$A$92,0))&lt;&gt;C49,"Fehler: Standort hängt selbst an anderem Standort",IF(D49=A49,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D49,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D49,Anlagen!$A$5:$A$92,0))&lt;&gt;C49,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q49" s="23" t="str">
+        <f aca="false">Anlagen!AA49</f>
+        <v>GUTWE</v>
+      </c>
+      <c r="R49" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB49&lt;&gt;"",Anlagen!AB49,COUNTIFS($C$5:$C$92,C49,$J$5:$J$92,"&lt;"&amp;J49)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="S49" s="23" t="n">
+        <f aca="false">1000+200*(R49-1)+1</f>
+        <v>1601</v>
+      </c>
+      <c r="T49" s="23" t="n">
+        <f aca="false">1000+200*(R49-1)+Anlagen!F49</f>
+        <v>1617</v>
+      </c>
+      <c r="U49" s="23" t="n">
+        <f aca="false">100+A49</f>
+        <v>145</v>
+      </c>
+      <c r="V49" s="23" t="n">
+        <f aca="false">200+A49</f>
+        <v>245</v>
+      </c>
+      <c r="W49" s="23" t="n">
+        <f aca="false">300+A49</f>
+        <v>345</v>
+      </c>
+      <c r="X49" s="23" t="str">
+        <f aca="false">"10."&amp;A49&amp;".1.0/24"</f>
+        <v>10.45.1.0/24</v>
+      </c>
+      <c r="Y49" s="23" t="str">
+        <f aca="false">IF(R49&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C49,$R$5:$R$92,R49)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q49)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F49&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="23" t="n">
@@ -20474,6 +22795,42 @@
         <f aca="false">IF(ISNA(MATCH(C50,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C50=A50,"OK",IF(INDEX($C$5:$C$92,MATCH(C50,Anlagen!$A$5:$A$92,0))&lt;&gt;C50,"Fehler: Standort hängt selbst an anderem Standort",IF(D50=A50,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D50,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D50,Anlagen!$A$5:$A$92,0))&lt;&gt;C50,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q50" s="23" t="str">
+        <f aca="false">Anlagen!AA50</f>
+        <v>HANDW</v>
+      </c>
+      <c r="R50" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB50&lt;&gt;"",Anlagen!AB50,COUNTIFS($C$5:$C$92,C50,$J$5:$J$92,"&lt;"&amp;J50)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="S50" s="23" t="n">
+        <f aca="false">1000+200*(R50-1)+1</f>
+        <v>2001</v>
+      </c>
+      <c r="T50" s="23" t="n">
+        <f aca="false">1000+200*(R50-1)+Anlagen!F50</f>
+        <v>2036</v>
+      </c>
+      <c r="U50" s="23" t="n">
+        <f aca="false">100+A50</f>
+        <v>146</v>
+      </c>
+      <c r="V50" s="23" t="n">
+        <f aca="false">200+A50</f>
+        <v>246</v>
+      </c>
+      <c r="W50" s="23" t="n">
+        <f aca="false">300+A50</f>
+        <v>346</v>
+      </c>
+      <c r="X50" s="23" t="str">
+        <f aca="false">"10."&amp;A50&amp;".1.0/24"</f>
+        <v>10.46.1.0/24</v>
+      </c>
+      <c r="Y50" s="23" t="str">
+        <f aca="false">IF(R50&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C50,$R$5:$R$92,R50)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q50)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F50&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="n">
@@ -20540,6 +22897,42 @@
         <f aca="false">IF(ISNA(MATCH(C51,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C51=A51,"OK",IF(INDEX($C$5:$C$92,MATCH(C51,Anlagen!$A$5:$A$92,0))&lt;&gt;C51,"Fehler: Standort hängt selbst an anderem Standort",IF(D51=A51,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D51,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D51,Anlagen!$A$5:$A$92,0))&lt;&gt;C51,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q51" s="23" t="str">
+        <f aca="false">Anlagen!AA51</f>
+        <v>HARMO</v>
+      </c>
+      <c r="R51" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB51&lt;&gt;"",Anlagen!AB51,COUNTIFS($C$5:$C$92,C51,$J$5:$J$92,"&lt;"&amp;J51)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="S51" s="23" t="n">
+        <f aca="false">1000+200*(R51-1)+1</f>
+        <v>1801</v>
+      </c>
+      <c r="T51" s="23" t="n">
+        <f aca="false">1000+200*(R51-1)+Anlagen!F51</f>
+        <v>1860</v>
+      </c>
+      <c r="U51" s="23" t="n">
+        <f aca="false">100+A51</f>
+        <v>147</v>
+      </c>
+      <c r="V51" s="23" t="n">
+        <f aca="false">200+A51</f>
+        <v>247</v>
+      </c>
+      <c r="W51" s="23" t="n">
+        <f aca="false">300+A51</f>
+        <v>347</v>
+      </c>
+      <c r="X51" s="23" t="str">
+        <f aca="false">"10."&amp;A51&amp;".1.0/24"</f>
+        <v>10.47.1.0/24</v>
+      </c>
+      <c r="Y51" s="23" t="str">
+        <f aca="false">IF(R51&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C51,$R$5:$R$92,R51)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q51)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F51&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="23" t="n">
@@ -20606,6 +22999,42 @@
         <f aca="false">IF(ISNA(MATCH(C52,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C52=A52,"OK",IF(INDEX($C$5:$C$92,MATCH(C52,Anlagen!$A$5:$A$92,0))&lt;&gt;C52,"Fehler: Standort hängt selbst an anderem Standort",IF(D52=A52,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D52,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D52,Anlagen!$A$5:$A$92,0))&lt;&gt;C52,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q52" s="23" t="str">
+        <f aca="false">Anlagen!AA52</f>
+        <v>HEIDE</v>
+      </c>
+      <c r="R52" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB52&lt;&gt;"",Anlagen!AB52,COUNTIFS($C$5:$C$92,C52,$J$5:$J$92,"&lt;"&amp;J52)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S52" s="23" t="n">
+        <f aca="false">1000+200*(R52-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T52" s="23" t="n">
+        <f aca="false">1000+200*(R52-1)+Anlagen!F52</f>
+        <v>1034</v>
+      </c>
+      <c r="U52" s="23" t="n">
+        <f aca="false">100+A52</f>
+        <v>148</v>
+      </c>
+      <c r="V52" s="23" t="n">
+        <f aca="false">200+A52</f>
+        <v>248</v>
+      </c>
+      <c r="W52" s="23" t="n">
+        <f aca="false">300+A52</f>
+        <v>348</v>
+      </c>
+      <c r="X52" s="23" t="str">
+        <f aca="false">"10."&amp;A52&amp;".1.0/24"</f>
+        <v>10.48.1.0/24</v>
+      </c>
+      <c r="Y52" s="23" t="str">
+        <f aca="false">IF(R52&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C52,$R$5:$R$92,R52)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q52)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F52&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="23" t="n">
@@ -20672,6 +23101,42 @@
         <f aca="false">IF(ISNA(MATCH(C53,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C53=A53,"OK",IF(INDEX($C$5:$C$92,MATCH(C53,Anlagen!$A$5:$A$92,0))&lt;&gt;C53,"Fehler: Standort hängt selbst an anderem Standort",IF(D53=A53,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D53,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D53,Anlagen!$A$5:$A$92,0))&lt;&gt;C53,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q53" s="23" t="str">
+        <f aca="false">Anlagen!AA53</f>
+        <v>HELGO</v>
+      </c>
+      <c r="R53" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB53&lt;&gt;"",Anlagen!AB53,COUNTIFS($C$5:$C$92,C53,$J$5:$J$92,"&lt;"&amp;J53)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S53" s="23" t="n">
+        <f aca="false">1000+200*(R53-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T53" s="23" t="n">
+        <f aca="false">1000+200*(R53-1)+Anlagen!F53</f>
+        <v>1110</v>
+      </c>
+      <c r="U53" s="23" t="n">
+        <f aca="false">100+A53</f>
+        <v>149</v>
+      </c>
+      <c r="V53" s="23" t="n">
+        <f aca="false">200+A53</f>
+        <v>249</v>
+      </c>
+      <c r="W53" s="23" t="n">
+        <f aca="false">300+A53</f>
+        <v>349</v>
+      </c>
+      <c r="X53" s="23" t="str">
+        <f aca="false">"10."&amp;A53&amp;".1.0/24"</f>
+        <v>10.49.1.0/24</v>
+      </c>
+      <c r="Y53" s="23" t="str">
+        <f aca="false">IF(R53&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C53,$R$5:$R$92,R53)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q53)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F53&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="n">
@@ -20738,6 +23203,42 @@
         <f aca="false">IF(ISNA(MATCH(C54,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C54=A54,"OK",IF(INDEX($C$5:$C$92,MATCH(C54,Anlagen!$A$5:$A$92,0))&lt;&gt;C54,"Fehler: Standort hängt selbst an anderem Standort",IF(D54=A54,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D54,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D54,Anlagen!$A$5:$A$92,0))&lt;&gt;C54,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q54" s="23" t="str">
+        <f aca="false">Anlagen!AA54</f>
+        <v>HOFFN</v>
+      </c>
+      <c r="R54" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB54&lt;&gt;"",Anlagen!AB54,COUNTIFS($C$5:$C$92,C54,$J$5:$J$92,"&lt;"&amp;J54)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="S54" s="23" t="n">
+        <f aca="false">1000+200*(R54-1)+1</f>
+        <v>2001</v>
+      </c>
+      <c r="T54" s="23" t="n">
+        <f aca="false">1000+200*(R54-1)+Anlagen!F54</f>
+        <v>2007</v>
+      </c>
+      <c r="U54" s="23" t="n">
+        <f aca="false">100+A54</f>
+        <v>150</v>
+      </c>
+      <c r="V54" s="23" t="n">
+        <f aca="false">200+A54</f>
+        <v>250</v>
+      </c>
+      <c r="W54" s="23" t="n">
+        <f aca="false">300+A54</f>
+        <v>350</v>
+      </c>
+      <c r="X54" s="23" t="str">
+        <f aca="false">"10."&amp;A54&amp;".1.0/24"</f>
+        <v>10.50.1.0/24</v>
+      </c>
+      <c r="Y54" s="23" t="str">
+        <f aca="false">IF(R54&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C54,$R$5:$R$92,R54)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q54)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F54&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="23" t="n">
@@ -20804,6 +23305,42 @@
         <f aca="false">IF(ISNA(MATCH(C55,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C55=A55,"OK",IF(INDEX($C$5:$C$92,MATCH(C55,Anlagen!$A$5:$A$92,0))&lt;&gt;C55,"Fehler: Standort hängt selbst an anderem Standort",IF(D55=A55,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D55,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D55,Anlagen!$A$5:$A$92,0))&lt;&gt;C55,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q55" s="23" t="str">
+        <f aca="false">Anlagen!AA55</f>
+        <v>HOLL</v>
+      </c>
+      <c r="R55" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB55&lt;&gt;"",Anlagen!AB55,COUNTIFS($C$5:$C$92,C55,$J$5:$J$92,"&lt;"&amp;J55)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="S55" s="23" t="n">
+        <f aca="false">1000+200*(R55-1)+1</f>
+        <v>1801</v>
+      </c>
+      <c r="T55" s="23" t="n">
+        <f aca="false">1000+200*(R55-1)+Anlagen!F55</f>
+        <v>1809</v>
+      </c>
+      <c r="U55" s="23" t="n">
+        <f aca="false">100+A55</f>
+        <v>151</v>
+      </c>
+      <c r="V55" s="23" t="n">
+        <f aca="false">200+A55</f>
+        <v>251</v>
+      </c>
+      <c r="W55" s="23" t="n">
+        <f aca="false">300+A55</f>
+        <v>351</v>
+      </c>
+      <c r="X55" s="23" t="str">
+        <f aca="false">"10."&amp;A55&amp;".1.0/24"</f>
+        <v>10.51.1.0/24</v>
+      </c>
+      <c r="Y55" s="23" t="str">
+        <f aca="false">IF(R55&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C55,$R$5:$R$92,R55)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q55)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F55&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="23" t="n">
@@ -20870,6 +23407,42 @@
         <f aca="false">IF(ISNA(MATCH(C56,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C56=A56,"OK",IF(INDEX($C$5:$C$92,MATCH(C56,Anlagen!$A$5:$A$92,0))&lt;&gt;C56,"Fehler: Standort hängt selbst an anderem Standort",IF(D56=A56,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D56,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D56,Anlagen!$A$5:$A$92,0))&lt;&gt;C56,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q56" s="23" t="str">
+        <f aca="false">Anlagen!AA56</f>
+        <v>MBR1</v>
+      </c>
+      <c r="R56" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB56&lt;&gt;"",Anlagen!AB56,COUNTIFS($C$5:$C$92,C56,$J$5:$J$92,"&lt;"&amp;J56)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S56" s="23" t="n">
+        <f aca="false">1000+200*(R56-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T56" s="23" t="n">
+        <f aca="false">1000+200*(R56-1)+Anlagen!F56</f>
+        <v>1233</v>
+      </c>
+      <c r="U56" s="23" t="n">
+        <f aca="false">100+A56</f>
+        <v>152</v>
+      </c>
+      <c r="V56" s="23" t="n">
+        <f aca="false">200+A56</f>
+        <v>252</v>
+      </c>
+      <c r="W56" s="23" t="n">
+        <f aca="false">300+A56</f>
+        <v>352</v>
+      </c>
+      <c r="X56" s="23" t="str">
+        <f aca="false">"10."&amp;A56&amp;".1.0/24"</f>
+        <v>10.52.1.0/24</v>
+      </c>
+      <c r="Y56" s="23" t="str">
+        <f aca="false">IF(R56&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C56,$R$5:$R$92,R56)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q56)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F56&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="23" t="n">
@@ -20936,6 +23509,42 @@
         <f aca="false">IF(ISNA(MATCH(C57,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C57=A57,"OK",IF(INDEX($C$5:$C$92,MATCH(C57,Anlagen!$A$5:$A$92,0))&lt;&gt;C57,"Fehler: Standort hängt selbst an anderem Standort",IF(D57=A57,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D57,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D57,Anlagen!$A$5:$A$92,0))&lt;&gt;C57,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q57" s="23" t="str">
+        <f aca="false">Anlagen!AA57</f>
+        <v>MBR2</v>
+      </c>
+      <c r="R57" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB57&lt;&gt;"",Anlagen!AB57,COUNTIFS($C$5:$C$92,C57,$J$5:$J$92,"&lt;"&amp;J57)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="S57" s="23" t="n">
+        <f aca="false">1000+200*(R57-1)+1</f>
+        <v>1401</v>
+      </c>
+      <c r="T57" s="23" t="n">
+        <f aca="false">1000+200*(R57-1)+Anlagen!F57</f>
+        <v>1447</v>
+      </c>
+      <c r="U57" s="23" t="n">
+        <f aca="false">100+A57</f>
+        <v>153</v>
+      </c>
+      <c r="V57" s="23" t="n">
+        <f aca="false">200+A57</f>
+        <v>253</v>
+      </c>
+      <c r="W57" s="23" t="n">
+        <f aca="false">300+A57</f>
+        <v>353</v>
+      </c>
+      <c r="X57" s="23" t="str">
+        <f aca="false">"10."&amp;A57&amp;".1.0/24"</f>
+        <v>10.53.1.0/24</v>
+      </c>
+      <c r="Y57" s="23" t="str">
+        <f aca="false">IF(R57&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C57,$R$5:$R$92,R57)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q57)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F57&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="23" t="n">
@@ -21002,6 +23611,42 @@
         <f aca="false">IF(ISNA(MATCH(C58,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C58=A58,"OK",IF(INDEX($C$5:$C$92,MATCH(C58,Anlagen!$A$5:$A$92,0))&lt;&gt;C58,"Fehler: Standort hängt selbst an anderem Standort",IF(D58=A58,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D58,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D58,Anlagen!$A$5:$A$92,0))&lt;&gt;C58,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q58" s="23" t="str">
+        <f aca="false">Anlagen!AA58</f>
+        <v>IMMER</v>
+      </c>
+      <c r="R58" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB58&lt;&gt;"",Anlagen!AB58,COUNTIFS($C$5:$C$92,C58,$J$5:$J$92,"&lt;"&amp;J58)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="S58" s="23" t="n">
+        <f aca="false">1000+200*(R58-1)+1</f>
+        <v>1801</v>
+      </c>
+      <c r="T58" s="23" t="n">
+        <f aca="false">1000+200*(R58-1)+Anlagen!F58</f>
+        <v>1857</v>
+      </c>
+      <c r="U58" s="23" t="n">
+        <f aca="false">100+A58</f>
+        <v>154</v>
+      </c>
+      <c r="V58" s="23" t="n">
+        <f aca="false">200+A58</f>
+        <v>254</v>
+      </c>
+      <c r="W58" s="23" t="n">
+        <f aca="false">300+A58</f>
+        <v>354</v>
+      </c>
+      <c r="X58" s="23" t="str">
+        <f aca="false">"10."&amp;A58&amp;".1.0/24"</f>
+        <v>10.54.1.0/24</v>
+      </c>
+      <c r="Y58" s="23" t="str">
+        <f aca="false">IF(R58&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C58,$R$5:$R$92,R58)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q58)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F58&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="23" t="n">
@@ -21068,6 +23713,42 @@
         <f aca="false">IF(ISNA(MATCH(C59,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C59=A59,"OK",IF(INDEX($C$5:$C$92,MATCH(C59,Anlagen!$A$5:$A$92,0))&lt;&gt;C59,"Fehler: Standort hängt selbst an anderem Standort",IF(D59=A59,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D59,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D59,Anlagen!$A$5:$A$92,0))&lt;&gt;C59,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q59" s="23" t="str">
+        <f aca="false">Anlagen!AA59</f>
+        <v>JAKWE</v>
+      </c>
+      <c r="R59" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB59&lt;&gt;"",Anlagen!AB59,COUNTIFS($C$5:$C$92,C59,$J$5:$J$92,"&lt;"&amp;J59)+1)</f>
+        <v>7</v>
+      </c>
+      <c r="S59" s="23" t="n">
+        <f aca="false">1000+200*(R59-1)+1</f>
+        <v>2201</v>
+      </c>
+      <c r="T59" s="23" t="n">
+        <f aca="false">1000+200*(R59-1)+Anlagen!F59</f>
+        <v>2249</v>
+      </c>
+      <c r="U59" s="23" t="n">
+        <f aca="false">100+A59</f>
+        <v>155</v>
+      </c>
+      <c r="V59" s="23" t="n">
+        <f aca="false">200+A59</f>
+        <v>255</v>
+      </c>
+      <c r="W59" s="23" t="n">
+        <f aca="false">300+A59</f>
+        <v>355</v>
+      </c>
+      <c r="X59" s="23" t="str">
+        <f aca="false">"10."&amp;A59&amp;".1.0/24"</f>
+        <v>10.55.1.0/24</v>
+      </c>
+      <c r="Y59" s="23" t="str">
+        <f aca="false">IF(R59&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C59,$R$5:$R$92,R59)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q59)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F59&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="23" t="n">
@@ -21134,6 +23815,42 @@
         <f aca="false">IF(ISNA(MATCH(C60,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C60=A60,"OK",IF(INDEX($C$5:$C$92,MATCH(C60,Anlagen!$A$5:$A$92,0))&lt;&gt;C60,"Fehler: Standort hängt selbst an anderem Standort",IF(D60=A60,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D60,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D60,Anlagen!$A$5:$A$92,0))&lt;&gt;C60,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q60" s="23" t="str">
+        <f aca="false">Anlagen!AA60</f>
+        <v>KAMM</v>
+      </c>
+      <c r="R60" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB60&lt;&gt;"",Anlagen!AB60,COUNTIFS($C$5:$C$92,C60,$J$5:$J$92,"&lt;"&amp;J60)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S60" s="23" t="n">
+        <f aca="false">1000+200*(R60-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T60" s="23" t="n">
+        <f aca="false">1000+200*(R60-1)+Anlagen!F60</f>
+        <v>1028</v>
+      </c>
+      <c r="U60" s="23" t="n">
+        <f aca="false">100+A60</f>
+        <v>156</v>
+      </c>
+      <c r="V60" s="23" t="n">
+        <f aca="false">200+A60</f>
+        <v>256</v>
+      </c>
+      <c r="W60" s="23" t="n">
+        <f aca="false">300+A60</f>
+        <v>356</v>
+      </c>
+      <c r="X60" s="23" t="str">
+        <f aca="false">"10."&amp;A60&amp;".1.0/24"</f>
+        <v>10.56.1.0/24</v>
+      </c>
+      <c r="Y60" s="23" t="str">
+        <f aca="false">IF(R60&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C60,$R$5:$R$92,R60)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q60)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F60&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="23" t="n">
@@ -21200,6 +23917,42 @@
         <f aca="false">IF(ISNA(MATCH(C61,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C61=A61,"OK",IF(INDEX($C$5:$C$92,MATCH(C61,Anlagen!$A$5:$A$92,0))&lt;&gt;C61,"Fehler: Standort hängt selbst an anderem Standort",IF(D61=A61,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D61,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D61,Anlagen!$A$5:$A$92,0))&lt;&gt;C61,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q61" s="23" t="str">
+        <f aca="false">Anlagen!AA61</f>
+        <v>KMDOR</v>
+      </c>
+      <c r="R61" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB61&lt;&gt;"",Anlagen!AB61,COUNTIFS($C$5:$C$92,C61,$J$5:$J$92,"&lt;"&amp;J61)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S61" s="23" t="n">
+        <f aca="false">1000+200*(R61-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T61" s="23" t="n">
+        <f aca="false">1000+200*(R61-1)+Anlagen!F61</f>
+        <v>1048</v>
+      </c>
+      <c r="U61" s="23" t="n">
+        <f aca="false">100+A61</f>
+        <v>157</v>
+      </c>
+      <c r="V61" s="23" t="n">
+        <f aca="false">200+A61</f>
+        <v>257</v>
+      </c>
+      <c r="W61" s="23" t="n">
+        <f aca="false">300+A61</f>
+        <v>357</v>
+      </c>
+      <c r="X61" s="23" t="str">
+        <f aca="false">"10."&amp;A61&amp;".1.0/24"</f>
+        <v>10.57.1.0/24</v>
+      </c>
+      <c r="Y61" s="23" t="str">
+        <f aca="false">IF(R61&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C61,$R$5:$R$92,R61)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q61)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F61&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="23" t="n">
@@ -21266,6 +24019,42 @@
         <f aca="false">IF(ISNA(MATCH(C62,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C62=A62,"OK",IF(INDEX($C$5:$C$92,MATCH(C62,Anlagen!$A$5:$A$92,0))&lt;&gt;C62,"Fehler: Standort hängt selbst an anderem Standort",IF(D62=A62,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D62,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D62,Anlagen!$A$5:$A$92,0))&lt;&gt;C62,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q62" s="23" t="str">
+        <f aca="false">Anlagen!AA62</f>
+        <v>KMLEH</v>
+      </c>
+      <c r="R62" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB62&lt;&gt;"",Anlagen!AB62,COUNTIFS($C$5:$C$92,C62,$J$5:$J$92,"&lt;"&amp;J62)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S62" s="23" t="n">
+        <f aca="false">1000+200*(R62-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T62" s="23" t="n">
+        <f aca="false">1000+200*(R62-1)+Anlagen!F62</f>
+        <v>1238</v>
+      </c>
+      <c r="U62" s="23" t="n">
+        <f aca="false">100+A62</f>
+        <v>158</v>
+      </c>
+      <c r="V62" s="23" t="n">
+        <f aca="false">200+A62</f>
+        <v>258</v>
+      </c>
+      <c r="W62" s="23" t="n">
+        <f aca="false">300+A62</f>
+        <v>358</v>
+      </c>
+      <c r="X62" s="23" t="str">
+        <f aca="false">"10."&amp;A62&amp;".1.0/24"</f>
+        <v>10.58.1.0/24</v>
+      </c>
+      <c r="Y62" s="23" t="str">
+        <f aca="false">IF(R62&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C62,$R$5:$R$92,R62)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q62)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F62&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="23" t="n">
@@ -21332,6 +24121,42 @@
         <f aca="false">IF(ISNA(MATCH(C63,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C63=A63,"OK",IF(INDEX($C$5:$C$92,MATCH(C63,Anlagen!$A$5:$A$92,0))&lt;&gt;C63,"Fehler: Standort hängt selbst an anderem Standort",IF(D63=A63,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D63,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D63,Anlagen!$A$5:$A$92,0))&lt;&gt;C63,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q63" s="23" t="str">
+        <f aca="false">Anlagen!AA63</f>
+        <v>KMOST</v>
+      </c>
+      <c r="R63" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB63&lt;&gt;"",Anlagen!AB63,COUNTIFS($C$5:$C$92,C63,$J$5:$J$92,"&lt;"&amp;J63)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S63" s="23" t="n">
+        <f aca="false">1000+200*(R63-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T63" s="23" t="n">
+        <f aca="false">1000+200*(R63-1)+Anlagen!F63</f>
+        <v>1066</v>
+      </c>
+      <c r="U63" s="23" t="n">
+        <f aca="false">100+A63</f>
+        <v>159</v>
+      </c>
+      <c r="V63" s="23" t="n">
+        <f aca="false">200+A63</f>
+        <v>259</v>
+      </c>
+      <c r="W63" s="23" t="n">
+        <f aca="false">300+A63</f>
+        <v>359</v>
+      </c>
+      <c r="X63" s="23" t="str">
+        <f aca="false">"10."&amp;A63&amp;".1.0/24"</f>
+        <v>10.59.1.0/24</v>
+      </c>
+      <c r="Y63" s="23" t="str">
+        <f aca="false">IF(R63&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C63,$R$5:$R$92,R63)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q63)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F63&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="23" t="n">
@@ -21398,6 +24223,42 @@
         <f aca="false">IF(ISNA(MATCH(C64,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C64=A64,"OK",IF(INDEX($C$5:$C$92,MATCH(C64,Anlagen!$A$5:$A$92,0))&lt;&gt;C64,"Fehler: Standort hängt selbst an anderem Standort",IF(D64=A64,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D64,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D64,Anlagen!$A$5:$A$92,0))&lt;&gt;C64,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q64" s="23" t="str">
+        <f aca="false">Anlagen!AA64</f>
+        <v>LANDH</v>
+      </c>
+      <c r="R64" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB64&lt;&gt;"",Anlagen!AB64,COUNTIFS($C$5:$C$92,C64,$J$5:$J$92,"&lt;"&amp;J64)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="S64" s="23" t="n">
+        <f aca="false">1000+200*(R64-1)+1</f>
+        <v>2001</v>
+      </c>
+      <c r="T64" s="23" t="n">
+        <f aca="false">1000+200*(R64-1)+Anlagen!F64</f>
+        <v>2109</v>
+      </c>
+      <c r="U64" s="23" t="n">
+        <f aca="false">100+A64</f>
+        <v>160</v>
+      </c>
+      <c r="V64" s="23" t="n">
+        <f aca="false">200+A64</f>
+        <v>260</v>
+      </c>
+      <c r="W64" s="23" t="n">
+        <f aca="false">300+A64</f>
+        <v>360</v>
+      </c>
+      <c r="X64" s="23" t="str">
+        <f aca="false">"10."&amp;A64&amp;".1.0/24"</f>
+        <v>10.60.1.0/24</v>
+      </c>
+      <c r="Y64" s="23" t="str">
+        <f aca="false">IF(R64&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C64,$R$5:$R$92,R64)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q64)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F64&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="23" t="n">
@@ -21464,6 +24325,42 @@
         <f aca="false">IF(ISNA(MATCH(C65,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C65=A65,"OK",IF(INDEX($C$5:$C$92,MATCH(C65,Anlagen!$A$5:$A$92,0))&lt;&gt;C65,"Fehler: Standort hängt selbst an anderem Standort",IF(D65=A65,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D65,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D65,Anlagen!$A$5:$A$92,0))&lt;&gt;C65,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q65" s="23" t="str">
+        <f aca="false">Anlagen!AA65</f>
+        <v>MAERK</v>
+      </c>
+      <c r="R65" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB65&lt;&gt;"",Anlagen!AB65,COUNTIFS($C$5:$C$92,C65,$J$5:$J$92,"&lt;"&amp;J65)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="S65" s="23" t="n">
+        <f aca="false">1000+200*(R65-1)+1</f>
+        <v>1601</v>
+      </c>
+      <c r="T65" s="23" t="n">
+        <f aca="false">1000+200*(R65-1)+Anlagen!F65</f>
+        <v>1673</v>
+      </c>
+      <c r="U65" s="23" t="n">
+        <f aca="false">100+A65</f>
+        <v>161</v>
+      </c>
+      <c r="V65" s="23" t="n">
+        <f aca="false">200+A65</f>
+        <v>261</v>
+      </c>
+      <c r="W65" s="23" t="n">
+        <f aca="false">300+A65</f>
+        <v>361</v>
+      </c>
+      <c r="X65" s="23" t="str">
+        <f aca="false">"10."&amp;A65&amp;".1.0/24"</f>
+        <v>10.61.1.0/24</v>
+      </c>
+      <c r="Y65" s="23" t="str">
+        <f aca="false">IF(R65&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C65,$R$5:$R$92,R65)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q65)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F65&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="23" t="n">
@@ -21530,6 +24427,42 @@
         <f aca="false">IF(ISNA(MATCH(C66,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C66=A66,"OK",IF(INDEX($C$5:$C$92,MATCH(C66,Anlagen!$A$5:$A$92,0))&lt;&gt;C66,"Fehler: Standort hängt selbst an anderem Standort",IF(D66=A66,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D66,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D66,Anlagen!$A$5:$A$92,0))&lt;&gt;C66,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q66" s="23" t="str">
+        <f aca="false">Anlagen!AA66</f>
+        <v>MITTW</v>
+      </c>
+      <c r="R66" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB66&lt;&gt;"",Anlagen!AB66,COUNTIFS($C$5:$C$92,C66,$J$5:$J$92,"&lt;"&amp;J66)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S66" s="23" t="n">
+        <f aca="false">1000+200*(R66-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T66" s="23" t="n">
+        <f aca="false">1000+200*(R66-1)+Anlagen!F66</f>
+        <v>1236</v>
+      </c>
+      <c r="U66" s="23" t="n">
+        <f aca="false">100+A66</f>
+        <v>162</v>
+      </c>
+      <c r="V66" s="23" t="n">
+        <f aca="false">200+A66</f>
+        <v>262</v>
+      </c>
+      <c r="W66" s="23" t="n">
+        <f aca="false">300+A66</f>
+        <v>362</v>
+      </c>
+      <c r="X66" s="23" t="str">
+        <f aca="false">"10."&amp;A66&amp;".1.0/24"</f>
+        <v>10.62.1.0/24</v>
+      </c>
+      <c r="Y66" s="23" t="str">
+        <f aca="false">IF(R66&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C66,$R$5:$R$92,R66)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q66)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F66&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="23" t="n">
@@ -21596,6 +24529,42 @@
         <f aca="false">IF(ISNA(MATCH(C67,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C67=A67,"OK",IF(INDEX($C$5:$C$92,MATCH(C67,Anlagen!$A$5:$A$92,0))&lt;&gt;C67,"Fehler: Standort hängt selbst an anderem Standort",IF(D67=A67,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D67,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D67,Anlagen!$A$5:$A$92,0))&lt;&gt;C67,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q67" s="23" t="str">
+        <f aca="false">Anlagen!AA67</f>
+        <v>MORGE</v>
+      </c>
+      <c r="R67" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB67&lt;&gt;"",Anlagen!AB67,COUNTIFS($C$5:$C$92,C67,$J$5:$J$92,"&lt;"&amp;J67)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="S67" s="23" t="n">
+        <f aca="false">1000+200*(R67-1)+1</f>
+        <v>1801</v>
+      </c>
+      <c r="T67" s="23" t="n">
+        <f aca="false">1000+200*(R67-1)+Anlagen!F67</f>
+        <v>1825</v>
+      </c>
+      <c r="U67" s="23" t="n">
+        <f aca="false">100+A67</f>
+        <v>163</v>
+      </c>
+      <c r="V67" s="23" t="n">
+        <f aca="false">200+A67</f>
+        <v>263</v>
+      </c>
+      <c r="W67" s="23" t="n">
+        <f aca="false">300+A67</f>
+        <v>363</v>
+      </c>
+      <c r="X67" s="23" t="str">
+        <f aca="false">"10."&amp;A67&amp;".1.0/24"</f>
+        <v>10.63.1.0/24</v>
+      </c>
+      <c r="Y67" s="23" t="str">
+        <f aca="false">IF(R67&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C67,$R$5:$R$92,R67)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q67)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F67&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="23" t="n">
@@ -21662,6 +24631,42 @@
         <f aca="false">IF(ISNA(MATCH(C68,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C68=A68,"OK",IF(INDEX($C$5:$C$92,MATCH(C68,Anlagen!$A$5:$A$92,0))&lt;&gt;C68,"Fehler: Standort hängt selbst an anderem Standort",IF(D68=A68,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D68,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D68,Anlagen!$A$5:$A$92,0))&lt;&gt;C68,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q68" s="23" t="str">
+        <f aca="false">Anlagen!AA68</f>
+        <v>NEUL</v>
+      </c>
+      <c r="R68" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB68&lt;&gt;"",Anlagen!AB68,COUNTIFS($C$5:$C$92,C68,$J$5:$J$92,"&lt;"&amp;J68)+1)</f>
+        <v>7</v>
+      </c>
+      <c r="S68" s="23" t="n">
+        <f aca="false">1000+200*(R68-1)+1</f>
+        <v>2201</v>
+      </c>
+      <c r="T68" s="23" t="n">
+        <f aca="false">1000+200*(R68-1)+Anlagen!F68</f>
+        <v>2262</v>
+      </c>
+      <c r="U68" s="23" t="n">
+        <f aca="false">100+A68</f>
+        <v>164</v>
+      </c>
+      <c r="V68" s="23" t="n">
+        <f aca="false">200+A68</f>
+        <v>264</v>
+      </c>
+      <c r="W68" s="23" t="n">
+        <f aca="false">300+A68</f>
+        <v>364</v>
+      </c>
+      <c r="X68" s="23" t="str">
+        <f aca="false">"10."&amp;A68&amp;".1.0/24"</f>
+        <v>10.64.1.0/24</v>
+      </c>
+      <c r="Y68" s="23" t="str">
+        <f aca="false">IF(R68&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C68,$R$5:$R$92,R68)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q68)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F68&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="23" t="n">
@@ -21728,6 +24733,42 @@
         <f aca="false">IF(ISNA(MATCH(C69,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C69=A69,"OK",IF(INDEX($C$5:$C$92,MATCH(C69,Anlagen!$A$5:$A$92,0))&lt;&gt;C69,"Fehler: Standort hängt selbst an anderem Standort",IF(D69=A69,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D69,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D69,Anlagen!$A$5:$A$92,0))&lt;&gt;C69,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q69" s="23" t="str">
+        <f aca="false">Anlagen!AA69</f>
+        <v>NSANS</v>
+      </c>
+      <c r="R69" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB69&lt;&gt;"",Anlagen!AB69,COUNTIFS($C$5:$C$92,C69,$J$5:$J$92,"&lt;"&amp;J69)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="S69" s="23" t="n">
+        <f aca="false">1000+200*(R69-1)+1</f>
+        <v>2401</v>
+      </c>
+      <c r="T69" s="23" t="n">
+        <f aca="false">1000+200*(R69-1)+Anlagen!F69</f>
+        <v>2477</v>
+      </c>
+      <c r="U69" s="23" t="n">
+        <f aca="false">100+A69</f>
+        <v>165</v>
+      </c>
+      <c r="V69" s="23" t="n">
+        <f aca="false">200+A69</f>
+        <v>265</v>
+      </c>
+      <c r="W69" s="23" t="n">
+        <f aca="false">300+A69</f>
+        <v>365</v>
+      </c>
+      <c r="X69" s="23" t="str">
+        <f aca="false">"10."&amp;A69&amp;".1.0/24"</f>
+        <v>10.65.1.0/24</v>
+      </c>
+      <c r="Y69" s="23" t="str">
+        <f aca="false">IF(R69&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C69,$R$5:$R$92,R69)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q69)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F69&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="23" t="n">
@@ -21794,6 +24835,42 @@
         <f aca="false">IF(ISNA(MATCH(C70,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C70=A70,"OK",IF(INDEX($C$5:$C$92,MATCH(C70,Anlagen!$A$5:$A$92,0))&lt;&gt;C70,"Fehler: Standort hängt selbst an anderem Standort",IF(D70=A70,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D70,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D70,Anlagen!$A$5:$A$92,0))&lt;&gt;C70,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q70" s="23" t="str">
+        <f aca="false">Anlagen!AA70</f>
+        <v>OASE</v>
+      </c>
+      <c r="R70" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB70&lt;&gt;"",Anlagen!AB70,COUNTIFS($C$5:$C$92,C70,$J$5:$J$92,"&lt;"&amp;J70)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="S70" s="23" t="n">
+        <f aca="false">1000+200*(R70-1)+1</f>
+        <v>2001</v>
+      </c>
+      <c r="T70" s="23" t="n">
+        <f aca="false">1000+200*(R70-1)+Anlagen!F70</f>
+        <v>2047</v>
+      </c>
+      <c r="U70" s="23" t="n">
+        <f aca="false">100+A70</f>
+        <v>166</v>
+      </c>
+      <c r="V70" s="23" t="n">
+        <f aca="false">200+A70</f>
+        <v>266</v>
+      </c>
+      <c r="W70" s="23" t="n">
+        <f aca="false">300+A70</f>
+        <v>366</v>
+      </c>
+      <c r="X70" s="23" t="str">
+        <f aca="false">"10."&amp;A70&amp;".1.0/24"</f>
+        <v>10.66.1.0/24</v>
+      </c>
+      <c r="Y70" s="23" t="str">
+        <f aca="false">IF(R70&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C70,$R$5:$R$92,R70)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q70)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F70&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="23" t="n">
@@ -21860,6 +24937,42 @@
         <f aca="false">IF(ISNA(MATCH(C71,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C71=A71,"OK",IF(INDEX($C$5:$C$92,MATCH(C71,Anlagen!$A$5:$A$92,0))&lt;&gt;C71,"Fehler: Standort hängt selbst an anderem Standort",IF(D71=A71,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D71,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D71,Anlagen!$A$5:$A$92,0))&lt;&gt;C71,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q71" s="23" t="str">
+        <f aca="false">Anlagen!AA71</f>
+        <v>PFERD</v>
+      </c>
+      <c r="R71" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB71&lt;&gt;"",Anlagen!AB71,COUNTIFS($C$5:$C$92,C71,$J$5:$J$92,"&lt;"&amp;J71)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S71" s="23" t="n">
+        <f aca="false">1000+200*(R71-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T71" s="23" t="n">
+        <f aca="false">1000+200*(R71-1)+Anlagen!F71</f>
+        <v>1255</v>
+      </c>
+      <c r="U71" s="23" t="n">
+        <f aca="false">100+A71</f>
+        <v>167</v>
+      </c>
+      <c r="V71" s="23" t="n">
+        <f aca="false">200+A71</f>
+        <v>267</v>
+      </c>
+      <c r="W71" s="23" t="n">
+        <f aca="false">300+A71</f>
+        <v>367</v>
+      </c>
+      <c r="X71" s="23" t="str">
+        <f aca="false">"10."&amp;A71&amp;".1.0/24"</f>
+        <v>10.67.1.0/24</v>
+      </c>
+      <c r="Y71" s="23" t="str">
+        <f aca="false">IF(R71&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C71,$R$5:$R$92,R71)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q71)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F71&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="23" t="n">
@@ -21926,6 +25039,42 @@
         <f aca="false">IF(ISNA(MATCH(C72,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C72=A72,"OK",IF(INDEX($C$5:$C$92,MATCH(C72,Anlagen!$A$5:$A$92,0))&lt;&gt;C72,"Fehler: Standort hängt selbst an anderem Standort",IF(D72=A72,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D72,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D72,Anlagen!$A$5:$A$92,0))&lt;&gt;C72,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q72" s="23" t="str">
+        <f aca="false">Anlagen!AA72</f>
+        <v>PLAN2</v>
+      </c>
+      <c r="R72" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB72&lt;&gt;"",Anlagen!AB72,COUNTIFS($C$5:$C$92,C72,$J$5:$J$92,"&lt;"&amp;J72)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="S72" s="23" t="n">
+        <f aca="false">1000+200*(R72-1)+1</f>
+        <v>2001</v>
+      </c>
+      <c r="T72" s="23" t="n">
+        <f aca="false">1000+200*(R72-1)+Anlagen!F72</f>
+        <v>2028</v>
+      </c>
+      <c r="U72" s="23" t="n">
+        <f aca="false">100+A72</f>
+        <v>168</v>
+      </c>
+      <c r="V72" s="23" t="n">
+        <f aca="false">200+A72</f>
+        <v>268</v>
+      </c>
+      <c r="W72" s="23" t="n">
+        <f aca="false">300+A72</f>
+        <v>368</v>
+      </c>
+      <c r="X72" s="23" t="str">
+        <f aca="false">"10."&amp;A72&amp;".1.0/24"</f>
+        <v>10.68.1.0/24</v>
+      </c>
+      <c r="Y72" s="23" t="str">
+        <f aca="false">IF(R72&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C72,$R$5:$R$92,R72)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q72)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F72&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="23" t="n">
@@ -21992,6 +25141,42 @@
         <f aca="false">IF(ISNA(MATCH(C73,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C73=A73,"OK",IF(INDEX($C$5:$C$92,MATCH(C73,Anlagen!$A$5:$A$92,0))&lt;&gt;C73,"Fehler: Standort hängt selbst an anderem Standort",IF(D73=A73,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D73,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D73,Anlagen!$A$5:$A$92,0))&lt;&gt;C73,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q73" s="23" t="str">
+        <f aca="false">Anlagen!AA73</f>
+        <v>PLEIN</v>
+      </c>
+      <c r="R73" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB73&lt;&gt;"",Anlagen!AB73,COUNTIFS($C$5:$C$92,C73,$J$5:$J$92,"&lt;"&amp;J73)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="S73" s="23" t="n">
+        <f aca="false">1000+200*(R73-1)+1</f>
+        <v>1201</v>
+      </c>
+      <c r="T73" s="23" t="n">
+        <f aca="false">1000+200*(R73-1)+Anlagen!F73</f>
+        <v>1248</v>
+      </c>
+      <c r="U73" s="23" t="n">
+        <f aca="false">100+A73</f>
+        <v>169</v>
+      </c>
+      <c r="V73" s="23" t="n">
+        <f aca="false">200+A73</f>
+        <v>269</v>
+      </c>
+      <c r="W73" s="23" t="n">
+        <f aca="false">300+A73</f>
+        <v>369</v>
+      </c>
+      <c r="X73" s="23" t="str">
+        <f aca="false">"10."&amp;A73&amp;".1.0/24"</f>
+        <v>10.69.1.0/24</v>
+      </c>
+      <c r="Y73" s="23" t="str">
+        <f aca="false">IF(R73&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C73,$R$5:$R$92,R73)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q73)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F73&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="23" t="n">
@@ -22058,6 +25243,42 @@
         <f aca="false">IF(ISNA(MATCH(C74,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C74=A74,"OK",IF(INDEX($C$5:$C$92,MATCH(C74,Anlagen!$A$5:$A$92,0))&lt;&gt;C74,"Fehler: Standort hängt selbst an anderem Standort",IF(D74=A74,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D74,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D74,Anlagen!$A$5:$A$92,0))&lt;&gt;C74,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q74" s="23" t="str">
+        <f aca="false">Anlagen!AA74</f>
+        <v>SFOAS</v>
+      </c>
+      <c r="R74" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB74&lt;&gt;"",Anlagen!AB74,COUNTIFS($C$5:$C$92,C74,$J$5:$J$92,"&lt;"&amp;J74)+1)</f>
+        <v>7</v>
+      </c>
+      <c r="S74" s="23" t="n">
+        <f aca="false">1000+200*(R74-1)+1</f>
+        <v>2201</v>
+      </c>
+      <c r="T74" s="23" t="n">
+        <f aca="false">1000+200*(R74-1)+Anlagen!F74</f>
+        <v>2215</v>
+      </c>
+      <c r="U74" s="23" t="n">
+        <f aca="false">100+A74</f>
+        <v>170</v>
+      </c>
+      <c r="V74" s="23" t="n">
+        <f aca="false">200+A74</f>
+        <v>270</v>
+      </c>
+      <c r="W74" s="23" t="n">
+        <f aca="false">300+A74</f>
+        <v>370</v>
+      </c>
+      <c r="X74" s="23" t="str">
+        <f aca="false">"10."&amp;A74&amp;".1.0/24"</f>
+        <v>10.70.1.0/24</v>
+      </c>
+      <c r="Y74" s="23" t="str">
+        <f aca="false">IF(R74&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C74,$R$5:$R$92,R74)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q74)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F74&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="23" t="n">
@@ -22124,6 +25345,42 @@
         <f aca="false">IF(ISNA(MATCH(C75,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C75=A75,"OK",IF(INDEX($C$5:$C$92,MATCH(C75,Anlagen!$A$5:$A$92,0))&lt;&gt;C75,"Fehler: Standort hängt selbst an anderem Standort",IF(D75=A75,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D75,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D75,Anlagen!$A$5:$A$92,0))&lt;&gt;C75,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q75" s="23" t="str">
+        <f aca="false">Anlagen!AA75</f>
+        <v>SANS</v>
+      </c>
+      <c r="R75" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB75&lt;&gt;"",Anlagen!AB75,COUNTIFS($C$5:$C$92,C75,$J$5:$J$92,"&lt;"&amp;J75)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="S75" s="23" t="n">
+        <f aca="false">1000+200*(R75-1)+1</f>
+        <v>2401</v>
+      </c>
+      <c r="T75" s="23" t="n">
+        <f aca="false">1000+200*(R75-1)+Anlagen!F75</f>
+        <v>2439</v>
+      </c>
+      <c r="U75" s="23" t="n">
+        <f aca="false">100+A75</f>
+        <v>171</v>
+      </c>
+      <c r="V75" s="23" t="n">
+        <f aca="false">200+A75</f>
+        <v>271</v>
+      </c>
+      <c r="W75" s="23" t="n">
+        <f aca="false">300+A75</f>
+        <v>371</v>
+      </c>
+      <c r="X75" s="23" t="str">
+        <f aca="false">"10."&amp;A75&amp;".1.0/24"</f>
+        <v>10.71.1.0/24</v>
+      </c>
+      <c r="Y75" s="23" t="str">
+        <f aca="false">IF(R75&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C75,$R$5:$R$92,R75)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q75)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F75&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="23" t="n">
@@ -22190,6 +25447,42 @@
         <f aca="false">IF(ISNA(MATCH(C76,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C76=A76,"OK",IF(INDEX($C$5:$C$92,MATCH(C76,Anlagen!$A$5:$A$92,0))&lt;&gt;C76,"Fehler: Standort hängt selbst an anderem Standort",IF(D76=A76,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D76,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D76,Anlagen!$A$5:$A$92,0))&lt;&gt;C76,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q76" s="23" t="str">
+        <f aca="false">Anlagen!AA76</f>
+        <v>SOMF1</v>
+      </c>
+      <c r="R76" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB76&lt;&gt;"",Anlagen!AB76,COUNTIFS($C$5:$C$92,C76,$J$5:$J$92,"&lt;"&amp;J76)+1)</f>
+        <v>7</v>
+      </c>
+      <c r="S76" s="23" t="n">
+        <f aca="false">1000+200*(R76-1)+1</f>
+        <v>2201</v>
+      </c>
+      <c r="T76" s="23" t="n">
+        <f aca="false">1000+200*(R76-1)+Anlagen!F76</f>
+        <v>2249</v>
+      </c>
+      <c r="U76" s="23" t="n">
+        <f aca="false">100+A76</f>
+        <v>172</v>
+      </c>
+      <c r="V76" s="23" t="n">
+        <f aca="false">200+A76</f>
+        <v>272</v>
+      </c>
+      <c r="W76" s="23" t="n">
+        <f aca="false">300+A76</f>
+        <v>372</v>
+      </c>
+      <c r="X76" s="23" t="str">
+        <f aca="false">"10."&amp;A76&amp;".1.0/24"</f>
+        <v>10.72.1.0/24</v>
+      </c>
+      <c r="Y76" s="23" t="str">
+        <f aca="false">IF(R76&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C76,$R$5:$R$92,R76)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q76)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F76&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="23" t="n">
@@ -22256,6 +25549,42 @@
         <f aca="false">IF(ISNA(MATCH(C77,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C77=A77,"OK",IF(INDEX($C$5:$C$92,MATCH(C77,Anlagen!$A$5:$A$92,0))&lt;&gt;C77,"Fehler: Standort hängt selbst an anderem Standort",IF(D77=A77,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D77,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D77,Anlagen!$A$5:$A$92,0))&lt;&gt;C77,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q77" s="23" t="str">
+        <f aca="false">Anlagen!AA77</f>
+        <v>SOMF2</v>
+      </c>
+      <c r="R77" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB77&lt;&gt;"",Anlagen!AB77,COUNTIFS($C$5:$C$92,C77,$J$5:$J$92,"&lt;"&amp;J77)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S77" s="23" t="n">
+        <f aca="false">1000+200*(R77-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T77" s="23" t="n">
+        <f aca="false">1000+200*(R77-1)+Anlagen!F77</f>
+        <v>1130</v>
+      </c>
+      <c r="U77" s="23" t="n">
+        <f aca="false">100+A77</f>
+        <v>173</v>
+      </c>
+      <c r="V77" s="23" t="n">
+        <f aca="false">200+A77</f>
+        <v>273</v>
+      </c>
+      <c r="W77" s="23" t="n">
+        <f aca="false">300+A77</f>
+        <v>373</v>
+      </c>
+      <c r="X77" s="23" t="str">
+        <f aca="false">"10."&amp;A77&amp;".1.0/24"</f>
+        <v>10.73.1.0/24</v>
+      </c>
+      <c r="Y77" s="23" t="str">
+        <f aca="false">IF(R77&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C77,$R$5:$R$92,R77)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q77)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F77&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="23" t="n">
@@ -22322,6 +25651,42 @@
         <f aca="false">IF(ISNA(MATCH(C78,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C78=A78,"OK",IF(INDEX($C$5:$C$92,MATCH(C78,Anlagen!$A$5:$A$92,0))&lt;&gt;C78,"Fehler: Standort hängt selbst an anderem Standort",IF(D78=A78,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D78,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D78,Anlagen!$A$5:$A$92,0))&lt;&gt;C78,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q78" s="23" t="str">
+        <f aca="false">Anlagen!AA78</f>
+        <v>SOROT</v>
+      </c>
+      <c r="R78" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB78&lt;&gt;"",Anlagen!AB78,COUNTIFS($C$5:$C$92,C78,$J$5:$J$92,"&lt;"&amp;J78)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="S78" s="23" t="n">
+        <f aca="false">1000+200*(R78-1)+1</f>
+        <v>2401</v>
+      </c>
+      <c r="T78" s="23" t="n">
+        <f aca="false">1000+200*(R78-1)+Anlagen!F78</f>
+        <v>2428</v>
+      </c>
+      <c r="U78" s="23" t="n">
+        <f aca="false">100+A78</f>
+        <v>174</v>
+      </c>
+      <c r="V78" s="23" t="n">
+        <f aca="false">200+A78</f>
+        <v>274</v>
+      </c>
+      <c r="W78" s="23" t="n">
+        <f aca="false">300+A78</f>
+        <v>374</v>
+      </c>
+      <c r="X78" s="23" t="str">
+        <f aca="false">"10."&amp;A78&amp;".1.0/24"</f>
+        <v>10.74.1.0/24</v>
+      </c>
+      <c r="Y78" s="23" t="str">
+        <f aca="false">IF(R78&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C78,$R$5:$R$92,R78)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q78)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F78&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="23" t="n">
@@ -22388,6 +25753,42 @@
         <f aca="false">IF(ISNA(MATCH(C79,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C79=A79,"OK",IF(INDEX($C$5:$C$92,MATCH(C79,Anlagen!$A$5:$A$92,0))&lt;&gt;C79,"Fehler: Standort hängt selbst an anderem Standort",IF(D79=A79,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D79,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D79,Anlagen!$A$5:$A$92,0))&lt;&gt;C79,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q79" s="23" t="str">
+        <f aca="false">Anlagen!AA79</f>
+        <v>SOSCH</v>
+      </c>
+      <c r="R79" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB79&lt;&gt;"",Anlagen!AB79,COUNTIFS($C$5:$C$92,C79,$J$5:$J$92,"&lt;"&amp;J79)+1)</f>
+        <v>7</v>
+      </c>
+      <c r="S79" s="23" t="n">
+        <f aca="false">1000+200*(R79-1)+1</f>
+        <v>2201</v>
+      </c>
+      <c r="T79" s="23" t="n">
+        <f aca="false">1000+200*(R79-1)+Anlagen!F79</f>
+        <v>2240</v>
+      </c>
+      <c r="U79" s="23" t="n">
+        <f aca="false">100+A79</f>
+        <v>175</v>
+      </c>
+      <c r="V79" s="23" t="n">
+        <f aca="false">200+A79</f>
+        <v>275</v>
+      </c>
+      <c r="W79" s="23" t="n">
+        <f aca="false">300+A79</f>
+        <v>375</v>
+      </c>
+      <c r="X79" s="23" t="str">
+        <f aca="false">"10."&amp;A79&amp;".1.0/24"</f>
+        <v>10.75.1.0/24</v>
+      </c>
+      <c r="Y79" s="23" t="str">
+        <f aca="false">IF(R79&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C79,$R$5:$R$92,R79)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q79)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F79&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="23" t="n">
@@ -22454,6 +25855,42 @@
         <f aca="false">IF(ISNA(MATCH(C80,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C80=A80,"OK",IF(INDEX($C$5:$C$92,MATCH(C80,Anlagen!$A$5:$A$92,0))&lt;&gt;C80,"Fehler: Standort hängt selbst an anderem Standort",IF(D80=A80,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D80,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D80,Anlagen!$A$5:$A$92,0))&lt;&gt;C80,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q80" s="23" t="str">
+        <f aca="false">Anlagen!AA80</f>
+        <v>SOWIN</v>
+      </c>
+      <c r="R80" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB80&lt;&gt;"",Anlagen!AB80,COUNTIFS($C$5:$C$92,C80,$J$5:$J$92,"&lt;"&amp;J80)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="S80" s="23" t="n">
+        <f aca="false">1000+200*(R80-1)+1</f>
+        <v>2401</v>
+      </c>
+      <c r="T80" s="23" t="n">
+        <f aca="false">1000+200*(R80-1)+Anlagen!F80</f>
+        <v>2448</v>
+      </c>
+      <c r="U80" s="23" t="n">
+        <f aca="false">100+A80</f>
+        <v>176</v>
+      </c>
+      <c r="V80" s="23" t="n">
+        <f aca="false">200+A80</f>
+        <v>276</v>
+      </c>
+      <c r="W80" s="23" t="n">
+        <f aca="false">300+A80</f>
+        <v>376</v>
+      </c>
+      <c r="X80" s="23" t="str">
+        <f aca="false">"10."&amp;A80&amp;".1.0/24"</f>
+        <v>10.76.1.0/24</v>
+      </c>
+      <c r="Y80" s="23" t="str">
+        <f aca="false">IF(R80&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C80,$R$5:$R$92,R80)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q80)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F80&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="23" t="n">
@@ -22520,6 +25957,42 @@
         <f aca="false">IF(ISNA(MATCH(C81,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C81=A81,"OK",IF(INDEX($C$5:$C$92,MATCH(C81,Anlagen!$A$5:$A$92,0))&lt;&gt;C81,"Fehler: Standort hängt selbst an anderem Standort",IF(D81=A81,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D81,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D81,Anlagen!$A$5:$A$92,0))&lt;&gt;C81,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q81" s="23" t="str">
+        <f aca="false">Anlagen!AA81</f>
+        <v>SORG1</v>
+      </c>
+      <c r="R81" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB81&lt;&gt;"",Anlagen!AB81,COUNTIFS($C$5:$C$92,C81,$J$5:$J$92,"&lt;"&amp;J81)+1)</f>
+        <v>9</v>
+      </c>
+      <c r="S81" s="23" t="n">
+        <f aca="false">1000+200*(R81-1)+1</f>
+        <v>2601</v>
+      </c>
+      <c r="T81" s="23" t="n">
+        <f aca="false">1000+200*(R81-1)+Anlagen!F81</f>
+        <v>2645</v>
+      </c>
+      <c r="U81" s="23" t="n">
+        <f aca="false">100+A81</f>
+        <v>177</v>
+      </c>
+      <c r="V81" s="23" t="n">
+        <f aca="false">200+A81</f>
+        <v>277</v>
+      </c>
+      <c r="W81" s="23" t="n">
+        <f aca="false">300+A81</f>
+        <v>377</v>
+      </c>
+      <c r="X81" s="23" t="str">
+        <f aca="false">"10."&amp;A81&amp;".1.0/24"</f>
+        <v>10.77.1.0/24</v>
+      </c>
+      <c r="Y81" s="23" t="str">
+        <f aca="false">IF(R81&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C81,$R$5:$R$92,R81)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q81)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F81&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="23" t="n">
@@ -22586,6 +26059,42 @@
         <f aca="false">IF(ISNA(MATCH(C82,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C82=A82,"OK",IF(INDEX($C$5:$C$92,MATCH(C82,Anlagen!$A$5:$A$92,0))&lt;&gt;C82,"Fehler: Standort hängt selbst an anderem Standort",IF(D82=A82,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D82,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D82,Anlagen!$A$5:$A$92,0))&lt;&gt;C82,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q82" s="23" t="str">
+        <f aca="false">Anlagen!AA82</f>
+        <v>SORG2</v>
+      </c>
+      <c r="R82" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB82&lt;&gt;"",Anlagen!AB82,COUNTIFS($C$5:$C$92,C82,$J$5:$J$92,"&lt;"&amp;J82)+1)</f>
+        <v>9</v>
+      </c>
+      <c r="S82" s="23" t="n">
+        <f aca="false">1000+200*(R82-1)+1</f>
+        <v>2601</v>
+      </c>
+      <c r="T82" s="23" t="n">
+        <f aca="false">1000+200*(R82-1)+Anlagen!F82</f>
+        <v>2623</v>
+      </c>
+      <c r="U82" s="23" t="n">
+        <f aca="false">100+A82</f>
+        <v>178</v>
+      </c>
+      <c r="V82" s="23" t="n">
+        <f aca="false">200+A82</f>
+        <v>278</v>
+      </c>
+      <c r="W82" s="23" t="n">
+        <f aca="false">300+A82</f>
+        <v>378</v>
+      </c>
+      <c r="X82" s="23" t="str">
+        <f aca="false">"10."&amp;A82&amp;".1.0/24"</f>
+        <v>10.78.1.0/24</v>
+      </c>
+      <c r="Y82" s="23" t="str">
+        <f aca="false">IF(R82&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C82,$R$5:$R$92,R82)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q82)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F82&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="23" t="n">
@@ -22652,6 +26161,42 @@
         <f aca="false">IF(ISNA(MATCH(C83,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C83=A83,"OK",IF(INDEX($C$5:$C$92,MATCH(C83,Anlagen!$A$5:$A$92,0))&lt;&gt;C83,"Fehler: Standort hängt selbst an anderem Standort",IF(D83=A83,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D83,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D83,Anlagen!$A$5:$A$92,0))&lt;&gt;C83,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q83" s="23" t="str">
+        <f aca="false">Anlagen!AA83</f>
+        <v>SPORT</v>
+      </c>
+      <c r="R83" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB83&lt;&gt;"",Anlagen!AB83,COUNTIFS($C$5:$C$92,C83,$J$5:$J$92,"&lt;"&amp;J83)+1)</f>
+        <v>9</v>
+      </c>
+      <c r="S83" s="23" t="n">
+        <f aca="false">1000+200*(R83-1)+1</f>
+        <v>2601</v>
+      </c>
+      <c r="T83" s="23" t="n">
+        <f aca="false">1000+200*(R83-1)+Anlagen!F83</f>
+        <v>2637</v>
+      </c>
+      <c r="U83" s="23" t="n">
+        <f aca="false">100+A83</f>
+        <v>179</v>
+      </c>
+      <c r="V83" s="23" t="n">
+        <f aca="false">200+A83</f>
+        <v>279</v>
+      </c>
+      <c r="W83" s="23" t="n">
+        <f aca="false">300+A83</f>
+        <v>379</v>
+      </c>
+      <c r="X83" s="23" t="str">
+        <f aca="false">"10."&amp;A83&amp;".1.0/24"</f>
+        <v>10.79.1.0/24</v>
+      </c>
+      <c r="Y83" s="23" t="str">
+        <f aca="false">IF(R83&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C83,$R$5:$R$92,R83)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q83)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F83&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="23" t="n">
@@ -22718,6 +26263,42 @@
         <f aca="false">IF(ISNA(MATCH(C84,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C84=A84,"OK",IF(INDEX($C$5:$C$92,MATCH(C84,Anlagen!$A$5:$A$92,0))&lt;&gt;C84,"Fehler: Standort hängt selbst an anderem Standort",IF(D84=A84,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D84,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D84,Anlagen!$A$5:$A$92,0))&lt;&gt;C84,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q84" s="23" t="str">
+        <f aca="false">Anlagen!AA84</f>
+        <v>STILL</v>
+      </c>
+      <c r="R84" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB84&lt;&gt;"",Anlagen!AB84,COUNTIFS($C$5:$C$92,C84,$J$5:$J$92,"&lt;"&amp;J84)+1)</f>
+        <v>10</v>
+      </c>
+      <c r="S84" s="23" t="n">
+        <f aca="false">1000+200*(R84-1)+1</f>
+        <v>2801</v>
+      </c>
+      <c r="T84" s="23" t="n">
+        <f aca="false">1000+200*(R84-1)+Anlagen!F84</f>
+        <v>2850</v>
+      </c>
+      <c r="U84" s="23" t="n">
+        <f aca="false">100+A84</f>
+        <v>180</v>
+      </c>
+      <c r="V84" s="23" t="n">
+        <f aca="false">200+A84</f>
+        <v>280</v>
+      </c>
+      <c r="W84" s="23" t="n">
+        <f aca="false">300+A84</f>
+        <v>380</v>
+      </c>
+      <c r="X84" s="23" t="str">
+        <f aca="false">"10."&amp;A84&amp;".1.0/24"</f>
+        <v>10.80.1.0/24</v>
+      </c>
+      <c r="Y84" s="23" t="str">
+        <f aca="false">IF(R84&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C84,$R$5:$R$92,R84)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q84)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F84&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="23" t="n">
@@ -22784,6 +26365,42 @@
         <f aca="false">IF(ISNA(MATCH(C85,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C85=A85,"OK",IF(INDEX($C$5:$C$92,MATCH(C85,Anlagen!$A$5:$A$92,0))&lt;&gt;C85,"Fehler: Standort hängt selbst an anderem Standort",IF(D85=A85,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D85,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D85,Anlagen!$A$5:$A$92,0))&lt;&gt;C85,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q85" s="23" t="str">
+        <f aca="false">Anlagen!AA85</f>
+        <v>TRAUM</v>
+      </c>
+      <c r="R85" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB85&lt;&gt;"",Anlagen!AB85,COUNTIFS($C$5:$C$92,C85,$J$5:$J$92,"&lt;"&amp;J85)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S85" s="23" t="n">
+        <f aca="false">1000+200*(R85-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T85" s="23" t="n">
+        <f aca="false">1000+200*(R85-1)+Anlagen!F85</f>
+        <v>1049</v>
+      </c>
+      <c r="U85" s="23" t="n">
+        <f aca="false">100+A85</f>
+        <v>181</v>
+      </c>
+      <c r="V85" s="23" t="n">
+        <f aca="false">200+A85</f>
+        <v>281</v>
+      </c>
+      <c r="W85" s="23" t="n">
+        <f aca="false">300+A85</f>
+        <v>381</v>
+      </c>
+      <c r="X85" s="23" t="str">
+        <f aca="false">"10."&amp;A85&amp;".1.0/24"</f>
+        <v>10.81.1.0/24</v>
+      </c>
+      <c r="Y85" s="23" t="str">
+        <f aca="false">IF(R85&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C85,$R$5:$R$92,R85)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q85)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F85&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="23" t="n">
@@ -22850,6 +26467,42 @@
         <f aca="false">IF(ISNA(MATCH(C86,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C86=A86,"OK",IF(INDEX($C$5:$C$92,MATCH(C86,Anlagen!$A$5:$A$92,0))&lt;&gt;C86,"Fehler: Standort hängt selbst an anderem Standort",IF(D86=A86,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D86,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D86,Anlagen!$A$5:$A$92,0))&lt;&gt;C86,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q86" s="23" t="str">
+        <f aca="false">Anlagen!AA86</f>
+        <v>WALDF</v>
+      </c>
+      <c r="R86" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB86&lt;&gt;"",Anlagen!AB86,COUNTIFS($C$5:$C$92,C86,$J$5:$J$92,"&lt;"&amp;J86)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="S86" s="23" t="n">
+        <f aca="false">1000+200*(R86-1)+1</f>
+        <v>2401</v>
+      </c>
+      <c r="T86" s="23" t="n">
+        <f aca="false">1000+200*(R86-1)+Anlagen!F86</f>
+        <v>2490</v>
+      </c>
+      <c r="U86" s="23" t="n">
+        <f aca="false">100+A86</f>
+        <v>182</v>
+      </c>
+      <c r="V86" s="23" t="n">
+        <f aca="false">200+A86</f>
+        <v>282</v>
+      </c>
+      <c r="W86" s="23" t="n">
+        <f aca="false">300+A86</f>
+        <v>382</v>
+      </c>
+      <c r="X86" s="23" t="str">
+        <f aca="false">"10."&amp;A86&amp;".1.0/24"</f>
+        <v>10.82.1.0/24</v>
+      </c>
+      <c r="Y86" s="23" t="str">
+        <f aca="false">IF(R86&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C86,$R$5:$R$92,R86)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q86)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F86&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="23" t="n">
@@ -22916,6 +26569,42 @@
         <f aca="false">IF(ISNA(MATCH(C87,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C87=A87,"OK",IF(INDEX($C$5:$C$92,MATCH(C87,Anlagen!$A$5:$A$92,0))&lt;&gt;C87,"Fehler: Standort hängt selbst an anderem Standort",IF(D87=A87,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D87,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D87,Anlagen!$A$5:$A$92,0))&lt;&gt;C87,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q87" s="23" t="str">
+        <f aca="false">Anlagen!AA87</f>
+        <v>WEINM</v>
+      </c>
+      <c r="R87" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB87&lt;&gt;"",Anlagen!AB87,COUNTIFS($C$5:$C$92,C87,$J$5:$J$92,"&lt;"&amp;J87)+1)</f>
+        <v>9</v>
+      </c>
+      <c r="S87" s="23" t="n">
+        <f aca="false">1000+200*(R87-1)+1</f>
+        <v>2601</v>
+      </c>
+      <c r="T87" s="23" t="n">
+        <f aca="false">1000+200*(R87-1)+Anlagen!F87</f>
+        <v>2626</v>
+      </c>
+      <c r="U87" s="23" t="n">
+        <f aca="false">100+A87</f>
+        <v>183</v>
+      </c>
+      <c r="V87" s="23" t="n">
+        <f aca="false">200+A87</f>
+        <v>283</v>
+      </c>
+      <c r="W87" s="23" t="n">
+        <f aca="false">300+A87</f>
+        <v>383</v>
+      </c>
+      <c r="X87" s="23" t="str">
+        <f aca="false">"10."&amp;A87&amp;".1.0/24"</f>
+        <v>10.83.1.0/24</v>
+      </c>
+      <c r="Y87" s="23" t="str">
+        <f aca="false">IF(R87&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C87,$R$5:$R$92,R87)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q87)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F87&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="23" t="n">
@@ -22982,6 +26671,42 @@
         <f aca="false">IF(ISNA(MATCH(C88,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C88=A88,"OK",IF(INDEX($C$5:$C$92,MATCH(C88,Anlagen!$A$5:$A$92,0))&lt;&gt;C88,"Fehler: Standort hängt selbst an anderem Standort",IF(D88=A88,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D88,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D88,Anlagen!$A$5:$A$92,0))&lt;&gt;C88,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q88" s="23" t="str">
+        <f aca="false">Anlagen!AA88</f>
+        <v>WITTS</v>
+      </c>
+      <c r="R88" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB88&lt;&gt;"",Anlagen!AB88,COUNTIFS($C$5:$C$92,C88,$J$5:$J$92,"&lt;"&amp;J88)+1)</f>
+        <v>11</v>
+      </c>
+      <c r="S88" s="23" t="n">
+        <f aca="false">1000+200*(R88-1)+1</f>
+        <v>3001</v>
+      </c>
+      <c r="T88" s="23" t="n">
+        <f aca="false">1000+200*(R88-1)+Anlagen!F88</f>
+        <v>3054</v>
+      </c>
+      <c r="U88" s="23" t="n">
+        <f aca="false">100+A88</f>
+        <v>184</v>
+      </c>
+      <c r="V88" s="23" t="n">
+        <f aca="false">200+A88</f>
+        <v>284</v>
+      </c>
+      <c r="W88" s="23" t="n">
+        <f aca="false">300+A88</f>
+        <v>384</v>
+      </c>
+      <c r="X88" s="23" t="str">
+        <f aca="false">"10."&amp;A88&amp;".1.0/24"</f>
+        <v>10.84.1.0/24</v>
+      </c>
+      <c r="Y88" s="23" t="str">
+        <f aca="false">IF(R88&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C88,$R$5:$R$92,R88)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q88)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F88&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="23" t="n">
@@ -23048,6 +26773,42 @@
         <f aca="false">IF(ISNA(MATCH(C89,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C89=A89,"OK",IF(INDEX($C$5:$C$92,MATCH(C89,Anlagen!$A$5:$A$92,0))&lt;&gt;C89,"Fehler: Standort hängt selbst an anderem Standort",IF(D89=A89,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D89,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D89,Anlagen!$A$5:$A$92,0))&lt;&gt;C89,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q89" s="23" t="str">
+        <f aca="false">Anlagen!AA89</f>
+        <v>ZUKUN</v>
+      </c>
+      <c r="R89" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB89&lt;&gt;"",Anlagen!AB89,COUNTIFS($C$5:$C$92,C89,$J$5:$J$92,"&lt;"&amp;J89)+1)</f>
+        <v>1</v>
+      </c>
+      <c r="S89" s="23" t="n">
+        <f aca="false">1000+200*(R89-1)+1</f>
+        <v>1001</v>
+      </c>
+      <c r="T89" s="23" t="n">
+        <f aca="false">1000+200*(R89-1)+Anlagen!F89</f>
+        <v>1085</v>
+      </c>
+      <c r="U89" s="23" t="n">
+        <f aca="false">100+A89</f>
+        <v>185</v>
+      </c>
+      <c r="V89" s="23" t="n">
+        <f aca="false">200+A89</f>
+        <v>285</v>
+      </c>
+      <c r="W89" s="23" t="n">
+        <f aca="false">300+A89</f>
+        <v>385</v>
+      </c>
+      <c r="X89" s="23" t="str">
+        <f aca="false">"10."&amp;A89&amp;".1.0/24"</f>
+        <v>10.85.1.0/24</v>
+      </c>
+      <c r="Y89" s="23" t="str">
+        <f aca="false">IF(R89&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C89,$R$5:$R$92,R89)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q89)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F89&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="23" t="n">
@@ -23114,6 +26875,42 @@
         <f aca="false">IF(ISNA(MATCH(C90,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C90=A90,"OK",IF(INDEX($C$5:$C$92,MATCH(C90,Anlagen!$A$5:$A$92,0))&lt;&gt;C90,"Fehler: Standort hängt selbst an anderem Standort",IF(D90=A90,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D90,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D90,Anlagen!$A$5:$A$92,0))&lt;&gt;C90,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q90" s="23" t="str">
+        <f aca="false">Anlagen!AA90</f>
+        <v>BURGW</v>
+      </c>
+      <c r="R90" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB90&lt;&gt;"",Anlagen!AB90,COUNTIFS($C$5:$C$92,C90,$J$5:$J$92,"&lt;"&amp;J90)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="S90" s="23" t="n">
+        <f aca="false">1000+200*(R90-1)+1</f>
+        <v>1801</v>
+      </c>
+      <c r="T90" s="23" t="n">
+        <f aca="false">1000+200*(R90-1)+Anlagen!F90</f>
+        <v>1809</v>
+      </c>
+      <c r="U90" s="23" t="n">
+        <f aca="false">100+A90</f>
+        <v>186</v>
+      </c>
+      <c r="V90" s="23" t="n">
+        <f aca="false">200+A90</f>
+        <v>286</v>
+      </c>
+      <c r="W90" s="23" t="n">
+        <f aca="false">300+A90</f>
+        <v>386</v>
+      </c>
+      <c r="X90" s="23" t="str">
+        <f aca="false">"10."&amp;A90&amp;".1.0/24"</f>
+        <v>10.86.1.0/24</v>
+      </c>
+      <c r="Y90" s="23" t="str">
+        <f aca="false">IF(R90&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C90,$R$5:$R$92,R90)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q90)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F90&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="23" t="n">
@@ -23180,6 +26977,42 @@
         <f aca="false">IF(ISNA(MATCH(C91,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C91=A91,"OK",IF(INDEX($C$5:$C$92,MATCH(C91,Anlagen!$A$5:$A$92,0))&lt;&gt;C91,"Fehler: Standort hängt selbst an anderem Standort",IF(D91=A91,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D91,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D91,Anlagen!$A$5:$A$92,0))&lt;&gt;C91,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q91" s="23" t="str">
+        <f aca="false">Anlagen!AA91</f>
+        <v>KUEHL</v>
+      </c>
+      <c r="R91" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB91&lt;&gt;"",Anlagen!AB91,COUNTIFS($C$5:$C$92,C91,$J$5:$J$92,"&lt;"&amp;J91)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="S91" s="23" t="n">
+        <f aca="false">1000+200*(R91-1)+1</f>
+        <v>2001</v>
+      </c>
+      <c r="T91" s="23" t="n">
+        <f aca="false">1000+200*(R91-1)+Anlagen!F91</f>
+        <v>2026</v>
+      </c>
+      <c r="U91" s="23" t="n">
+        <f aca="false">100+A91</f>
+        <v>187</v>
+      </c>
+      <c r="V91" s="23" t="n">
+        <f aca="false">200+A91</f>
+        <v>287</v>
+      </c>
+      <c r="W91" s="23" t="n">
+        <f aca="false">300+A91</f>
+        <v>387</v>
+      </c>
+      <c r="X91" s="23" t="str">
+        <f aca="false">"10."&amp;A91&amp;".1.0/24"</f>
+        <v>10.87.1.0/24</v>
+      </c>
+      <c r="Y91" s="23" t="str">
+        <f aca="false">IF(R91&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C91,$R$5:$R$92,R91)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q91)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F91&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="23" t="n">
@@ -23246,10 +27079,46 @@
         <f aca="false">IF(ISNA(MATCH(C92,Anlagen!$A$5:$A$92,0)),"Fehler: Standort unbekannt",IF(C92=A92,"OK",IF(INDEX($C$5:$C$92,MATCH(C92,Anlagen!$A$5:$A$92,0))&lt;&gt;C92,"Fehler: Standort hängt selbst an anderem Standort",IF(D92=A92,"Fehler: Zuleitung von sich selbst",IF(ISNA(MATCH(D92,Anlagen!$A$5:$A$92,0)),"Fehler: Zuleitung unbekannt",IF(INDEX($C$5:$C$92,MATCH(D92,Anlagen!$A$5:$A$92,0))&lt;&gt;C92,"Fehler: Zuleitung hängt an anderem Standort","OK"))))))</f>
         <v>OK</v>
       </c>
+      <c r="Q92" s="23" t="str">
+        <f aca="false">Anlagen!AA92</f>
+        <v>INSEL</v>
+      </c>
+      <c r="R92" s="23" t="n">
+        <f aca="false">IF(Anlagen!AB92&lt;&gt;"",Anlagen!AB92,COUNTIFS($C$5:$C$92,C92,$J$5:$J$92,"&lt;"&amp;J92)+1)</f>
+        <v>9</v>
+      </c>
+      <c r="S92" s="23" t="n">
+        <f aca="false">1000+200*(R92-1)+1</f>
+        <v>2601</v>
+      </c>
+      <c r="T92" s="23" t="n">
+        <f aca="false">1000+200*(R92-1)+Anlagen!F92</f>
+        <v>2686</v>
+      </c>
+      <c r="U92" s="23" t="n">
+        <f aca="false">100+A92</f>
+        <v>188</v>
+      </c>
+      <c r="V92" s="23" t="n">
+        <f aca="false">200+A92</f>
+        <v>288</v>
+      </c>
+      <c r="W92" s="23" t="n">
+        <f aca="false">300+A92</f>
+        <v>388</v>
+      </c>
+      <c r="X92" s="23" t="str">
+        <f aca="false">"10."&amp;A92&amp;".1.0/24"</f>
+        <v>10.88.1.0/24</v>
+      </c>
+      <c r="Y92" s="23" t="str">
+        <f aca="false">IF(R92&gt;15,"Fehler: VLAN-Block über 15",IF(COUNTIFS($C$5:$C$92,C92,$R$5:$R$92,R92)&gt;1,"Fehler: VLAN-Block am Standort doppelt",IF(COUNTIF($Q$5:$Q$92,Q92)&gt;1,"Fehler: Kürzel doppelt",IF(Anlagen!F92&gt;199,"Fehler: mehr als 199 Parzellen","OK"))))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="32" t="s">
-        <v>419</v>
+        <v>518</v>
       </c>
       <c r="G93" s="33" t="n">
         <f aca="false">SUM(G5:G92)</f>
@@ -23268,14 +27137,24 @@
         <v>2814.81360437705</v>
       </c>
     </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="Y5:Y92">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>LEFT(Y5,6)="Fehler"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P5:P92">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>LEFT(P5,6)="Fehler"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E92">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>E5="Gateway-Standort"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23317,68 +27196,68 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>420</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>421</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>422</v>
+        <v>522</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>423</v>
+        <v>523</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>424</v>
+        <v>524</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>425</v>
+        <v>525</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>426</v>
+        <v>526</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>427</v>
+        <v>527</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>428</v>
+        <v>528</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>429</v>
+        <v>529</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>430</v>
+        <v>530</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>431</v>
+        <v>531</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>432</v>
+        <v>532</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>433</v>
+        <v>533</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>434</v>
+        <v>534</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>435</v>
+        <v>535</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>436</v>
+        <v>536</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>437</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29895,7 +33774,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="32" t="s">
-        <v>419</v>
+        <v>518</v>
       </c>
       <c r="C93" s="33" t="n">
         <f aca="false">SUM(C5:C92)</f>
@@ -29964,7 +33843,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="2" t="s">
-        <v>438</v>
+        <v>538</v>
       </c>
       <c r="Q95" s="40" t="n">
         <f aca="false">INDEX(Q5:Q92,MATCH(20,A5:A92,0))</f>
@@ -30004,62 +33883,62 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>439</v>
+        <v>539</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>440</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>441</v>
+        <v>541</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>442</v>
+        <v>542</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>443</v>
+        <v>543</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>444</v>
+        <v>544</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>445</v>
+        <v>545</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>446</v>
+        <v>546</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>447</v>
+        <v>547</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>448</v>
+        <v>548</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>449</v>
+        <v>549</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>418</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35872,7 +39751,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="32" t="s">
-        <v>419</v>
+        <v>518</v>
       </c>
       <c r="C93" s="35" t="n">
         <f aca="false">COUNTIF(Netz!E5:E92,"Gateway-Standort")+COUNTIF(Netz!E5:E92,"eigenständig")</f>
@@ -35953,56 +39832,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>451</v>
+        <v>551</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>452</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>417</v>
+        <v>508</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>453</v>
+        <v>553</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>454</v>
+        <v>554</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>455</v>
+        <v>555</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>456</v>
+        <v>556</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>457</v>
+        <v>557</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41111,7 +44990,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="32" t="s">
-        <v>419</v>
+        <v>518</v>
       </c>
       <c r="E93" s="33" t="n">
         <f aca="false">SUM(E5:E92)</f>
